--- a/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_TecnolLogistica_VNAL.xlsx
+++ b/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_TecnolLogistica_VNAL.xlsx
@@ -5,19 +5,19 @@
   <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/micortes_poligran_edu_co/Documents/Escritorio/FORMATOS RA CICLO UNO RC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Analisis_Curricular/data/raw/FORMATOS RA CICLO UNO RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="812" documentId="13_ncr:1_{523E9347-1CEE-415F-A1AF-C055F087266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CE81520-70D5-4443-A75B-6CB89613D0C1}"/>
+  <xr:revisionPtr revIDLastSave="815" documentId="13_ncr:1_{523E9347-1CEE-415F-A1AF-C055F087266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC3EA0F7-65A0-406E-8149-E6EEE82C22E7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
   </bookViews>
   <sheets>
     <sheet name="Paso1 Analisis perfil egreso" sheetId="1" r:id="rId1"/>
     <sheet name="Paso 2 Redacción competen" sheetId="6" r:id="rId2"/>
     <sheet name="Paso 3 Redacción RA " sheetId="5" r:id="rId3"/>
     <sheet name="Paso 4 Estrategias mesocurricu" sheetId="8" r:id="rId4"/>
-    <sheet name="P5 Estrat microcurricu" sheetId="10" r:id="rId5"/>
+    <sheet name="Paso 5 Estrategias microcurr" sheetId="10" r:id="rId5"/>
     <sheet name="Taxonomia para Competencias" sheetId="11" r:id="rId6"/>
     <sheet name="Taxonomias para RA" sheetId="9" r:id="rId7"/>
   </sheets>
@@ -25,9 +25,9 @@
     <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'P5 Estrat microcurricu'!$A$1:$Q$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Paso 3 Redacción RA '!$A$2:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Paso 4 Estrategias mesocurricu'!$A$2:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Paso 5 Estrategias microcurr'!$A$1:$Q$108</definedName>
     <definedName name="actitudinalB" localSheetId="4">Tabla5785[ActitudinalB]</definedName>
     <definedName name="actitudinalB">Tabla5785[ActitudinalB]</definedName>
     <definedName name="ActitudinalBAK">'Taxonomias para RA'!$AC$3:$AG$3</definedName>
@@ -4108,14 +4108,69 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4124,12 +4179,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4168,14 +4217,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4197,49 +4240,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8356,23 +8356,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FA7EDF-246F-4EE0-BFE4-7EACACD45C48}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="76.26953125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="76.21875" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" style="21" customWidth="1"/>
-    <col min="2" max="2" width="17.1796875" style="21" customWidth="1"/>
+    <col min="1" max="1" width="23.21875" style="21" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" style="21" customWidth="1"/>
     <col min="3" max="3" width="40" style="21" customWidth="1"/>
-    <col min="4" max="4" width="52.1796875" style="21" customWidth="1"/>
-    <col min="5" max="5" width="32.1796875" style="21" customWidth="1"/>
+    <col min="4" max="4" width="52.21875" style="21" customWidth="1"/>
+    <col min="5" max="5" width="32.21875" style="21" customWidth="1"/>
     <col min="6" max="6" width="34" style="12" customWidth="1"/>
     <col min="7" max="7" width="51" style="21" customWidth="1"/>
-    <col min="8" max="8" width="25.1796875" style="21" customWidth="1"/>
+    <col min="8" max="8" width="25.21875" style="21" customWidth="1"/>
     <col min="9" max="9" width="67" style="21" customWidth="1"/>
-    <col min="10" max="10" width="26.453125" style="21" customWidth="1"/>
+    <col min="10" max="10" width="26.44140625" style="21" customWidth="1"/>
     <col min="11" max="11" width="49" style="21" customWidth="1"/>
-    <col min="12" max="16384" width="76.26953125" style="21"/>
+    <col min="12" max="16384" width="76.21875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="19" customFormat="1" ht="55.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="19" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -8385,21 +8385,21 @@
       <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="117" t="s">
+      <c r="E1" s="134" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117" t="s">
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
       <c r="K1" s="104" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="105" t="s">
         <v>7</v>
       </c>
@@ -8434,17 +8434,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="116" t="s">
+    <row r="3" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="116" t="s">
+      <c r="B3" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="118" t="s">
+      <c r="C3" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="118" t="s">
+      <c r="D3" s="126" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="16" t="s">
@@ -8456,24 +8456,24 @@
       <c r="G3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="118" t="s">
+      <c r="H3" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="118" t="s">
+      <c r="I3" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="118" t="s">
+      <c r="J3" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="116" t="s">
+      <c r="K3" s="119" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="82.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="116"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
+    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.3">
+      <c r="A4" s="119"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="126"/>
       <c r="E4" s="16" t="s">
         <v>29</v>
       </c>
@@ -8483,16 +8483,16 @@
       <c r="G4" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="116"/>
-    </row>
-    <row r="5" spans="1:11" ht="62.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="116"/>
-      <c r="B5" s="116"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="126"/>
+      <c r="J4" s="126"/>
+      <c r="K4" s="119"/>
+    </row>
+    <row r="5" spans="1:11" ht="62.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="119"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
       <c r="E5" s="27" t="s">
         <v>32</v>
       </c>
@@ -8502,16 +8502,16 @@
       <c r="G5" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="116"/>
-    </row>
-    <row r="6" spans="1:11" ht="66" x14ac:dyDescent="0.35">
-      <c r="A6" s="116"/>
-      <c r="B6" s="116"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="119"/>
+    </row>
+    <row r="6" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="119"/>
+      <c r="B6" s="119"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
       <c r="E6" s="21" t="s">
         <v>35</v>
       </c>
@@ -8521,50 +8521,50 @@
       <c r="G6" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="118"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
-      <c r="K6" s="116"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H6" s="126"/>
+      <c r="I6" s="126"/>
+      <c r="J6" s="126"/>
+      <c r="K6" s="119"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C7" s="20"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E8" s="22"/>
       <c r="F8" s="16"/>
       <c r="G8" s="22"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E12" s="16"/>
       <c r="F12" s="16"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="H13" s="16"/>
       <c r="I13" s="20"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
     </row>
@@ -8593,30 +8593,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C1850E-A9C8-4F69-8E80-DEAF9721FFBF}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="21" customWidth="1"/>
     <col min="2" max="2" width="18" style="21" customWidth="1"/>
-    <col min="3" max="3" width="30.453125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="30.44140625" style="21" customWidth="1"/>
     <col min="4" max="4" width="34" style="21" customWidth="1"/>
-    <col min="5" max="5" width="56.7265625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="90.453125" style="21" customWidth="1"/>
-    <col min="7" max="7" width="32.453125" style="21" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="21"/>
+    <col min="5" max="5" width="56.77734375" style="21" customWidth="1"/>
+    <col min="6" max="6" width="90.44140625" style="21" customWidth="1"/>
+    <col min="7" max="7" width="32.44140625" style="21" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="119" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="135" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-    </row>
-    <row r="2" spans="1:7" s="30" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+    </row>
+    <row r="2" spans="1:7" s="30" customFormat="1" ht="60" x14ac:dyDescent="0.3">
       <c r="A2" s="97" t="s">
         <v>39</v>
       </c>
@@ -8639,7 +8639,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="33" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" s="33" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A3" s="100" t="s">
         <v>46</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="36" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>1</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="20" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" s="20" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2</v>
       </c>
@@ -8708,7 +8708,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="103">
         <v>3</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
         <v>4</v>
       </c>
@@ -8754,35 +8754,35 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="19"/>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="20"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="19"/>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
       <c r="E9" s="22"/>
       <c r="F9" s="20"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="20"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="19"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22"/>
       <c r="F11" s="20"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
@@ -8809,22 +8809,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AAF649-42F4-466A-BE11-44357078F961}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="88.453125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="23.1796875" style="19" customWidth="1"/>
+    <col min="1" max="1" width="88.44140625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" style="19" customWidth="1"/>
     <col min="3" max="3" width="23" style="21" customWidth="1"/>
-    <col min="4" max="4" width="44.81640625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="25.54296875" style="21" customWidth="1"/>
-    <col min="6" max="6" width="21.81640625" style="21" customWidth="1"/>
-    <col min="7" max="7" width="27.453125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="44.77734375" style="21" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" style="21" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" style="21" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" style="12" customWidth="1"/>
     <col min="8" max="8" width="20" style="12" customWidth="1"/>
     <col min="9" max="9" width="72" style="39" customWidth="1"/>
-    <col min="10" max="10" width="21.26953125" style="16" customWidth="1"/>
-    <col min="11" max="16384" width="11.453125" style="16"/>
+    <col min="10" max="10" width="21.21875" style="16" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="35" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="35" customFormat="1" ht="48" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>65</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="37" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>74</v>
       </c>
@@ -8882,7 +8882,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="54" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>54</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="49.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:11" ht="54" x14ac:dyDescent="0.5">
       <c r="A4" s="21" t="s">
         <v>54</v>
       </c>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="K4" s="65"/>
     </row>
-    <row r="5" spans="1:11" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="40" t="s">
         <v>54</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="22" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" s="22" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>57</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="22" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" s="22" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>57</v>
       </c>
@@ -9028,7 +9028,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="22" customFormat="1" ht="99.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" s="22" customFormat="1" ht="108.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="42" t="s">
         <v>57</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="25" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" s="25" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>59</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="25" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" s="25" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>59</v>
       </c>
@@ -9115,7 +9115,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="42" t="s">
         <v>59</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="54" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>63</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="20"/>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
@@ -9183,7 +9183,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="16"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -9193,7 +9193,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="16"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="20"/>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -9203,7 +9203,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="16"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -9213,7 +9213,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="20"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="20"/>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -9223,7 +9223,7 @@
       <c r="H17" s="2"/>
       <c r="I17" s="16"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="20"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -9233,7 +9233,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="20"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="20"/>
       <c r="C19" s="20"/>
       <c r="D19" s="20"/>
@@ -9280,18 +9280,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F726B80-E6B4-4ED4-A764-E59AF4E18393}">
   <dimension ref="A1:F40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="101.453125" style="12" customWidth="1"/>
-    <col min="2" max="2" width="42.7265625" style="50" customWidth="1"/>
-    <col min="3" max="3" width="44.81640625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="46.1796875" style="21" customWidth="1"/>
-    <col min="5" max="5" width="35.7265625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="38.7265625" style="12" customWidth="1"/>
-    <col min="7" max="16384" width="11.453125" style="12"/>
+    <col min="1" max="1" width="101.44140625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="42.77734375" style="50" customWidth="1"/>
+    <col min="3" max="3" width="44.77734375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="46.21875" style="21" customWidth="1"/>
+    <col min="5" max="5" width="35.77734375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="38.77734375" style="12" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>108</v>
       </c>
@@ -9311,7 +9311,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>114</v>
       </c>
@@ -9331,499 +9331,499 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="124" t="s">
+      <c r="B3" s="138" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="127" t="s">
+      <c r="C3" s="141" t="s">
         <v>121</v>
       </c>
       <c r="D3" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="121" t="s">
+      <c r="E3" s="137" t="s">
         <v>123</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="125"/>
-      <c r="C4" s="128"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="142"/>
       <c r="D4" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E4" s="118"/>
+      <c r="E4" s="126"/>
       <c r="F4" s="21" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="125"/>
-      <c r="C5" s="128"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="142"/>
       <c r="D5" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="118"/>
+      <c r="E5" s="126"/>
       <c r="F5" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="126"/>
-      <c r="C6" s="129"/>
+      <c r="B6" s="140"/>
+      <c r="C6" s="143"/>
       <c r="D6" s="46"/>
-      <c r="E6" s="122"/>
+      <c r="E6" s="127"/>
       <c r="F6" s="40"/>
     </row>
-    <row r="7" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="130" t="s">
+      <c r="B7" s="144" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="131" t="s">
+      <c r="C7" s="145" t="s">
         <v>130</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="123" t="s">
+      <c r="E7" s="125" t="s">
         <v>123</v>
       </c>
       <c r="F7" s="48" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="125"/>
-      <c r="C8" s="128"/>
+      <c r="B8" s="139"/>
+      <c r="C8" s="142"/>
       <c r="D8" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="118"/>
+      <c r="E8" s="126"/>
       <c r="F8" s="21" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="125"/>
-      <c r="C9" s="128"/>
+      <c r="B9" s="139"/>
+      <c r="C9" s="142"/>
       <c r="D9" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="118"/>
+      <c r="E9" s="126"/>
       <c r="F9" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="125"/>
-      <c r="C10" s="128"/>
-      <c r="E10" s="118"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="142"/>
+      <c r="E10" s="126"/>
       <c r="F10" s="21"/>
     </row>
-    <row r="11" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A11" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="144" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="132" t="s">
+      <c r="C11" s="146" t="s">
         <v>132</v>
       </c>
       <c r="D11" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="123" t="s">
+      <c r="E11" s="125" t="s">
         <v>133</v>
       </c>
       <c r="F11" s="48" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="125"/>
-      <c r="C12" s="133"/>
+      <c r="B12" s="139"/>
+      <c r="C12" s="147"/>
       <c r="D12" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E12" s="118"/>
+      <c r="E12" s="126"/>
       <c r="F12" s="21" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="125"/>
-      <c r="C13" s="133"/>
+      <c r="B13" s="139"/>
+      <c r="C13" s="147"/>
       <c r="D13" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="118"/>
+      <c r="E13" s="126"/>
       <c r="F13" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="125"/>
-      <c r="C14" s="133"/>
+      <c r="B14" s="139"/>
+      <c r="C14" s="147"/>
       <c r="D14" s="44"/>
-      <c r="E14" s="118"/>
+      <c r="E14" s="126"/>
       <c r="F14" s="21"/>
     </row>
-    <row r="15" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="133"/>
+      <c r="B15" s="139"/>
+      <c r="C15" s="147"/>
       <c r="D15" s="44"/>
-      <c r="E15" s="118"/>
+      <c r="E15" s="126"/>
       <c r="F15" s="21"/>
     </row>
-    <row r="16" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="126"/>
-      <c r="C16" s="134"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="148"/>
       <c r="D16" s="46"/>
-      <c r="E16" s="122"/>
+      <c r="E16" s="127"/>
       <c r="F16" s="40"/>
     </row>
-    <row r="17" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A17" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="138" t="s">
+      <c r="B17" s="124" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="123" t="s">
+      <c r="C17" s="125" t="s">
         <v>135</v>
       </c>
       <c r="D17" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="123" t="s">
+      <c r="E17" s="125" t="s">
         <v>136</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="116"/>
-      <c r="C18" s="118"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="126"/>
       <c r="D18" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="118"/>
+      <c r="E18" s="126"/>
       <c r="F18" s="21" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="116"/>
-      <c r="C19" s="118"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="126"/>
       <c r="D19" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E19" s="118"/>
+      <c r="E19" s="126"/>
       <c r="F19" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="116"/>
-      <c r="C20" s="118"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="126"/>
       <c r="D20" s="44"/>
-      <c r="E20" s="118"/>
+      <c r="E20" s="126"/>
       <c r="F20" s="21"/>
     </row>
-    <row r="21" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="116"/>
-      <c r="C21" s="118"/>
-      <c r="E21" s="118"/>
-    </row>
-    <row r="22" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="119"/>
+      <c r="C21" s="126"/>
+      <c r="E21" s="126"/>
+    </row>
+    <row r="22" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="136"/>
-      <c r="C22" s="122"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="127"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="122"/>
+      <c r="E22" s="127"/>
       <c r="F22" s="41"/>
     </row>
-    <row r="23" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A23" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="138" t="s">
+      <c r="B23" s="124" t="s">
         <v>137</v>
       </c>
-      <c r="C23" s="123" t="s">
+      <c r="C23" s="125" t="s">
         <v>138</v>
       </c>
       <c r="D23" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="E23" s="123" t="s">
+      <c r="E23" s="125" t="s">
         <v>139</v>
       </c>
       <c r="F23" s="48" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="116"/>
-      <c r="C24" s="118"/>
+      <c r="B24" s="119"/>
+      <c r="C24" s="126"/>
       <c r="D24" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="118"/>
+      <c r="E24" s="126"/>
       <c r="F24" s="21" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="116"/>
-      <c r="C25" s="118"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="126"/>
       <c r="D25" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E25" s="118"/>
+      <c r="E25" s="126"/>
       <c r="F25" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="116"/>
-      <c r="C26" s="118"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="126"/>
       <c r="D26" s="44"/>
-      <c r="E26" s="118"/>
+      <c r="E26" s="126"/>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B27" s="116"/>
-      <c r="C27" s="118"/>
-      <c r="E27" s="118"/>
-    </row>
-    <row r="28" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="119"/>
+      <c r="C27" s="126"/>
+      <c r="E27" s="126"/>
+    </row>
+    <row r="28" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="136"/>
-      <c r="C28" s="122"/>
+      <c r="B28" s="120"/>
+      <c r="C28" s="127"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="122"/>
+      <c r="E28" s="127"/>
       <c r="F28" s="41"/>
     </row>
-    <row r="29" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A29" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="139" t="s">
+      <c r="B29" s="151" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="142" t="s">
+      <c r="C29" s="154" t="s">
         <v>141</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="123" t="s">
+      <c r="E29" s="125" t="s">
         <v>142</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A30" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="140"/>
-      <c r="C30" s="143"/>
+      <c r="B30" s="152"/>
+      <c r="C30" s="155"/>
       <c r="D30" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="E30" s="118"/>
+      <c r="E30" s="126"/>
       <c r="F30" s="12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="140"/>
-      <c r="C31" s="143"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="155"/>
       <c r="D31" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="E31" s="118"/>
+      <c r="E31" s="126"/>
       <c r="F31" s="12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A32" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="140"/>
-      <c r="C32" s="143"/>
-      <c r="E32" s="118"/>
-    </row>
-    <row r="33" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="B32" s="152"/>
+      <c r="C32" s="155"/>
+      <c r="E32" s="126"/>
+    </row>
+    <row r="33" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="140"/>
-      <c r="C33" s="143"/>
+      <c r="B33" s="152"/>
+      <c r="C33" s="155"/>
       <c r="D33" s="44"/>
-      <c r="E33" s="118"/>
-    </row>
-    <row r="34" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E33" s="126"/>
+    </row>
+    <row r="34" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="141"/>
-      <c r="C34" s="144"/>
+      <c r="B34" s="153"/>
+      <c r="C34" s="156"/>
       <c r="D34" s="46"/>
-      <c r="E34" s="145"/>
+      <c r="E34" s="157"/>
       <c r="F34" s="92"/>
     </row>
-    <row r="35" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="135" t="s">
+      <c r="B35" s="149" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="137" t="s">
+      <c r="C35" s="150" t="s">
         <v>145</v>
       </c>
       <c r="D35" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="137" t="s">
+      <c r="E35" s="150" t="s">
         <v>136</v>
       </c>
       <c r="F35" s="12" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="116"/>
-      <c r="C36" s="118"/>
+      <c r="B36" s="119"/>
+      <c r="C36" s="126"/>
       <c r="D36" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E36" s="118"/>
+      <c r="E36" s="126"/>
       <c r="F36" s="12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="116"/>
-      <c r="C37" s="118"/>
+      <c r="B37" s="119"/>
+      <c r="C37" s="126"/>
       <c r="D37" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="E37" s="118"/>
+      <c r="E37" s="126"/>
       <c r="F37" s="12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="116"/>
-      <c r="C38" s="118"/>
+      <c r="B38" s="119"/>
+      <c r="C38" s="126"/>
       <c r="D38" s="44"/>
-      <c r="E38" s="118"/>
-    </row>
-    <row r="39" spans="1:6" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="E38" s="126"/>
+    </row>
+    <row r="39" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A39" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="116"/>
-      <c r="C39" s="118"/>
-      <c r="E39" s="118"/>
-    </row>
-    <row r="40" spans="1:6" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="119"/>
+      <c r="C39" s="126"/>
+      <c r="E39" s="126"/>
+    </row>
+    <row r="40" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="136"/>
-      <c r="C40" s="122"/>
+      <c r="B40" s="120"/>
+      <c r="C40" s="127"/>
       <c r="D40" s="40"/>
-      <c r="E40" s="122"/>
+      <c r="E40" s="127"/>
       <c r="F40" s="41"/>
     </row>
   </sheetData>
@@ -9864,30 +9864,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CB1331-AF3E-489A-B433-09E21B4DF482}">
   <dimension ref="A1:S182"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="58.7265625" defaultRowHeight="16" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="58.77734375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.453125" style="62" customWidth="1"/>
-    <col min="2" max="2" width="73.453125" style="57" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" style="51" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="62" customWidth="1"/>
+    <col min="2" max="2" width="73.44140625" style="57" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="51" customWidth="1"/>
     <col min="4" max="4" width="27" style="52" customWidth="1"/>
-    <col min="5" max="5" width="58.7265625" style="62"/>
-    <col min="6" max="6" width="18.81640625" style="51" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" style="51" customWidth="1"/>
-    <col min="8" max="8" width="17.26953125" style="51" customWidth="1"/>
-    <col min="9" max="9" width="21.1796875" style="51" customWidth="1"/>
-    <col min="10" max="10" width="14.26953125" style="51" customWidth="1"/>
-    <col min="11" max="11" width="23.7265625" style="51" customWidth="1"/>
-    <col min="12" max="12" width="20.81640625" style="51" customWidth="1"/>
-    <col min="13" max="13" width="16.7265625" style="51" customWidth="1"/>
+    <col min="5" max="5" width="58.77734375" style="62"/>
+    <col min="6" max="6" width="18.77734375" style="51" customWidth="1"/>
+    <col min="7" max="7" width="21.77734375" style="51" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" style="51" customWidth="1"/>
+    <col min="9" max="9" width="21.21875" style="51" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" style="51" customWidth="1"/>
+    <col min="11" max="11" width="23.77734375" style="51" customWidth="1"/>
+    <col min="12" max="12" width="20.77734375" style="51" customWidth="1"/>
+    <col min="13" max="13" width="16.77734375" style="51" customWidth="1"/>
     <col min="14" max="14" width="36" style="62" customWidth="1"/>
-    <col min="15" max="15" width="49.453125" style="62" customWidth="1"/>
-    <col min="16" max="16" width="87.81640625" style="62" customWidth="1"/>
-    <col min="17" max="17" width="76.54296875" style="62" customWidth="1"/>
-    <col min="18" max="19" width="3.453125" style="51" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="58.7265625" style="51"/>
+    <col min="15" max="15" width="49.44140625" style="62" customWidth="1"/>
+    <col min="16" max="16" width="87.77734375" style="62" customWidth="1"/>
+    <col min="17" max="17" width="76.5546875" style="62" customWidth="1"/>
+    <col min="18" max="19" width="3.44140625" style="51" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="58.77734375" style="51"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="12" customFormat="1" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" s="12" customFormat="1" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>147</v>
       </c>
@@ -9906,11 +9906,11 @@
       <c r="F1" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="G1" s="146" t="s">
+      <c r="G1" s="116" t="s">
         <v>153</v>
       </c>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
       <c r="J1" s="18" t="s">
         <v>154</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="12" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" s="12" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A2" s="113" t="s">
         <v>162</v>
       </c>
@@ -9989,7 +9989,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="50" customFormat="1" ht="264" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" s="50" customFormat="1" ht="324" x14ac:dyDescent="0.3">
       <c r="A3" s="88" t="str">
         <f>_xlfn.XLOOKUP(B3,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10042,7 +10042,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="50" customFormat="1" ht="297.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" s="50" customFormat="1" ht="342.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="88" t="str">
         <f>_xlfn.XLOOKUP(B4,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10095,7 +10095,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="str">
         <f>_xlfn.XLOOKUP(B5,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10103,52 +10103,52 @@
       <c r="B5" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="147">
+      <c r="C5" s="117">
         <v>1</v>
       </c>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="119" t="s">
         <v>190</v>
       </c>
-      <c r="E5" s="149" t="s">
+      <c r="E5" s="121" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="147" t="s">
+      <c r="F5" s="117" t="s">
         <v>180</v>
       </c>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147" t="s">
+      <c r="G5" s="117"/>
+      <c r="H5" s="117" t="s">
         <v>181</v>
       </c>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147">
+      <c r="I5" s="117"/>
+      <c r="J5" s="117">
         <v>3</v>
       </c>
-      <c r="K5" s="147">
+      <c r="K5" s="117">
         <f>J5*12</f>
         <v>36</v>
       </c>
-      <c r="L5" s="147">
+      <c r="L5" s="117">
         <f>36*J5</f>
         <v>108</v>
       </c>
-      <c r="M5" s="147">
+      <c r="M5" s="117">
         <f>SUM(K5:L5)</f>
         <v>144</v>
       </c>
-      <c r="N5" s="149" t="s">
+      <c r="N5" s="121" t="s">
         <v>192</v>
       </c>
-      <c r="O5" s="149" t="s">
+      <c r="O5" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="P5" s="149" t="s">
+      <c r="P5" s="121" t="s">
         <v>193</v>
       </c>
-      <c r="Q5" s="149" t="s">
+      <c r="Q5" s="121" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="50" customFormat="1" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" s="50" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="24" t="str">
         <f>_xlfn.XLOOKUP(B6,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10156,23 +10156,23 @@
       <c r="B6" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="147"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="147"/>
-      <c r="G6" s="147"/>
-      <c r="H6" s="147"/>
-      <c r="I6" s="147"/>
-      <c r="J6" s="147"/>
-      <c r="K6" s="147"/>
-      <c r="L6" s="147"/>
-      <c r="M6" s="147"/>
-      <c r="N6" s="149"/>
-      <c r="O6" s="149"/>
-      <c r="P6" s="149"/>
-      <c r="Q6" s="149"/>
-    </row>
-    <row r="7" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C6" s="117"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="117"/>
+      <c r="N6" s="121"/>
+      <c r="O6" s="121"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="121"/>
+    </row>
+    <row r="7" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="80" t="str">
         <f>_xlfn.XLOOKUP(B7,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -10180,23 +10180,23 @@
       <c r="B7" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="148"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="148"/>
-      <c r="G7" s="148"/>
-      <c r="H7" s="148"/>
-      <c r="I7" s="148"/>
-      <c r="J7" s="148"/>
-      <c r="K7" s="148"/>
-      <c r="L7" s="148"/>
-      <c r="M7" s="148"/>
-      <c r="N7" s="150"/>
-      <c r="O7" s="150"/>
-      <c r="P7" s="150"/>
-      <c r="Q7" s="150"/>
-    </row>
-    <row r="8" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C7" s="118"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="122"/>
+      <c r="O7" s="122"/>
+      <c r="P7" s="122"/>
+      <c r="Q7" s="122"/>
+    </row>
+    <row r="8" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="str">
         <f>_xlfn.XLOOKUP(B8,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10204,52 +10204,52 @@
       <c r="B8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="151">
+      <c r="C8" s="123">
         <v>1</v>
       </c>
-      <c r="D8" s="138" t="s">
+      <c r="D8" s="124" t="s">
         <v>194</v>
       </c>
-      <c r="E8" s="123" t="s">
+      <c r="E8" s="125" t="s">
         <v>195</v>
       </c>
-      <c r="F8" s="138" t="s">
+      <c r="F8" s="124" t="s">
         <v>196</v>
       </c>
-      <c r="G8" s="138"/>
-      <c r="H8" s="138" t="s">
+      <c r="G8" s="124"/>
+      <c r="H8" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I8" s="138"/>
-      <c r="J8" s="138">
+      <c r="I8" s="124"/>
+      <c r="J8" s="124">
         <v>2</v>
       </c>
-      <c r="K8" s="147">
+      <c r="K8" s="117">
         <f>J8*12</f>
         <v>24</v>
       </c>
-      <c r="L8" s="147">
+      <c r="L8" s="117">
         <f>36*J8</f>
         <v>72</v>
       </c>
-      <c r="M8" s="138">
+      <c r="M8" s="124">
         <f>SUM(K8:L8)</f>
         <v>96</v>
       </c>
-      <c r="N8" s="123" t="s">
+      <c r="N8" s="125" t="s">
         <v>197</v>
       </c>
-      <c r="O8" s="123" t="s">
+      <c r="O8" s="125" t="s">
         <v>198</v>
       </c>
-      <c r="P8" s="123" t="s">
+      <c r="P8" s="125" t="s">
         <v>199</v>
       </c>
-      <c r="Q8" s="123" t="s">
+      <c r="Q8" s="125" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="str">
         <f>_xlfn.XLOOKUP(B9,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10257,23 +10257,23 @@
       <c r="B9" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="147"/>
-      <c r="D9" s="116"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="116"/>
-      <c r="G9" s="116"/>
-      <c r="H9" s="116"/>
-      <c r="I9" s="116"/>
-      <c r="J9" s="116"/>
-      <c r="K9" s="147"/>
-      <c r="L9" s="147"/>
-      <c r="M9" s="116"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="118"/>
-      <c r="P9" s="118"/>
-      <c r="Q9" s="118"/>
-    </row>
-    <row r="10" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C9" s="117"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="126"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="119"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="126"/>
+      <c r="O9" s="126"/>
+      <c r="P9" s="126"/>
+      <c r="Q9" s="126"/>
+    </row>
+    <row r="10" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A10" s="80" t="str">
         <f>_xlfn.XLOOKUP(B10,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10281,23 +10281,23 @@
       <c r="B10" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="148"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="122"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="136"/>
-      <c r="H10" s="136"/>
-      <c r="I10" s="136"/>
-      <c r="J10" s="136"/>
-      <c r="K10" s="148"/>
-      <c r="L10" s="148"/>
-      <c r="M10" s="136"/>
-      <c r="N10" s="122"/>
-      <c r="O10" s="122"/>
-      <c r="P10" s="122"/>
-      <c r="Q10" s="122"/>
-    </row>
-    <row r="11" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C10" s="118"/>
+      <c r="D10" s="120"/>
+      <c r="E10" s="127"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="120"/>
+      <c r="K10" s="118"/>
+      <c r="L10" s="118"/>
+      <c r="M10" s="120"/>
+      <c r="N10" s="127"/>
+      <c r="O10" s="127"/>
+      <c r="P10" s="127"/>
+      <c r="Q10" s="127"/>
+    </row>
+    <row r="11" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="24" t="str">
         <f>_xlfn.XLOOKUP(B11,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10305,52 +10305,52 @@
       <c r="B11" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="151">
+      <c r="C11" s="123">
         <v>1</v>
       </c>
-      <c r="D11" s="138" t="s">
+      <c r="D11" s="124" t="s">
         <v>200</v>
       </c>
-      <c r="E11" s="152" t="s">
+      <c r="E11" s="128" t="s">
         <v>201</v>
       </c>
-      <c r="F11" s="151" t="s">
+      <c r="F11" s="123" t="s">
         <v>180</v>
       </c>
-      <c r="G11" s="151"/>
-      <c r="H11" s="151" t="s">
+      <c r="G11" s="123"/>
+      <c r="H11" s="123" t="s">
         <v>181</v>
       </c>
-      <c r="I11" s="151"/>
-      <c r="J11" s="151">
+      <c r="I11" s="123"/>
+      <c r="J11" s="123">
         <v>3</v>
       </c>
-      <c r="K11" s="147">
+      <c r="K11" s="117">
         <f>J11*12</f>
         <v>36</v>
       </c>
-      <c r="L11" s="147">
+      <c r="L11" s="117">
         <f>36*J11</f>
         <v>108</v>
       </c>
-      <c r="M11" s="151">
+      <c r="M11" s="123">
         <f>SUM(K11:L11)</f>
         <v>144</v>
       </c>
-      <c r="N11" s="152" t="s">
+      <c r="N11" s="128" t="s">
         <v>202</v>
       </c>
-      <c r="O11" s="152" t="s">
+      <c r="O11" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="P11" s="152" t="s">
+      <c r="P11" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q11" s="152" t="s">
+      <c r="Q11" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="24" t="str">
         <f>_xlfn.XLOOKUP(B12,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -10358,23 +10358,23 @@
       <c r="B12" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="147"/>
-      <c r="D12" s="116"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="147"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="147"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="147"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="153"/>
-      <c r="O12" s="153"/>
-      <c r="P12" s="153"/>
-      <c r="Q12" s="153"/>
-    </row>
-    <row r="13" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C12" s="117"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="129"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="117"/>
+      <c r="L12" s="117"/>
+      <c r="M12" s="117"/>
+      <c r="N12" s="129"/>
+      <c r="O12" s="129"/>
+      <c r="P12" s="129"/>
+      <c r="Q12" s="129"/>
+    </row>
+    <row r="13" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="80" t="str">
         <f>_xlfn.XLOOKUP(B13,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10382,21 +10382,21 @@
       <c r="B13" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="148"/>
-      <c r="D13" s="136"/>
-      <c r="E13" s="154"/>
-      <c r="F13" s="148"/>
-      <c r="G13" s="148"/>
-      <c r="H13" s="148"/>
-      <c r="I13" s="148"/>
-      <c r="J13" s="148"/>
-      <c r="K13" s="148"/>
-      <c r="L13" s="148"/>
-      <c r="M13" s="148"/>
-      <c r="N13" s="154"/>
-      <c r="O13" s="154"/>
-      <c r="P13" s="154"/>
-      <c r="Q13" s="154"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
+      <c r="K13" s="118"/>
+      <c r="L13" s="118"/>
+      <c r="M13" s="118"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="130"/>
       <c r="R13" s="50">
         <f>SUM(J3:J13)</f>
         <v>14</v>
@@ -10406,7 +10406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="50" customFormat="1" ht="264.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" s="50" customFormat="1" ht="324.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="88" t="str">
         <f>_xlfn.XLOOKUP(B14,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10459,7 +10459,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="str">
         <f>_xlfn.XLOOKUP(B15,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10467,52 +10467,52 @@
       <c r="B15" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="138">
+      <c r="C15" s="124">
         <v>2</v>
       </c>
-      <c r="D15" s="138" t="s">
+      <c r="D15" s="124" t="s">
         <v>206</v>
       </c>
-      <c r="E15" s="152" t="s">
+      <c r="E15" s="128" t="s">
         <v>207</v>
       </c>
-      <c r="F15" s="138" t="s">
+      <c r="F15" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G15" s="138"/>
-      <c r="H15" s="138" t="s">
+      <c r="G15" s="124"/>
+      <c r="H15" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I15" s="138"/>
-      <c r="J15" s="138">
+      <c r="I15" s="124"/>
+      <c r="J15" s="124">
         <v>3</v>
       </c>
-      <c r="K15" s="147">
+      <c r="K15" s="117">
         <f>J15*12</f>
         <v>36</v>
       </c>
-      <c r="L15" s="147">
+      <c r="L15" s="117">
         <f>36*J15</f>
         <v>108</v>
       </c>
-      <c r="M15" s="138">
+      <c r="M15" s="124">
         <f>SUM(K15:L15)</f>
         <v>144</v>
       </c>
-      <c r="N15" s="152" t="s">
+      <c r="N15" s="128" t="s">
         <v>208</v>
       </c>
-      <c r="O15" s="152" t="s">
+      <c r="O15" s="128" t="s">
         <v>209</v>
       </c>
-      <c r="P15" s="152" t="s">
+      <c r="P15" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q15" s="152" t="s">
+      <c r="Q15" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A16" s="24" t="str">
         <f>_xlfn.XLOOKUP(B16,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10520,23 +10520,23 @@
       <c r="B16" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="116"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="153"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="116"/>
-      <c r="H16" s="116"/>
-      <c r="I16" s="116"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="147"/>
-      <c r="L16" s="147"/>
-      <c r="M16" s="116"/>
-      <c r="N16" s="153"/>
-      <c r="O16" s="153"/>
-      <c r="P16" s="153"/>
-      <c r="Q16" s="153"/>
-    </row>
-    <row r="17" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C16" s="119"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="119"/>
+      <c r="N16" s="129"/>
+      <c r="O16" s="129"/>
+      <c r="P16" s="129"/>
+      <c r="Q16" s="129"/>
+    </row>
+    <row r="17" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="80" t="str">
         <f>_xlfn.XLOOKUP(B17,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10544,23 +10544,23 @@
       <c r="B17" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="154"/>
-      <c r="F17" s="136"/>
-      <c r="G17" s="136"/>
-      <c r="H17" s="136"/>
-      <c r="I17" s="136"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="148"/>
-      <c r="L17" s="148"/>
-      <c r="M17" s="136"/>
-      <c r="N17" s="154"/>
-      <c r="O17" s="154"/>
-      <c r="P17" s="154"/>
-      <c r="Q17" s="154"/>
-    </row>
-    <row r="18" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C17" s="120"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="120"/>
+      <c r="H17" s="120"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="118"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="130"/>
+      <c r="O17" s="130"/>
+      <c r="P17" s="130"/>
+      <c r="Q17" s="130"/>
+    </row>
+    <row r="18" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="str">
         <f>_xlfn.XLOOKUP(B18,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10568,52 +10568,52 @@
       <c r="B18" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="138">
+      <c r="C18" s="124">
         <v>2</v>
       </c>
-      <c r="D18" s="138" t="s">
+      <c r="D18" s="124" t="s">
         <v>210</v>
       </c>
-      <c r="E18" s="152" t="s">
+      <c r="E18" s="128" t="s">
         <v>211</v>
       </c>
-      <c r="F18" s="138" t="s">
+      <c r="F18" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G18" s="138"/>
-      <c r="H18" s="138" t="s">
+      <c r="G18" s="124"/>
+      <c r="H18" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I18" s="138"/>
-      <c r="J18" s="138">
+      <c r="I18" s="124"/>
+      <c r="J18" s="124">
         <v>4</v>
       </c>
-      <c r="K18" s="147">
+      <c r="K18" s="117">
         <f>J18*12</f>
         <v>48</v>
       </c>
-      <c r="L18" s="147">
+      <c r="L18" s="117">
         <f>36*J18</f>
         <v>144</v>
       </c>
-      <c r="M18" s="138">
+      <c r="M18" s="124">
         <f>SUM(K18:L18)</f>
         <v>192</v>
       </c>
-      <c r="N18" s="152" t="s">
+      <c r="N18" s="128" t="s">
         <v>212</v>
       </c>
-      <c r="O18" s="152" t="s">
+      <c r="O18" s="128" t="s">
         <v>209</v>
       </c>
-      <c r="P18" s="152" t="s">
+      <c r="P18" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q18" s="152" t="s">
+      <c r="Q18" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="str">
         <f>_xlfn.XLOOKUP(B19,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10621,23 +10621,23 @@
       <c r="B19" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="153"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="116"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="116"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="147"/>
-      <c r="L19" s="147"/>
-      <c r="M19" s="116"/>
-      <c r="N19" s="153"/>
-      <c r="O19" s="153"/>
-      <c r="P19" s="153"/>
-      <c r="Q19" s="153"/>
-    </row>
-    <row r="20" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="129"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="129"/>
+      <c r="O19" s="129"/>
+      <c r="P19" s="129"/>
+      <c r="Q19" s="129"/>
+    </row>
+    <row r="20" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="80" t="str">
         <f>_xlfn.XLOOKUP(B20,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10645,23 +10645,23 @@
       <c r="B20" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="136"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="154"/>
-      <c r="F20" s="136"/>
-      <c r="G20" s="136"/>
-      <c r="H20" s="136"/>
-      <c r="I20" s="136"/>
-      <c r="J20" s="136"/>
-      <c r="K20" s="148"/>
-      <c r="L20" s="148"/>
-      <c r="M20" s="136"/>
-      <c r="N20" s="154"/>
-      <c r="O20" s="154"/>
-      <c r="P20" s="154"/>
-      <c r="Q20" s="154"/>
-    </row>
-    <row r="21" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="118"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="120"/>
+      <c r="N20" s="130"/>
+      <c r="O20" s="130"/>
+      <c r="P20" s="130"/>
+      <c r="Q20" s="130"/>
+    </row>
+    <row r="21" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="str">
         <f>_xlfn.XLOOKUP(B21,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10669,52 +10669,52 @@
       <c r="B21" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="138">
+      <c r="C21" s="124">
         <v>2</v>
       </c>
-      <c r="D21" s="138" t="s">
+      <c r="D21" s="124" t="s">
         <v>213</v>
       </c>
-      <c r="E21" s="152" t="s">
+      <c r="E21" s="128" t="s">
         <v>214</v>
       </c>
-      <c r="F21" s="138" t="s">
+      <c r="F21" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G21" s="138"/>
-      <c r="H21" s="138" t="s">
+      <c r="G21" s="124"/>
+      <c r="H21" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I21" s="138"/>
-      <c r="J21" s="138">
+      <c r="I21" s="124"/>
+      <c r="J21" s="124">
         <v>3</v>
       </c>
-      <c r="K21" s="147">
+      <c r="K21" s="117">
         <f>J21*12</f>
         <v>36</v>
       </c>
-      <c r="L21" s="147">
+      <c r="L21" s="117">
         <f>36*J21</f>
         <v>108</v>
       </c>
-      <c r="M21" s="138">
+      <c r="M21" s="124">
         <f>SUM(K21:L21)</f>
         <v>144</v>
       </c>
-      <c r="N21" s="152" t="s">
+      <c r="N21" s="128" t="s">
         <v>215</v>
       </c>
-      <c r="O21" s="152" t="s">
+      <c r="O21" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="P21" s="152" t="s">
+      <c r="P21" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q21" s="152" t="s">
+      <c r="Q21" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="str">
         <f>_xlfn.XLOOKUP(B22,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10722,23 +10722,23 @@
       <c r="B22" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="116"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="147"/>
-      <c r="L22" s="147"/>
-      <c r="M22" s="116"/>
-      <c r="N22" s="153"/>
-      <c r="O22" s="153"/>
-      <c r="P22" s="153"/>
-      <c r="Q22" s="153"/>
-    </row>
-    <row r="23" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="117"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="119"/>
+      <c r="N22" s="129"/>
+      <c r="O22" s="129"/>
+      <c r="P22" s="129"/>
+      <c r="Q22" s="129"/>
+    </row>
+    <row r="23" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="80" t="str">
         <f>_xlfn.XLOOKUP(B23,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10746,23 +10746,23 @@
       <c r="B23" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="136"/>
-      <c r="D23" s="136"/>
-      <c r="E23" s="154"/>
-      <c r="F23" s="136"/>
-      <c r="G23" s="136"/>
-      <c r="H23" s="136"/>
-      <c r="I23" s="136"/>
-      <c r="J23" s="136"/>
-      <c r="K23" s="148"/>
-      <c r="L23" s="148"/>
-      <c r="M23" s="136"/>
-      <c r="N23" s="154"/>
-      <c r="O23" s="154"/>
-      <c r="P23" s="154"/>
-      <c r="Q23" s="154"/>
-    </row>
-    <row r="24" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C23" s="120"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="120"/>
+      <c r="H23" s="120"/>
+      <c r="I23" s="120"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="120"/>
+      <c r="N23" s="130"/>
+      <c r="O23" s="130"/>
+      <c r="P23" s="130"/>
+      <c r="Q23" s="130"/>
+    </row>
+    <row r="24" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="str">
         <f>_xlfn.XLOOKUP(B24,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10770,52 +10770,52 @@
       <c r="B24" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="138">
+      <c r="C24" s="124">
         <v>2</v>
       </c>
-      <c r="D24" s="138" t="s">
+      <c r="D24" s="124" t="s">
         <v>216</v>
       </c>
-      <c r="E24" s="152" t="s">
+      <c r="E24" s="128" t="s">
         <v>217</v>
       </c>
-      <c r="F24" s="138" t="s">
+      <c r="F24" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G24" s="138"/>
-      <c r="H24" s="138" t="s">
+      <c r="G24" s="124"/>
+      <c r="H24" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I24" s="138"/>
-      <c r="J24" s="138">
+      <c r="I24" s="124"/>
+      <c r="J24" s="124">
         <v>3</v>
       </c>
-      <c r="K24" s="147">
+      <c r="K24" s="117">
         <f>J24*12</f>
         <v>36</v>
       </c>
-      <c r="L24" s="147">
+      <c r="L24" s="117">
         <f>36*J24</f>
         <v>108</v>
       </c>
-      <c r="M24" s="138">
+      <c r="M24" s="124">
         <f>SUM(K24:L24)</f>
         <v>144</v>
       </c>
-      <c r="N24" s="152" t="s">
+      <c r="N24" s="128" t="s">
         <v>218</v>
       </c>
-      <c r="O24" s="152" t="s">
+      <c r="O24" s="128" t="s">
         <v>209</v>
       </c>
-      <c r="P24" s="152" t="s">
+      <c r="P24" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q24" s="152" t="s">
+      <c r="Q24" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="str">
         <f>_xlfn.XLOOKUP(B25,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10823,23 +10823,23 @@
       <c r="B25" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="116"/>
-      <c r="D25" s="116"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="116"/>
-      <c r="G25" s="116"/>
-      <c r="H25" s="116"/>
-      <c r="I25" s="116"/>
-      <c r="J25" s="116"/>
-      <c r="K25" s="147"/>
-      <c r="L25" s="147"/>
-      <c r="M25" s="116"/>
-      <c r="N25" s="153"/>
-      <c r="O25" s="153"/>
-      <c r="P25" s="153"/>
-      <c r="Q25" s="153"/>
-    </row>
-    <row r="26" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="129"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="117"/>
+      <c r="L25" s="117"/>
+      <c r="M25" s="119"/>
+      <c r="N25" s="129"/>
+      <c r="O25" s="129"/>
+      <c r="P25" s="129"/>
+      <c r="Q25" s="129"/>
+    </row>
+    <row r="26" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="80" t="str">
         <f>_xlfn.XLOOKUP(B26,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10847,21 +10847,21 @@
       <c r="B26" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="136"/>
-      <c r="D26" s="136"/>
-      <c r="E26" s="154"/>
-      <c r="F26" s="136"/>
-      <c r="G26" s="136"/>
-      <c r="H26" s="136"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="136"/>
-      <c r="K26" s="148"/>
-      <c r="L26" s="148"/>
-      <c r="M26" s="136"/>
-      <c r="N26" s="154"/>
-      <c r="O26" s="154"/>
-      <c r="P26" s="154"/>
-      <c r="Q26" s="154"/>
+      <c r="C26" s="120"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="130"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="120"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="118"/>
+      <c r="L26" s="118"/>
+      <c r="M26" s="120"/>
+      <c r="N26" s="130"/>
+      <c r="O26" s="130"/>
+      <c r="P26" s="130"/>
+      <c r="Q26" s="130"/>
       <c r="R26" s="50">
         <f>SUM(J14:J26)</f>
         <v>16</v>
@@ -10871,7 +10871,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="12" customFormat="1" ht="264" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19" s="12" customFormat="1" ht="324" x14ac:dyDescent="0.3">
       <c r="A27" s="88" t="str">
         <f>_xlfn.XLOOKUP(B27,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10924,7 +10924,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:19" s="50" customFormat="1" ht="264.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:19" s="50" customFormat="1" ht="324.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="88" t="str">
         <f>_xlfn.XLOOKUP(B28,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10977,7 +10977,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="str">
         <f>_xlfn.XLOOKUP(B29,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -10985,52 +10985,52 @@
       <c r="B29" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="138">
+      <c r="C29" s="124">
         <v>3</v>
       </c>
-      <c r="D29" s="138" t="s">
+      <c r="D29" s="124" t="s">
         <v>225</v>
       </c>
-      <c r="E29" s="152" t="s">
+      <c r="E29" s="128" t="s">
         <v>226</v>
       </c>
-      <c r="F29" s="138" t="s">
+      <c r="F29" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G29" s="138"/>
-      <c r="H29" s="138" t="s">
+      <c r="G29" s="124"/>
+      <c r="H29" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I29" s="138"/>
-      <c r="J29" s="138">
+      <c r="I29" s="124"/>
+      <c r="J29" s="124">
         <v>3</v>
       </c>
-      <c r="K29" s="147">
+      <c r="K29" s="117">
         <f>J29*12</f>
         <v>36</v>
       </c>
-      <c r="L29" s="147">
+      <c r="L29" s="117">
         <f>36*J29</f>
         <v>108</v>
       </c>
-      <c r="M29" s="138">
+      <c r="M29" s="124">
         <f>SUM(K29:L29)</f>
         <v>144</v>
       </c>
-      <c r="N29" s="152" t="s">
+      <c r="N29" s="128" t="s">
         <v>227</v>
       </c>
-      <c r="O29" s="152" t="s">
+      <c r="O29" s="128" t="s">
         <v>209</v>
       </c>
-      <c r="P29" s="152" t="s">
+      <c r="P29" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q29" s="152" t="s">
+      <c r="Q29" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:19" s="50" customFormat="1" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" s="50" customFormat="1" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="str">
         <f>_xlfn.XLOOKUP(B30,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11038,23 +11038,23 @@
       <c r="B30" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="116"/>
-      <c r="D30" s="116"/>
-      <c r="E30" s="153"/>
-      <c r="F30" s="116"/>
-      <c r="G30" s="116"/>
-      <c r="H30" s="116"/>
-      <c r="I30" s="116"/>
-      <c r="J30" s="116"/>
-      <c r="K30" s="147"/>
-      <c r="L30" s="147"/>
-      <c r="M30" s="116"/>
-      <c r="N30" s="153"/>
-      <c r="O30" s="153"/>
-      <c r="P30" s="153"/>
-      <c r="Q30" s="153"/>
-    </row>
-    <row r="31" spans="1:19" s="50" customFormat="1" ht="53.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C30" s="119"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="129"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="119"/>
+      <c r="H30" s="119"/>
+      <c r="I30" s="119"/>
+      <c r="J30" s="119"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="119"/>
+      <c r="N30" s="129"/>
+      <c r="O30" s="129"/>
+      <c r="P30" s="129"/>
+      <c r="Q30" s="129"/>
+    </row>
+    <row r="31" spans="1:19" s="50" customFormat="1" ht="53.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="80" t="str">
         <f>_xlfn.XLOOKUP(B31,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11062,23 +11062,23 @@
       <c r="B31" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="136"/>
-      <c r="D31" s="136"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="136"/>
-      <c r="G31" s="136"/>
-      <c r="H31" s="136"/>
-      <c r="I31" s="136"/>
-      <c r="J31" s="136"/>
-      <c r="K31" s="148"/>
-      <c r="L31" s="148"/>
-      <c r="M31" s="136"/>
-      <c r="N31" s="154"/>
-      <c r="O31" s="154"/>
-      <c r="P31" s="154"/>
-      <c r="Q31" s="154"/>
-    </row>
-    <row r="32" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C31" s="120"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="118"/>
+      <c r="L31" s="118"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="130"/>
+      <c r="O31" s="130"/>
+      <c r="P31" s="130"/>
+      <c r="Q31" s="130"/>
+    </row>
+    <row r="32" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A32" s="24" t="str">
         <f>_xlfn.XLOOKUP(B32,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11086,52 +11086,52 @@
       <c r="B32" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C32" s="138">
+      <c r="C32" s="124">
         <v>3</v>
       </c>
-      <c r="D32" s="138" t="s">
+      <c r="D32" s="124" t="s">
         <v>228</v>
       </c>
-      <c r="E32" s="152" t="s">
+      <c r="E32" s="128" t="s">
         <v>229</v>
       </c>
-      <c r="F32" s="138" t="s">
+      <c r="F32" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G32" s="138"/>
-      <c r="H32" s="138" t="s">
+      <c r="G32" s="124"/>
+      <c r="H32" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I32" s="138"/>
-      <c r="J32" s="138">
+      <c r="I32" s="124"/>
+      <c r="J32" s="124">
         <v>3</v>
       </c>
-      <c r="K32" s="147">
+      <c r="K32" s="117">
         <f>J32*12</f>
         <v>36</v>
       </c>
-      <c r="L32" s="147">
+      <c r="L32" s="117">
         <f>36*J32</f>
         <v>108</v>
       </c>
-      <c r="M32" s="138">
+      <c r="M32" s="124">
         <f>SUM(K32:L32)</f>
         <v>144</v>
       </c>
-      <c r="N32" s="152" t="s">
+      <c r="N32" s="128" t="s">
         <v>230</v>
       </c>
-      <c r="O32" s="152" t="s">
+      <c r="O32" s="128" t="s">
         <v>231</v>
       </c>
-      <c r="P32" s="152" t="s">
+      <c r="P32" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q32" s="152" t="s">
+      <c r="Q32" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="33" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A33" s="24" t="str">
         <f>_xlfn.XLOOKUP(B33,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11139,23 +11139,23 @@
       <c r="B33" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="116"/>
-      <c r="D33" s="116"/>
-      <c r="E33" s="153"/>
-      <c r="F33" s="116"/>
-      <c r="G33" s="116"/>
-      <c r="H33" s="116"/>
-      <c r="I33" s="116"/>
-      <c r="J33" s="116"/>
-      <c r="K33" s="147"/>
-      <c r="L33" s="147"/>
-      <c r="M33" s="116"/>
-      <c r="N33" s="153"/>
-      <c r="O33" s="153"/>
-      <c r="P33" s="153"/>
-      <c r="Q33" s="153"/>
-    </row>
-    <row r="34" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C33" s="119"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="129"/>
+      <c r="F33" s="119"/>
+      <c r="G33" s="119"/>
+      <c r="H33" s="119"/>
+      <c r="I33" s="119"/>
+      <c r="J33" s="119"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="117"/>
+      <c r="M33" s="119"/>
+      <c r="N33" s="129"/>
+      <c r="O33" s="129"/>
+      <c r="P33" s="129"/>
+      <c r="Q33" s="129"/>
+    </row>
+    <row r="34" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="80" t="str">
         <f>_xlfn.XLOOKUP(B34,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11163,23 +11163,23 @@
       <c r="B34" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="136"/>
-      <c r="D34" s="136"/>
-      <c r="E34" s="154"/>
-      <c r="F34" s="136"/>
-      <c r="G34" s="136"/>
-      <c r="H34" s="136"/>
-      <c r="I34" s="136"/>
-      <c r="J34" s="136"/>
-      <c r="K34" s="148"/>
-      <c r="L34" s="148"/>
-      <c r="M34" s="136"/>
-      <c r="N34" s="154"/>
-      <c r="O34" s="154"/>
-      <c r="P34" s="154"/>
-      <c r="Q34" s="154"/>
-    </row>
-    <row r="35" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C34" s="120"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="130"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="120"/>
+      <c r="H34" s="120"/>
+      <c r="I34" s="120"/>
+      <c r="J34" s="120"/>
+      <c r="K34" s="118"/>
+      <c r="L34" s="118"/>
+      <c r="M34" s="120"/>
+      <c r="N34" s="130"/>
+      <c r="O34" s="130"/>
+      <c r="P34" s="130"/>
+      <c r="Q34" s="130"/>
+    </row>
+    <row r="35" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A35" s="24" t="str">
         <f>_xlfn.XLOOKUP(B35,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11187,52 +11187,52 @@
       <c r="B35" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="138">
+      <c r="C35" s="124">
         <v>3</v>
       </c>
-      <c r="D35" s="138" t="s">
+      <c r="D35" s="124" t="s">
         <v>232</v>
       </c>
-      <c r="E35" s="152" t="s">
+      <c r="E35" s="128" t="s">
         <v>233</v>
       </c>
-      <c r="F35" s="138" t="s">
+      <c r="F35" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G35" s="138"/>
-      <c r="H35" s="138" t="s">
+      <c r="G35" s="124"/>
+      <c r="H35" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I35" s="138"/>
-      <c r="J35" s="138">
+      <c r="I35" s="124"/>
+      <c r="J35" s="124">
         <v>4</v>
       </c>
-      <c r="K35" s="147">
+      <c r="K35" s="117">
         <f>J35*12</f>
         <v>48</v>
       </c>
-      <c r="L35" s="147">
+      <c r="L35" s="117">
         <f>36*J35</f>
         <v>144</v>
       </c>
-      <c r="M35" s="138">
+      <c r="M35" s="124">
         <f>SUM(K35:L35)</f>
         <v>192</v>
       </c>
-      <c r="N35" s="152" t="s">
+      <c r="N35" s="128" t="s">
         <v>234</v>
       </c>
-      <c r="O35" s="152" t="s">
+      <c r="O35" s="128" t="s">
         <v>209</v>
       </c>
-      <c r="P35" s="152" t="s">
+      <c r="P35" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q35" s="152" t="s">
+      <c r="Q35" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A36" s="24" t="str">
         <f>_xlfn.XLOOKUP(B36,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11240,23 +11240,23 @@
       <c r="B36" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C36" s="116"/>
-      <c r="D36" s="116"/>
-      <c r="E36" s="153"/>
-      <c r="F36" s="116"/>
-      <c r="G36" s="116"/>
-      <c r="H36" s="116"/>
-      <c r="I36" s="116"/>
-      <c r="J36" s="116"/>
-      <c r="K36" s="147"/>
-      <c r="L36" s="147"/>
-      <c r="M36" s="116"/>
-      <c r="N36" s="153"/>
-      <c r="O36" s="153"/>
-      <c r="P36" s="153"/>
-      <c r="Q36" s="153"/>
-    </row>
-    <row r="37" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C36" s="119"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="129"/>
+      <c r="F36" s="119"/>
+      <c r="G36" s="119"/>
+      <c r="H36" s="119"/>
+      <c r="I36" s="119"/>
+      <c r="J36" s="119"/>
+      <c r="K36" s="117"/>
+      <c r="L36" s="117"/>
+      <c r="M36" s="119"/>
+      <c r="N36" s="129"/>
+      <c r="O36" s="129"/>
+      <c r="P36" s="129"/>
+      <c r="Q36" s="129"/>
+    </row>
+    <row r="37" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="80" t="str">
         <f>_xlfn.XLOOKUP(B37,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11264,21 +11264,21 @@
       <c r="B37" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="136"/>
-      <c r="D37" s="136"/>
-      <c r="E37" s="154"/>
-      <c r="F37" s="136"/>
-      <c r="G37" s="136"/>
-      <c r="H37" s="136"/>
-      <c r="I37" s="136"/>
-      <c r="J37" s="136"/>
-      <c r="K37" s="148"/>
-      <c r="L37" s="148"/>
-      <c r="M37" s="136"/>
-      <c r="N37" s="154"/>
-      <c r="O37" s="154"/>
-      <c r="P37" s="154"/>
-      <c r="Q37" s="154"/>
+      <c r="C37" s="120"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="120"/>
+      <c r="H37" s="120"/>
+      <c r="I37" s="120"/>
+      <c r="J37" s="120"/>
+      <c r="K37" s="118"/>
+      <c r="L37" s="118"/>
+      <c r="M37" s="120"/>
+      <c r="N37" s="130"/>
+      <c r="O37" s="130"/>
+      <c r="P37" s="130"/>
+      <c r="Q37" s="130"/>
       <c r="R37" s="50">
         <f>SUM(J27:J37)</f>
         <v>16</v>
@@ -11288,7 +11288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="50" customFormat="1" ht="264.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:19" s="50" customFormat="1" ht="324.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="88" t="str">
         <f>_xlfn.XLOOKUP(B38,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11341,7 +11341,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="39" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="str">
         <f>_xlfn.XLOOKUP(B39,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11349,52 +11349,52 @@
       <c r="B39" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C39" s="138">
+      <c r="C39" s="124">
         <v>4</v>
       </c>
-      <c r="D39" s="138" t="s">
+      <c r="D39" s="124" t="s">
         <v>238</v>
       </c>
-      <c r="E39" s="152" t="s">
+      <c r="E39" s="128" t="s">
         <v>239</v>
       </c>
-      <c r="F39" s="138" t="s">
+      <c r="F39" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G39" s="138"/>
-      <c r="H39" s="138" t="s">
+      <c r="G39" s="124"/>
+      <c r="H39" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I39" s="138"/>
-      <c r="J39" s="138">
+      <c r="I39" s="124"/>
+      <c r="J39" s="124">
         <v>3</v>
       </c>
-      <c r="K39" s="147">
+      <c r="K39" s="117">
         <f>J39*12</f>
         <v>36</v>
       </c>
-      <c r="L39" s="147">
+      <c r="L39" s="117">
         <f>36*J39</f>
         <v>108</v>
       </c>
-      <c r="M39" s="138">
+      <c r="M39" s="124">
         <f>SUM(K39:L39)</f>
         <v>144</v>
       </c>
-      <c r="N39" s="152" t="s">
+      <c r="N39" s="128" t="s">
         <v>240</v>
       </c>
-      <c r="O39" s="152" t="s">
+      <c r="O39" s="128" t="s">
         <v>241</v>
       </c>
-      <c r="P39" s="152" t="s">
+      <c r="P39" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q39" s="152" t="s">
+      <c r="Q39" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="40" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A40" s="24" t="str">
         <f>_xlfn.XLOOKUP(B40,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11402,23 +11402,23 @@
       <c r="B40" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C40" s="116"/>
-      <c r="D40" s="116"/>
-      <c r="E40" s="153"/>
-      <c r="F40" s="116"/>
-      <c r="G40" s="116"/>
-      <c r="H40" s="116"/>
-      <c r="I40" s="116"/>
-      <c r="J40" s="116"/>
-      <c r="K40" s="147"/>
-      <c r="L40" s="147"/>
-      <c r="M40" s="116"/>
-      <c r="N40" s="153"/>
-      <c r="O40" s="153"/>
-      <c r="P40" s="153"/>
-      <c r="Q40" s="153"/>
-    </row>
-    <row r="41" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C40" s="119"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="129"/>
+      <c r="F40" s="119"/>
+      <c r="G40" s="119"/>
+      <c r="H40" s="119"/>
+      <c r="I40" s="119"/>
+      <c r="J40" s="119"/>
+      <c r="K40" s="117"/>
+      <c r="L40" s="117"/>
+      <c r="M40" s="119"/>
+      <c r="N40" s="129"/>
+      <c r="O40" s="129"/>
+      <c r="P40" s="129"/>
+      <c r="Q40" s="129"/>
+    </row>
+    <row r="41" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="80" t="str">
         <f>_xlfn.XLOOKUP(B41,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11426,23 +11426,23 @@
       <c r="B41" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="136"/>
-      <c r="D41" s="136"/>
-      <c r="E41" s="154"/>
-      <c r="F41" s="136"/>
-      <c r="G41" s="136"/>
-      <c r="H41" s="136"/>
-      <c r="I41" s="136"/>
-      <c r="J41" s="136"/>
-      <c r="K41" s="148"/>
-      <c r="L41" s="148"/>
-      <c r="M41" s="136"/>
-      <c r="N41" s="154"/>
-      <c r="O41" s="154"/>
-      <c r="P41" s="154"/>
-      <c r="Q41" s="154"/>
-    </row>
-    <row r="42" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C41" s="120"/>
+      <c r="D41" s="120"/>
+      <c r="E41" s="130"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="120"/>
+      <c r="H41" s="120"/>
+      <c r="I41" s="120"/>
+      <c r="J41" s="120"/>
+      <c r="K41" s="118"/>
+      <c r="L41" s="118"/>
+      <c r="M41" s="120"/>
+      <c r="N41" s="130"/>
+      <c r="O41" s="130"/>
+      <c r="P41" s="130"/>
+      <c r="Q41" s="130"/>
+    </row>
+    <row r="42" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A42" s="24" t="str">
         <f>_xlfn.XLOOKUP(B42,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11450,52 +11450,52 @@
       <c r="B42" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="138">
+      <c r="C42" s="124">
         <v>4</v>
       </c>
-      <c r="D42" s="138" t="s">
+      <c r="D42" s="124" t="s">
         <v>242</v>
       </c>
-      <c r="E42" s="155" t="s">
+      <c r="E42" s="131" t="s">
         <v>243</v>
       </c>
-      <c r="F42" s="138" t="s">
+      <c r="F42" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G42" s="138"/>
-      <c r="H42" s="138" t="s">
+      <c r="G42" s="124"/>
+      <c r="H42" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I42" s="138"/>
-      <c r="J42" s="138">
+      <c r="I42" s="124"/>
+      <c r="J42" s="124">
         <v>3</v>
       </c>
-      <c r="K42" s="138">
+      <c r="K42" s="124">
         <f>J42*12</f>
         <v>36</v>
       </c>
-      <c r="L42" s="138">
+      <c r="L42" s="124">
         <f>36*J42</f>
         <v>108</v>
       </c>
-      <c r="M42" s="138">
+      <c r="M42" s="124">
         <f>SUM(K42:L42)</f>
         <v>144</v>
       </c>
-      <c r="N42" s="152" t="s">
+      <c r="N42" s="128" t="s">
         <v>244</v>
       </c>
-      <c r="O42" s="152" t="s">
+      <c r="O42" s="128" t="s">
         <v>241</v>
       </c>
-      <c r="P42" s="152" t="s">
+      <c r="P42" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q42" s="152" t="s">
+      <c r="Q42" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="43" spans="1:19" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A43" s="24" t="str">
         <f>_xlfn.XLOOKUP(B43,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11503,23 +11503,23 @@
       <c r="B43" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="116"/>
-      <c r="D43" s="116"/>
-      <c r="E43" s="149"/>
-      <c r="F43" s="116"/>
-      <c r="G43" s="116"/>
-      <c r="H43" s="116"/>
-      <c r="I43" s="116"/>
-      <c r="J43" s="116"/>
-      <c r="K43" s="116"/>
-      <c r="L43" s="116"/>
-      <c r="M43" s="116"/>
-      <c r="N43" s="153"/>
-      <c r="O43" s="153"/>
-      <c r="P43" s="153"/>
-      <c r="Q43" s="153"/>
-    </row>
-    <row r="44" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C43" s="119"/>
+      <c r="D43" s="119"/>
+      <c r="E43" s="121"/>
+      <c r="F43" s="119"/>
+      <c r="G43" s="119"/>
+      <c r="H43" s="119"/>
+      <c r="I43" s="119"/>
+      <c r="J43" s="119"/>
+      <c r="K43" s="119"/>
+      <c r="L43" s="119"/>
+      <c r="M43" s="119"/>
+      <c r="N43" s="129"/>
+      <c r="O43" s="129"/>
+      <c r="P43" s="129"/>
+      <c r="Q43" s="129"/>
+    </row>
+    <row r="44" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="str">
         <f>_xlfn.XLOOKUP(B44,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11527,23 +11527,23 @@
       <c r="B44" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="116"/>
-      <c r="D44" s="116"/>
-      <c r="E44" s="149"/>
-      <c r="F44" s="116"/>
-      <c r="G44" s="116"/>
-      <c r="H44" s="116"/>
-      <c r="I44" s="116"/>
-      <c r="J44" s="116"/>
-      <c r="K44" s="116"/>
-      <c r="L44" s="116"/>
-      <c r="M44" s="116"/>
-      <c r="N44" s="153"/>
-      <c r="O44" s="153"/>
-      <c r="P44" s="153"/>
-      <c r="Q44" s="153"/>
-    </row>
-    <row r="45" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C44" s="119"/>
+      <c r="D44" s="119"/>
+      <c r="E44" s="121"/>
+      <c r="F44" s="119"/>
+      <c r="G44" s="119"/>
+      <c r="H44" s="119"/>
+      <c r="I44" s="119"/>
+      <c r="J44" s="119"/>
+      <c r="K44" s="119"/>
+      <c r="L44" s="119"/>
+      <c r="M44" s="119"/>
+      <c r="N44" s="129"/>
+      <c r="O44" s="129"/>
+      <c r="P44" s="129"/>
+      <c r="Q44" s="129"/>
+    </row>
+    <row r="45" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="80" t="str">
         <f>_xlfn.XLOOKUP(B45,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11551,23 +11551,23 @@
       <c r="B45" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="136"/>
-      <c r="D45" s="136"/>
-      <c r="E45" s="150"/>
-      <c r="F45" s="136"/>
-      <c r="G45" s="136"/>
-      <c r="H45" s="136"/>
-      <c r="I45" s="136"/>
-      <c r="J45" s="136"/>
-      <c r="K45" s="136"/>
-      <c r="L45" s="136"/>
-      <c r="M45" s="136"/>
-      <c r="N45" s="154"/>
-      <c r="O45" s="154"/>
-      <c r="P45" s="154"/>
-      <c r="Q45" s="154"/>
-    </row>
-    <row r="46" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C45" s="120"/>
+      <c r="D45" s="120"/>
+      <c r="E45" s="122"/>
+      <c r="F45" s="120"/>
+      <c r="G45" s="120"/>
+      <c r="H45" s="120"/>
+      <c r="I45" s="120"/>
+      <c r="J45" s="120"/>
+      <c r="K45" s="120"/>
+      <c r="L45" s="120"/>
+      <c r="M45" s="120"/>
+      <c r="N45" s="130"/>
+      <c r="O45" s="130"/>
+      <c r="P45" s="130"/>
+      <c r="Q45" s="130"/>
+    </row>
+    <row r="46" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A46" s="24" t="str">
         <f>_xlfn.XLOOKUP(B46,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11575,52 +11575,52 @@
       <c r="B46" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C46" s="138">
+      <c r="C46" s="124">
         <v>4</v>
       </c>
-      <c r="D46" s="138" t="s">
+      <c r="D46" s="124" t="s">
         <v>245</v>
       </c>
-      <c r="E46" s="152" t="s">
+      <c r="E46" s="128" t="s">
         <v>246</v>
       </c>
-      <c r="F46" s="138" t="s">
+      <c r="F46" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G46" s="138"/>
-      <c r="H46" s="138" t="s">
+      <c r="G46" s="124"/>
+      <c r="H46" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I46" s="138"/>
-      <c r="J46" s="138">
+      <c r="I46" s="124"/>
+      <c r="J46" s="124">
         <v>4</v>
       </c>
-      <c r="K46" s="138">
+      <c r="K46" s="124">
         <f>J46*12</f>
         <v>48</v>
       </c>
-      <c r="L46" s="138">
+      <c r="L46" s="124">
         <f>36*J46</f>
         <v>144</v>
       </c>
-      <c r="M46" s="138">
+      <c r="M46" s="124">
         <f>SUM(K46:L46)</f>
         <v>192</v>
       </c>
-      <c r="N46" s="152" t="s">
+      <c r="N46" s="128" t="s">
         <v>247</v>
       </c>
-      <c r="O46" s="152" t="s">
+      <c r="O46" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="P46" s="152" t="s">
+      <c r="P46" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q46" s="152" t="s">
+      <c r="Q46" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="47" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A47" s="24" t="str">
         <f>_xlfn.XLOOKUP(B47,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11628,23 +11628,23 @@
       <c r="B47" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="116"/>
-      <c r="D47" s="116"/>
-      <c r="E47" s="153"/>
-      <c r="F47" s="116"/>
-      <c r="G47" s="116"/>
-      <c r="H47" s="116"/>
-      <c r="I47" s="116"/>
-      <c r="J47" s="116"/>
-      <c r="K47" s="116"/>
-      <c r="L47" s="116"/>
-      <c r="M47" s="116"/>
-      <c r="N47" s="153"/>
-      <c r="O47" s="153"/>
-      <c r="P47" s="153"/>
-      <c r="Q47" s="153"/>
-    </row>
-    <row r="48" spans="1:19" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+      <c r="C47" s="119"/>
+      <c r="D47" s="119"/>
+      <c r="E47" s="129"/>
+      <c r="F47" s="119"/>
+      <c r="G47" s="119"/>
+      <c r="H47" s="119"/>
+      <c r="I47" s="119"/>
+      <c r="J47" s="119"/>
+      <c r="K47" s="119"/>
+      <c r="L47" s="119"/>
+      <c r="M47" s="119"/>
+      <c r="N47" s="129"/>
+      <c r="O47" s="129"/>
+      <c r="P47" s="129"/>
+      <c r="Q47" s="129"/>
+    </row>
+    <row r="48" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A48" s="24" t="str">
         <f>_xlfn.XLOOKUP(B48,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11652,23 +11652,23 @@
       <c r="B48" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="116"/>
-      <c r="D48" s="116"/>
-      <c r="E48" s="153"/>
-      <c r="F48" s="116"/>
-      <c r="G48" s="116"/>
-      <c r="H48" s="116"/>
-      <c r="I48" s="116"/>
-      <c r="J48" s="116"/>
-      <c r="K48" s="116"/>
-      <c r="L48" s="116"/>
-      <c r="M48" s="116"/>
-      <c r="N48" s="153"/>
-      <c r="O48" s="153"/>
-      <c r="P48" s="153"/>
-      <c r="Q48" s="153"/>
-    </row>
-    <row r="49" spans="1:19" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+      <c r="C48" s="119"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="129"/>
+      <c r="F48" s="119"/>
+      <c r="G48" s="119"/>
+      <c r="H48" s="119"/>
+      <c r="I48" s="119"/>
+      <c r="J48" s="119"/>
+      <c r="K48" s="119"/>
+      <c r="L48" s="119"/>
+      <c r="M48" s="119"/>
+      <c r="N48" s="129"/>
+      <c r="O48" s="129"/>
+      <c r="P48" s="129"/>
+      <c r="Q48" s="129"/>
+    </row>
+    <row r="49" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A49" s="24" t="str">
         <f>_xlfn.XLOOKUP(B49,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11676,23 +11676,23 @@
       <c r="B49" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="116"/>
-      <c r="D49" s="116"/>
-      <c r="E49" s="153"/>
-      <c r="F49" s="116"/>
-      <c r="G49" s="116"/>
-      <c r="H49" s="116"/>
-      <c r="I49" s="116"/>
-      <c r="J49" s="116"/>
-      <c r="K49" s="116"/>
-      <c r="L49" s="116"/>
-      <c r="M49" s="116"/>
-      <c r="N49" s="153"/>
-      <c r="O49" s="153"/>
-      <c r="P49" s="153"/>
-      <c r="Q49" s="153"/>
-    </row>
-    <row r="50" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C49" s="119"/>
+      <c r="D49" s="119"/>
+      <c r="E49" s="129"/>
+      <c r="F49" s="119"/>
+      <c r="G49" s="119"/>
+      <c r="H49" s="119"/>
+      <c r="I49" s="119"/>
+      <c r="J49" s="119"/>
+      <c r="K49" s="119"/>
+      <c r="L49" s="119"/>
+      <c r="M49" s="119"/>
+      <c r="N49" s="129"/>
+      <c r="O49" s="129"/>
+      <c r="P49" s="129"/>
+      <c r="Q49" s="129"/>
+    </row>
+    <row r="50" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="80" t="str">
         <f>_xlfn.XLOOKUP(B50,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11700,23 +11700,23 @@
       <c r="B50" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="136"/>
-      <c r="D50" s="136"/>
-      <c r="E50" s="154"/>
-      <c r="F50" s="136"/>
-      <c r="G50" s="136"/>
-      <c r="H50" s="136"/>
-      <c r="I50" s="136"/>
-      <c r="J50" s="136"/>
-      <c r="K50" s="136"/>
-      <c r="L50" s="136"/>
-      <c r="M50" s="136"/>
-      <c r="N50" s="154"/>
-      <c r="O50" s="154"/>
-      <c r="P50" s="154"/>
-      <c r="Q50" s="154"/>
-    </row>
-    <row r="51" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C50" s="120"/>
+      <c r="D50" s="120"/>
+      <c r="E50" s="130"/>
+      <c r="F50" s="120"/>
+      <c r="G50" s="120"/>
+      <c r="H50" s="120"/>
+      <c r="I50" s="120"/>
+      <c r="J50" s="120"/>
+      <c r="K50" s="120"/>
+      <c r="L50" s="120"/>
+      <c r="M50" s="120"/>
+      <c r="N50" s="130"/>
+      <c r="O50" s="130"/>
+      <c r="P50" s="130"/>
+      <c r="Q50" s="130"/>
+    </row>
+    <row r="51" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A51" s="24" t="str">
         <f>_xlfn.XLOOKUP(B51,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11724,52 +11724,52 @@
       <c r="B51" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C51" s="138">
+      <c r="C51" s="124">
         <v>4</v>
       </c>
-      <c r="D51" s="138" t="s">
+      <c r="D51" s="124" t="s">
         <v>248</v>
       </c>
-      <c r="E51" s="152" t="s">
+      <c r="E51" s="128" t="s">
         <v>249</v>
       </c>
-      <c r="F51" s="138" t="s">
+      <c r="F51" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G51" s="138"/>
-      <c r="H51" s="138" t="s">
+      <c r="G51" s="124"/>
+      <c r="H51" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I51" s="138"/>
-      <c r="J51" s="138">
+      <c r="I51" s="124"/>
+      <c r="J51" s="124">
         <v>3</v>
       </c>
-      <c r="K51" s="138">
+      <c r="K51" s="124">
         <f>J51*12</f>
         <v>36</v>
       </c>
-      <c r="L51" s="138">
+      <c r="L51" s="124">
         <f>36*J51</f>
         <v>108</v>
       </c>
-      <c r="M51" s="138">
+      <c r="M51" s="124">
         <f>SUM(K51:L51)</f>
         <v>144</v>
       </c>
-      <c r="N51" s="152" t="s">
+      <c r="N51" s="128" t="s">
         <v>250</v>
       </c>
-      <c r="O51" s="152" t="s">
+      <c r="O51" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="P51" s="152" t="s">
+      <c r="P51" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q51" s="152" t="s">
+      <c r="Q51" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="52" spans="1:19" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A52" s="24" t="str">
         <f>_xlfn.XLOOKUP(B52,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11777,23 +11777,23 @@
       <c r="B52" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C52" s="116"/>
-      <c r="D52" s="116"/>
-      <c r="E52" s="153"/>
-      <c r="F52" s="116"/>
-      <c r="G52" s="116"/>
-      <c r="H52" s="116"/>
-      <c r="I52" s="116"/>
-      <c r="J52" s="116"/>
-      <c r="K52" s="116"/>
-      <c r="L52" s="116"/>
-      <c r="M52" s="116"/>
-      <c r="N52" s="153"/>
-      <c r="O52" s="153"/>
-      <c r="P52" s="153"/>
-      <c r="Q52" s="153"/>
-    </row>
-    <row r="53" spans="1:19" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+      <c r="C52" s="119"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="129"/>
+      <c r="F52" s="119"/>
+      <c r="G52" s="119"/>
+      <c r="H52" s="119"/>
+      <c r="I52" s="119"/>
+      <c r="J52" s="119"/>
+      <c r="K52" s="119"/>
+      <c r="L52" s="119"/>
+      <c r="M52" s="119"/>
+      <c r="N52" s="129"/>
+      <c r="O52" s="129"/>
+      <c r="P52" s="129"/>
+      <c r="Q52" s="129"/>
+    </row>
+    <row r="53" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A53" s="24" t="str">
         <f>_xlfn.XLOOKUP(B53,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11801,23 +11801,23 @@
       <c r="B53" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C53" s="116"/>
-      <c r="D53" s="116"/>
-      <c r="E53" s="153"/>
-      <c r="F53" s="116"/>
-      <c r="G53" s="116"/>
-      <c r="H53" s="116"/>
-      <c r="I53" s="116"/>
-      <c r="J53" s="116"/>
-      <c r="K53" s="116"/>
-      <c r="L53" s="116"/>
-      <c r="M53" s="116"/>
-      <c r="N53" s="153"/>
-      <c r="O53" s="153"/>
-      <c r="P53" s="153"/>
-      <c r="Q53" s="153"/>
-    </row>
-    <row r="54" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C53" s="119"/>
+      <c r="D53" s="119"/>
+      <c r="E53" s="129"/>
+      <c r="F53" s="119"/>
+      <c r="G53" s="119"/>
+      <c r="H53" s="119"/>
+      <c r="I53" s="119"/>
+      <c r="J53" s="119"/>
+      <c r="K53" s="119"/>
+      <c r="L53" s="119"/>
+      <c r="M53" s="119"/>
+      <c r="N53" s="129"/>
+      <c r="O53" s="129"/>
+      <c r="P53" s="129"/>
+      <c r="Q53" s="129"/>
+    </row>
+    <row r="54" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="str">
         <f>_xlfn.XLOOKUP(B54,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -11825,23 +11825,23 @@
       <c r="B54" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="116"/>
-      <c r="D54" s="116"/>
-      <c r="E54" s="153"/>
-      <c r="F54" s="116"/>
-      <c r="G54" s="116"/>
-      <c r="H54" s="116"/>
-      <c r="I54" s="116"/>
-      <c r="J54" s="116"/>
-      <c r="K54" s="116"/>
-      <c r="L54" s="116"/>
-      <c r="M54" s="116"/>
-      <c r="N54" s="153"/>
-      <c r="O54" s="153"/>
-      <c r="P54" s="153"/>
-      <c r="Q54" s="153"/>
-    </row>
-    <row r="55" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C54" s="119"/>
+      <c r="D54" s="119"/>
+      <c r="E54" s="129"/>
+      <c r="F54" s="119"/>
+      <c r="G54" s="119"/>
+      <c r="H54" s="119"/>
+      <c r="I54" s="119"/>
+      <c r="J54" s="119"/>
+      <c r="K54" s="119"/>
+      <c r="L54" s="119"/>
+      <c r="M54" s="119"/>
+      <c r="N54" s="129"/>
+      <c r="O54" s="129"/>
+      <c r="P54" s="129"/>
+      <c r="Q54" s="129"/>
+    </row>
+    <row r="55" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="80" t="str">
         <f>_xlfn.XLOOKUP(B55,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11849,21 +11849,21 @@
       <c r="B55" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="136"/>
-      <c r="D55" s="136"/>
-      <c r="E55" s="154"/>
-      <c r="F55" s="136"/>
-      <c r="G55" s="136"/>
-      <c r="H55" s="136"/>
-      <c r="I55" s="136"/>
-      <c r="J55" s="136"/>
-      <c r="K55" s="136"/>
-      <c r="L55" s="136"/>
-      <c r="M55" s="136"/>
-      <c r="N55" s="154"/>
-      <c r="O55" s="154"/>
-      <c r="P55" s="154"/>
-      <c r="Q55" s="154"/>
+      <c r="C55" s="120"/>
+      <c r="D55" s="120"/>
+      <c r="E55" s="130"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="120"/>
+      <c r="H55" s="120"/>
+      <c r="I55" s="120"/>
+      <c r="J55" s="120"/>
+      <c r="K55" s="120"/>
+      <c r="L55" s="120"/>
+      <c r="M55" s="120"/>
+      <c r="N55" s="130"/>
+      <c r="O55" s="130"/>
+      <c r="P55" s="130"/>
+      <c r="Q55" s="130"/>
       <c r="R55" s="50">
         <f>SUM(J38:J55)</f>
         <v>16</v>
@@ -11873,7 +11873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A56" s="24" t="str">
         <f>_xlfn.XLOOKUP(B56,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11881,52 +11881,52 @@
       <c r="B56" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="138">
+      <c r="C56" s="124">
         <v>5</v>
       </c>
-      <c r="D56" s="138" t="s">
+      <c r="D56" s="124" t="s">
         <v>251</v>
       </c>
-      <c r="E56" s="152" t="s">
+      <c r="E56" s="128" t="s">
         <v>252</v>
       </c>
-      <c r="F56" s="138" t="s">
+      <c r="F56" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G56" s="138"/>
-      <c r="H56" s="138" t="s">
+      <c r="G56" s="124"/>
+      <c r="H56" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I56" s="138"/>
-      <c r="J56" s="138">
+      <c r="I56" s="124"/>
+      <c r="J56" s="124">
         <v>3</v>
       </c>
-      <c r="K56" s="138">
+      <c r="K56" s="124">
         <f>J56*12</f>
         <v>36</v>
       </c>
-      <c r="L56" s="138">
+      <c r="L56" s="124">
         <f>36*J56</f>
         <v>108</v>
       </c>
-      <c r="M56" s="138">
+      <c r="M56" s="124">
         <f>SUM(K56:L56)</f>
         <v>144</v>
       </c>
-      <c r="N56" s="152" t="s">
+      <c r="N56" s="128" t="s">
         <v>253</v>
       </c>
-      <c r="O56" s="152" t="s">
+      <c r="O56" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="P56" s="152" t="s">
+      <c r="P56" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q56" s="152" t="s">
+      <c r="Q56" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="57" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A57" s="24" t="str">
         <f>_xlfn.XLOOKUP(B57,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11934,23 +11934,23 @@
       <c r="B57" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C57" s="116"/>
-      <c r="D57" s="116"/>
-      <c r="E57" s="153"/>
-      <c r="F57" s="116"/>
-      <c r="G57" s="116"/>
-      <c r="H57" s="116"/>
-      <c r="I57" s="116"/>
-      <c r="J57" s="116"/>
-      <c r="K57" s="116"/>
-      <c r="L57" s="116"/>
-      <c r="M57" s="116"/>
-      <c r="N57" s="153"/>
-      <c r="O57" s="153"/>
-      <c r="P57" s="153"/>
-      <c r="Q57" s="153"/>
-    </row>
-    <row r="58" spans="1:19" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+      <c r="C57" s="119"/>
+      <c r="D57" s="119"/>
+      <c r="E57" s="129"/>
+      <c r="F57" s="119"/>
+      <c r="G57" s="119"/>
+      <c r="H57" s="119"/>
+      <c r="I57" s="119"/>
+      <c r="J57" s="119"/>
+      <c r="K57" s="119"/>
+      <c r="L57" s="119"/>
+      <c r="M57" s="119"/>
+      <c r="N57" s="129"/>
+      <c r="O57" s="129"/>
+      <c r="P57" s="129"/>
+      <c r="Q57" s="129"/>
+    </row>
+    <row r="58" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A58" s="24" t="str">
         <f>_xlfn.XLOOKUP(B58,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11958,23 +11958,23 @@
       <c r="B58" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="116"/>
-      <c r="D58" s="116"/>
-      <c r="E58" s="153"/>
-      <c r="F58" s="116"/>
-      <c r="G58" s="116"/>
-      <c r="H58" s="116"/>
-      <c r="I58" s="116"/>
-      <c r="J58" s="116"/>
-      <c r="K58" s="116"/>
-      <c r="L58" s="116"/>
-      <c r="M58" s="116"/>
-      <c r="N58" s="153"/>
-      <c r="O58" s="153"/>
-      <c r="P58" s="153"/>
-      <c r="Q58" s="153"/>
-    </row>
-    <row r="59" spans="1:19" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+      <c r="C58" s="119"/>
+      <c r="D58" s="119"/>
+      <c r="E58" s="129"/>
+      <c r="F58" s="119"/>
+      <c r="G58" s="119"/>
+      <c r="H58" s="119"/>
+      <c r="I58" s="119"/>
+      <c r="J58" s="119"/>
+      <c r="K58" s="119"/>
+      <c r="L58" s="119"/>
+      <c r="M58" s="119"/>
+      <c r="N58" s="129"/>
+      <c r="O58" s="129"/>
+      <c r="P58" s="129"/>
+      <c r="Q58" s="129"/>
+    </row>
+    <row r="59" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="24" t="str">
         <f>_xlfn.XLOOKUP(B59,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -11982,23 +11982,23 @@
       <c r="B59" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C59" s="116"/>
-      <c r="D59" s="116"/>
-      <c r="E59" s="153"/>
-      <c r="F59" s="116"/>
-      <c r="G59" s="116"/>
-      <c r="H59" s="116"/>
-      <c r="I59" s="116"/>
-      <c r="J59" s="116"/>
-      <c r="K59" s="116"/>
-      <c r="L59" s="116"/>
-      <c r="M59" s="116"/>
-      <c r="N59" s="153"/>
-      <c r="O59" s="153"/>
-      <c r="P59" s="153"/>
-      <c r="Q59" s="153"/>
-    </row>
-    <row r="60" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C59" s="119"/>
+      <c r="D59" s="119"/>
+      <c r="E59" s="129"/>
+      <c r="F59" s="119"/>
+      <c r="G59" s="119"/>
+      <c r="H59" s="119"/>
+      <c r="I59" s="119"/>
+      <c r="J59" s="119"/>
+      <c r="K59" s="119"/>
+      <c r="L59" s="119"/>
+      <c r="M59" s="119"/>
+      <c r="N59" s="129"/>
+      <c r="O59" s="129"/>
+      <c r="P59" s="129"/>
+      <c r="Q59" s="129"/>
+    </row>
+    <row r="60" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="80" t="str">
         <f>_xlfn.XLOOKUP(B60,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12006,23 +12006,23 @@
       <c r="B60" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C60" s="136"/>
-      <c r="D60" s="136"/>
-      <c r="E60" s="154"/>
-      <c r="F60" s="136"/>
-      <c r="G60" s="136"/>
-      <c r="H60" s="136"/>
-      <c r="I60" s="136"/>
-      <c r="J60" s="136"/>
-      <c r="K60" s="136"/>
-      <c r="L60" s="136"/>
-      <c r="M60" s="136"/>
-      <c r="N60" s="154"/>
-      <c r="O60" s="154"/>
-      <c r="P60" s="154"/>
-      <c r="Q60" s="154"/>
-    </row>
-    <row r="61" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C60" s="120"/>
+      <c r="D60" s="120"/>
+      <c r="E60" s="130"/>
+      <c r="F60" s="120"/>
+      <c r="G60" s="120"/>
+      <c r="H60" s="120"/>
+      <c r="I60" s="120"/>
+      <c r="J60" s="120"/>
+      <c r="K60" s="120"/>
+      <c r="L60" s="120"/>
+      <c r="M60" s="120"/>
+      <c r="N60" s="130"/>
+      <c r="O60" s="130"/>
+      <c r="P60" s="130"/>
+      <c r="Q60" s="130"/>
+    </row>
+    <row r="61" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="str">
         <f>_xlfn.XLOOKUP(B61,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12030,52 +12030,52 @@
       <c r="B61" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="138">
+      <c r="C61" s="124">
         <v>5</v>
       </c>
-      <c r="D61" s="138" t="s">
+      <c r="D61" s="124" t="s">
         <v>254</v>
       </c>
-      <c r="E61" s="152" t="s">
+      <c r="E61" s="128" t="s">
         <v>255</v>
       </c>
-      <c r="F61" s="138" t="s">
+      <c r="F61" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G61" s="138"/>
-      <c r="H61" s="138" t="s">
+      <c r="G61" s="124"/>
+      <c r="H61" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I61" s="138"/>
-      <c r="J61" s="138">
+      <c r="I61" s="124"/>
+      <c r="J61" s="124">
         <v>3</v>
       </c>
-      <c r="K61" s="138">
+      <c r="K61" s="124">
         <f>J61*12</f>
         <v>36</v>
       </c>
-      <c r="L61" s="138">
+      <c r="L61" s="124">
         <f>36*J61</f>
         <v>108</v>
       </c>
-      <c r="M61" s="138">
+      <c r="M61" s="124">
         <f>SUM(K61:L61)</f>
         <v>144</v>
       </c>
-      <c r="N61" s="152" t="s">
+      <c r="N61" s="128" t="s">
         <v>256</v>
       </c>
-      <c r="O61" s="152" t="s">
+      <c r="O61" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="P61" s="152" t="s">
+      <c r="P61" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q61" s="152" t="s">
+      <c r="Q61" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="62" spans="1:19" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="str">
         <f>_xlfn.XLOOKUP(B62,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12083,23 +12083,23 @@
       <c r="B62" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C62" s="116"/>
-      <c r="D62" s="116"/>
-      <c r="E62" s="153"/>
-      <c r="F62" s="116"/>
-      <c r="G62" s="116"/>
-      <c r="H62" s="116"/>
-      <c r="I62" s="116"/>
-      <c r="J62" s="116"/>
-      <c r="K62" s="116"/>
-      <c r="L62" s="116"/>
-      <c r="M62" s="116"/>
-      <c r="N62" s="153"/>
-      <c r="O62" s="153"/>
-      <c r="P62" s="153"/>
-      <c r="Q62" s="153"/>
-    </row>
-    <row r="63" spans="1:19" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+      <c r="C62" s="119"/>
+      <c r="D62" s="119"/>
+      <c r="E62" s="129"/>
+      <c r="F62" s="119"/>
+      <c r="G62" s="119"/>
+      <c r="H62" s="119"/>
+      <c r="I62" s="119"/>
+      <c r="J62" s="119"/>
+      <c r="K62" s="119"/>
+      <c r="L62" s="119"/>
+      <c r="M62" s="119"/>
+      <c r="N62" s="129"/>
+      <c r="O62" s="129"/>
+      <c r="P62" s="129"/>
+      <c r="Q62" s="129"/>
+    </row>
+    <row r="63" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="str">
         <f>_xlfn.XLOOKUP(B63,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12107,23 +12107,23 @@
       <c r="B63" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C63" s="116"/>
-      <c r="D63" s="116"/>
-      <c r="E63" s="153"/>
-      <c r="F63" s="116"/>
-      <c r="G63" s="116"/>
-      <c r="H63" s="116"/>
-      <c r="I63" s="116"/>
-      <c r="J63" s="116"/>
-      <c r="K63" s="116"/>
-      <c r="L63" s="116"/>
-      <c r="M63" s="116"/>
-      <c r="N63" s="153"/>
-      <c r="O63" s="153"/>
-      <c r="P63" s="153"/>
-      <c r="Q63" s="153"/>
-    </row>
-    <row r="64" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C63" s="119"/>
+      <c r="D63" s="119"/>
+      <c r="E63" s="129"/>
+      <c r="F63" s="119"/>
+      <c r="G63" s="119"/>
+      <c r="H63" s="119"/>
+      <c r="I63" s="119"/>
+      <c r="J63" s="119"/>
+      <c r="K63" s="119"/>
+      <c r="L63" s="119"/>
+      <c r="M63" s="119"/>
+      <c r="N63" s="129"/>
+      <c r="O63" s="129"/>
+      <c r="P63" s="129"/>
+      <c r="Q63" s="129"/>
+    </row>
+    <row r="64" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A64" s="24" t="str">
         <f>_xlfn.XLOOKUP(B64,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12131,23 +12131,23 @@
       <c r="B64" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C64" s="116"/>
-      <c r="D64" s="116"/>
-      <c r="E64" s="153"/>
-      <c r="F64" s="116"/>
-      <c r="G64" s="116"/>
-      <c r="H64" s="116"/>
-      <c r="I64" s="116"/>
-      <c r="J64" s="116"/>
-      <c r="K64" s="116"/>
-      <c r="L64" s="116"/>
-      <c r="M64" s="116"/>
-      <c r="N64" s="153"/>
-      <c r="O64" s="153"/>
-      <c r="P64" s="153"/>
-      <c r="Q64" s="153"/>
-    </row>
-    <row r="65" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C64" s="119"/>
+      <c r="D64" s="119"/>
+      <c r="E64" s="129"/>
+      <c r="F64" s="119"/>
+      <c r="G64" s="119"/>
+      <c r="H64" s="119"/>
+      <c r="I64" s="119"/>
+      <c r="J64" s="119"/>
+      <c r="K64" s="119"/>
+      <c r="L64" s="119"/>
+      <c r="M64" s="119"/>
+      <c r="N64" s="129"/>
+      <c r="O64" s="129"/>
+      <c r="P64" s="129"/>
+      <c r="Q64" s="129"/>
+    </row>
+    <row r="65" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="80" t="str">
         <f>_xlfn.XLOOKUP(B65,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12155,23 +12155,23 @@
       <c r="B65" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C65" s="136"/>
-      <c r="D65" s="136"/>
-      <c r="E65" s="154"/>
-      <c r="F65" s="136"/>
-      <c r="G65" s="136"/>
-      <c r="H65" s="136"/>
-      <c r="I65" s="136"/>
-      <c r="J65" s="136"/>
-      <c r="K65" s="136"/>
-      <c r="L65" s="136"/>
-      <c r="M65" s="136"/>
-      <c r="N65" s="154"/>
-      <c r="O65" s="154"/>
-      <c r="P65" s="154"/>
-      <c r="Q65" s="154"/>
-    </row>
-    <row r="66" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C65" s="120"/>
+      <c r="D65" s="120"/>
+      <c r="E65" s="130"/>
+      <c r="F65" s="120"/>
+      <c r="G65" s="120"/>
+      <c r="H65" s="120"/>
+      <c r="I65" s="120"/>
+      <c r="J65" s="120"/>
+      <c r="K65" s="120"/>
+      <c r="L65" s="120"/>
+      <c r="M65" s="120"/>
+      <c r="N65" s="130"/>
+      <c r="O65" s="130"/>
+      <c r="P65" s="130"/>
+      <c r="Q65" s="130"/>
+    </row>
+    <row r="66" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A66" s="24" t="str">
         <f>_xlfn.XLOOKUP(B66,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12179,52 +12179,52 @@
       <c r="B66" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C66" s="138">
+      <c r="C66" s="124">
         <v>5</v>
       </c>
-      <c r="D66" s="138" t="s">
+      <c r="D66" s="124" t="s">
         <v>257</v>
       </c>
-      <c r="E66" s="152" t="s">
+      <c r="E66" s="128" t="s">
         <v>258</v>
       </c>
-      <c r="F66" s="138" t="s">
+      <c r="F66" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G66" s="138"/>
-      <c r="H66" s="138" t="s">
+      <c r="G66" s="124"/>
+      <c r="H66" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I66" s="138"/>
-      <c r="J66" s="138">
+      <c r="I66" s="124"/>
+      <c r="J66" s="124">
         <v>3</v>
       </c>
-      <c r="K66" s="138">
+      <c r="K66" s="124">
         <f>J66*12</f>
         <v>36</v>
       </c>
-      <c r="L66" s="138">
+      <c r="L66" s="124">
         <f>36*J66</f>
         <v>108</v>
       </c>
-      <c r="M66" s="138">
+      <c r="M66" s="124">
         <f>SUM(K66:L66)</f>
         <v>144</v>
       </c>
-      <c r="N66" s="152" t="s">
+      <c r="N66" s="128" t="s">
         <v>259</v>
       </c>
-      <c r="O66" s="152" t="s">
+      <c r="O66" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="P66" s="152" t="s">
+      <c r="P66" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q66" s="152" t="s">
+      <c r="Q66" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="67" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A67" s="24" t="str">
         <f>_xlfn.XLOOKUP(B67,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12232,23 +12232,23 @@
       <c r="B67" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C67" s="116"/>
-      <c r="D67" s="116"/>
-      <c r="E67" s="153"/>
-      <c r="F67" s="116"/>
-      <c r="G67" s="116"/>
-      <c r="H67" s="116"/>
-      <c r="I67" s="116"/>
-      <c r="J67" s="116"/>
-      <c r="K67" s="116"/>
-      <c r="L67" s="116"/>
-      <c r="M67" s="116"/>
-      <c r="N67" s="153"/>
-      <c r="O67" s="153"/>
-      <c r="P67" s="153"/>
-      <c r="Q67" s="153"/>
-    </row>
-    <row r="68" spans="1:19" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+      <c r="C67" s="119"/>
+      <c r="D67" s="119"/>
+      <c r="E67" s="129"/>
+      <c r="F67" s="119"/>
+      <c r="G67" s="119"/>
+      <c r="H67" s="119"/>
+      <c r="I67" s="119"/>
+      <c r="J67" s="119"/>
+      <c r="K67" s="119"/>
+      <c r="L67" s="119"/>
+      <c r="M67" s="119"/>
+      <c r="N67" s="129"/>
+      <c r="O67" s="129"/>
+      <c r="P67" s="129"/>
+      <c r="Q67" s="129"/>
+    </row>
+    <row r="68" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A68" s="24" t="str">
         <f>_xlfn.XLOOKUP(B68,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12256,23 +12256,23 @@
       <c r="B68" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C68" s="116"/>
-      <c r="D68" s="116"/>
-      <c r="E68" s="153"/>
-      <c r="F68" s="116"/>
-      <c r="G68" s="116"/>
-      <c r="H68" s="116"/>
-      <c r="I68" s="116"/>
-      <c r="J68" s="116"/>
-      <c r="K68" s="116"/>
-      <c r="L68" s="116"/>
-      <c r="M68" s="116"/>
-      <c r="N68" s="153"/>
-      <c r="O68" s="153"/>
-      <c r="P68" s="153"/>
-      <c r="Q68" s="153"/>
-    </row>
-    <row r="69" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C68" s="119"/>
+      <c r="D68" s="119"/>
+      <c r="E68" s="129"/>
+      <c r="F68" s="119"/>
+      <c r="G68" s="119"/>
+      <c r="H68" s="119"/>
+      <c r="I68" s="119"/>
+      <c r="J68" s="119"/>
+      <c r="K68" s="119"/>
+      <c r="L68" s="119"/>
+      <c r="M68" s="119"/>
+      <c r="N68" s="129"/>
+      <c r="O68" s="129"/>
+      <c r="P68" s="129"/>
+      <c r="Q68" s="129"/>
+    </row>
+    <row r="69" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A69" s="24" t="str">
         <f>_xlfn.XLOOKUP(B69,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12280,23 +12280,23 @@
       <c r="B69" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C69" s="116"/>
-      <c r="D69" s="116"/>
-      <c r="E69" s="153"/>
-      <c r="F69" s="116"/>
-      <c r="G69" s="116"/>
-      <c r="H69" s="116"/>
-      <c r="I69" s="116"/>
-      <c r="J69" s="116"/>
-      <c r="K69" s="116"/>
-      <c r="L69" s="116"/>
-      <c r="M69" s="116"/>
-      <c r="N69" s="153"/>
-      <c r="O69" s="153"/>
-      <c r="P69" s="153"/>
-      <c r="Q69" s="153"/>
-    </row>
-    <row r="70" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C69" s="119"/>
+      <c r="D69" s="119"/>
+      <c r="E69" s="129"/>
+      <c r="F69" s="119"/>
+      <c r="G69" s="119"/>
+      <c r="H69" s="119"/>
+      <c r="I69" s="119"/>
+      <c r="J69" s="119"/>
+      <c r="K69" s="119"/>
+      <c r="L69" s="119"/>
+      <c r="M69" s="119"/>
+      <c r="N69" s="129"/>
+      <c r="O69" s="129"/>
+      <c r="P69" s="129"/>
+      <c r="Q69" s="129"/>
+    </row>
+    <row r="70" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="80" t="str">
         <f>_xlfn.XLOOKUP(B70,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12304,23 +12304,23 @@
       <c r="B70" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C70" s="136"/>
-      <c r="D70" s="136"/>
-      <c r="E70" s="156"/>
-      <c r="F70" s="136"/>
-      <c r="G70" s="136"/>
-      <c r="H70" s="136"/>
-      <c r="I70" s="136"/>
-      <c r="J70" s="136"/>
-      <c r="K70" s="136"/>
-      <c r="L70" s="136"/>
-      <c r="M70" s="136"/>
-      <c r="N70" s="154"/>
-      <c r="O70" s="154"/>
-      <c r="P70" s="154"/>
-      <c r="Q70" s="154"/>
-    </row>
-    <row r="71" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C70" s="120"/>
+      <c r="D70" s="120"/>
+      <c r="E70" s="132"/>
+      <c r="F70" s="120"/>
+      <c r="G70" s="120"/>
+      <c r="H70" s="120"/>
+      <c r="I70" s="120"/>
+      <c r="J70" s="120"/>
+      <c r="K70" s="120"/>
+      <c r="L70" s="120"/>
+      <c r="M70" s="120"/>
+      <c r="N70" s="130"/>
+      <c r="O70" s="130"/>
+      <c r="P70" s="130"/>
+      <c r="Q70" s="130"/>
+    </row>
+    <row r="71" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A71" s="24" t="str">
         <f>_xlfn.XLOOKUP(B71,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12328,52 +12328,52 @@
       <c r="B71" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C71" s="138">
+      <c r="C71" s="124">
         <v>5</v>
       </c>
-      <c r="D71" s="138" t="s">
+      <c r="D71" s="124" t="s">
         <v>260</v>
       </c>
-      <c r="E71" s="153" t="s">
+      <c r="E71" s="129" t="s">
         <v>261</v>
       </c>
-      <c r="F71" s="138" t="s">
+      <c r="F71" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G71" s="138"/>
-      <c r="H71" s="138" t="s">
+      <c r="G71" s="124"/>
+      <c r="H71" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I71" s="138"/>
-      <c r="J71" s="138">
+      <c r="I71" s="124"/>
+      <c r="J71" s="124">
         <v>3</v>
       </c>
-      <c r="K71" s="138">
+      <c r="K71" s="124">
         <f>J71*12</f>
         <v>36</v>
       </c>
-      <c r="L71" s="138">
+      <c r="L71" s="124">
         <f>36*J71</f>
         <v>108</v>
       </c>
-      <c r="M71" s="138">
+      <c r="M71" s="124">
         <f>SUM(K71:L71)</f>
         <v>144</v>
       </c>
-      <c r="N71" s="152" t="s">
+      <c r="N71" s="128" t="s">
         <v>262</v>
       </c>
-      <c r="O71" s="152" t="s">
+      <c r="O71" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="P71" s="152" t="s">
+      <c r="P71" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q71" s="152" t="s">
+      <c r="Q71" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="72" spans="1:19" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A72" s="24" t="str">
         <f>_xlfn.XLOOKUP(B72,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12381,23 +12381,23 @@
       <c r="B72" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C72" s="116"/>
-      <c r="D72" s="116"/>
-      <c r="E72" s="153"/>
-      <c r="F72" s="116"/>
-      <c r="G72" s="116"/>
-      <c r="H72" s="116"/>
-      <c r="I72" s="116"/>
-      <c r="J72" s="116"/>
-      <c r="K72" s="116"/>
-      <c r="L72" s="116"/>
-      <c r="M72" s="116"/>
-      <c r="N72" s="153"/>
-      <c r="O72" s="153"/>
-      <c r="P72" s="153"/>
-      <c r="Q72" s="153"/>
-    </row>
-    <row r="73" spans="1:19" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+      <c r="C72" s="119"/>
+      <c r="D72" s="119"/>
+      <c r="E72" s="129"/>
+      <c r="F72" s="119"/>
+      <c r="G72" s="119"/>
+      <c r="H72" s="119"/>
+      <c r="I72" s="119"/>
+      <c r="J72" s="119"/>
+      <c r="K72" s="119"/>
+      <c r="L72" s="119"/>
+      <c r="M72" s="119"/>
+      <c r="N72" s="129"/>
+      <c r="O72" s="129"/>
+      <c r="P72" s="129"/>
+      <c r="Q72" s="129"/>
+    </row>
+    <row r="73" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A73" s="24" t="str">
         <f>_xlfn.XLOOKUP(B73,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12405,23 +12405,23 @@
       <c r="B73" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C73" s="116"/>
-      <c r="D73" s="116"/>
-      <c r="E73" s="153"/>
-      <c r="F73" s="116"/>
-      <c r="G73" s="116"/>
-      <c r="H73" s="116"/>
-      <c r="I73" s="116"/>
-      <c r="J73" s="116"/>
-      <c r="K73" s="116"/>
-      <c r="L73" s="116"/>
-      <c r="M73" s="116"/>
-      <c r="N73" s="153"/>
-      <c r="O73" s="153"/>
-      <c r="P73" s="153"/>
-      <c r="Q73" s="153"/>
-    </row>
-    <row r="74" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C73" s="119"/>
+      <c r="D73" s="119"/>
+      <c r="E73" s="129"/>
+      <c r="F73" s="119"/>
+      <c r="G73" s="119"/>
+      <c r="H73" s="119"/>
+      <c r="I73" s="119"/>
+      <c r="J73" s="119"/>
+      <c r="K73" s="119"/>
+      <c r="L73" s="119"/>
+      <c r="M73" s="119"/>
+      <c r="N73" s="129"/>
+      <c r="O73" s="129"/>
+      <c r="P73" s="129"/>
+      <c r="Q73" s="129"/>
+    </row>
+    <row r="74" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A74" s="24" t="str">
         <f>_xlfn.XLOOKUP(B74,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12429,23 +12429,23 @@
       <c r="B74" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="116"/>
-      <c r="D74" s="116"/>
-      <c r="E74" s="153"/>
-      <c r="F74" s="116"/>
-      <c r="G74" s="116"/>
-      <c r="H74" s="116"/>
-      <c r="I74" s="116"/>
-      <c r="J74" s="116"/>
-      <c r="K74" s="116"/>
-      <c r="L74" s="116"/>
-      <c r="M74" s="116"/>
-      <c r="N74" s="153"/>
-      <c r="O74" s="153"/>
-      <c r="P74" s="153"/>
-      <c r="Q74" s="153"/>
-    </row>
-    <row r="75" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C74" s="119"/>
+      <c r="D74" s="119"/>
+      <c r="E74" s="129"/>
+      <c r="F74" s="119"/>
+      <c r="G74" s="119"/>
+      <c r="H74" s="119"/>
+      <c r="I74" s="119"/>
+      <c r="J74" s="119"/>
+      <c r="K74" s="119"/>
+      <c r="L74" s="119"/>
+      <c r="M74" s="119"/>
+      <c r="N74" s="129"/>
+      <c r="O74" s="129"/>
+      <c r="P74" s="129"/>
+      <c r="Q74" s="129"/>
+    </row>
+    <row r="75" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="80" t="str">
         <f>_xlfn.XLOOKUP(B75,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12453,23 +12453,23 @@
       <c r="B75" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C75" s="136"/>
-      <c r="D75" s="136"/>
-      <c r="E75" s="156"/>
-      <c r="F75" s="157"/>
-      <c r="G75" s="157"/>
-      <c r="H75" s="157"/>
-      <c r="I75" s="157"/>
-      <c r="J75" s="157"/>
-      <c r="K75" s="136"/>
-      <c r="L75" s="136"/>
-      <c r="M75" s="157"/>
-      <c r="N75" s="156"/>
-      <c r="O75" s="154"/>
-      <c r="P75" s="154"/>
-      <c r="Q75" s="154"/>
-    </row>
-    <row r="76" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C75" s="120"/>
+      <c r="D75" s="120"/>
+      <c r="E75" s="132"/>
+      <c r="F75" s="133"/>
+      <c r="G75" s="133"/>
+      <c r="H75" s="133"/>
+      <c r="I75" s="133"/>
+      <c r="J75" s="133"/>
+      <c r="K75" s="120"/>
+      <c r="L75" s="120"/>
+      <c r="M75" s="133"/>
+      <c r="N75" s="132"/>
+      <c r="O75" s="130"/>
+      <c r="P75" s="130"/>
+      <c r="Q75" s="130"/>
+    </row>
+    <row r="76" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A76" s="24" t="str">
         <f>_xlfn.XLOOKUP(B76,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12477,52 +12477,52 @@
       <c r="B76" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C76" s="138">
+      <c r="C76" s="124">
         <v>5</v>
       </c>
-      <c r="D76" s="138" t="s">
+      <c r="D76" s="124" t="s">
         <v>263</v>
       </c>
-      <c r="E76" s="153" t="s">
+      <c r="E76" s="129" t="s">
         <v>264</v>
       </c>
-      <c r="F76" s="116" t="s">
+      <c r="F76" s="119" t="s">
         <v>180</v>
       </c>
-      <c r="G76" s="116"/>
-      <c r="H76" s="116" t="s">
+      <c r="G76" s="119"/>
+      <c r="H76" s="119" t="s">
         <v>181</v>
       </c>
-      <c r="I76" s="116"/>
-      <c r="J76" s="116">
+      <c r="I76" s="119"/>
+      <c r="J76" s="119">
         <v>4</v>
       </c>
-      <c r="K76" s="147">
+      <c r="K76" s="117">
         <f>J76*12</f>
         <v>48</v>
       </c>
-      <c r="L76" s="147">
+      <c r="L76" s="117">
         <f>36*J76</f>
         <v>144</v>
       </c>
-      <c r="M76" s="116">
+      <c r="M76" s="119">
         <f>SUM(K76:L76)</f>
         <v>192</v>
       </c>
-      <c r="N76" s="153" t="s">
+      <c r="N76" s="129" t="s">
         <v>265</v>
       </c>
-      <c r="O76" s="152" t="s">
+      <c r="O76" s="128" t="s">
         <v>231</v>
       </c>
-      <c r="P76" s="152" t="s">
+      <c r="P76" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q76" s="152" t="s">
+      <c r="Q76" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="77" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A77" s="24" t="str">
         <f>_xlfn.XLOOKUP(B77,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12530,23 +12530,23 @@
       <c r="B77" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C77" s="116"/>
-      <c r="D77" s="116"/>
-      <c r="E77" s="153"/>
-      <c r="F77" s="116"/>
-      <c r="G77" s="116"/>
-      <c r="H77" s="116"/>
-      <c r="I77" s="116"/>
-      <c r="J77" s="116"/>
-      <c r="K77" s="147"/>
-      <c r="L77" s="147"/>
-      <c r="M77" s="116"/>
-      <c r="N77" s="153"/>
-      <c r="O77" s="153"/>
-      <c r="P77" s="153"/>
-      <c r="Q77" s="153"/>
-    </row>
-    <row r="78" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C77" s="119"/>
+      <c r="D77" s="119"/>
+      <c r="E77" s="129"/>
+      <c r="F77" s="119"/>
+      <c r="G77" s="119"/>
+      <c r="H77" s="119"/>
+      <c r="I77" s="119"/>
+      <c r="J77" s="119"/>
+      <c r="K77" s="117"/>
+      <c r="L77" s="117"/>
+      <c r="M77" s="119"/>
+      <c r="N77" s="129"/>
+      <c r="O77" s="129"/>
+      <c r="P77" s="129"/>
+      <c r="Q77" s="129"/>
+    </row>
+    <row r="78" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="80" t="str">
         <f>_xlfn.XLOOKUP(B78,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12554,21 +12554,21 @@
       <c r="B78" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C78" s="136"/>
-      <c r="D78" s="136"/>
-      <c r="E78" s="154"/>
-      <c r="F78" s="136"/>
-      <c r="G78" s="136"/>
-      <c r="H78" s="136"/>
-      <c r="I78" s="136"/>
-      <c r="J78" s="136"/>
-      <c r="K78" s="148"/>
-      <c r="L78" s="148"/>
-      <c r="M78" s="136"/>
-      <c r="N78" s="154"/>
-      <c r="O78" s="154"/>
-      <c r="P78" s="154"/>
-      <c r="Q78" s="154"/>
+      <c r="C78" s="120"/>
+      <c r="D78" s="120"/>
+      <c r="E78" s="130"/>
+      <c r="F78" s="120"/>
+      <c r="G78" s="120"/>
+      <c r="H78" s="120"/>
+      <c r="I78" s="120"/>
+      <c r="J78" s="120"/>
+      <c r="K78" s="118"/>
+      <c r="L78" s="118"/>
+      <c r="M78" s="120"/>
+      <c r="N78" s="130"/>
+      <c r="O78" s="130"/>
+      <c r="P78" s="130"/>
+      <c r="Q78" s="130"/>
       <c r="R78" s="50">
         <f>SUM(J56:J78)</f>
         <v>16</v>
@@ -12578,7 +12578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A79" s="24" t="str">
         <f>_xlfn.XLOOKUP(B79,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12586,52 +12586,52 @@
       <c r="B79" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C79" s="138">
+      <c r="C79" s="124">
         <v>6</v>
       </c>
-      <c r="D79" s="138" t="s">
+      <c r="D79" s="124" t="s">
         <v>266</v>
       </c>
-      <c r="E79" s="152" t="s">
+      <c r="E79" s="128" t="s">
         <v>267</v>
       </c>
-      <c r="F79" s="138" t="s">
+      <c r="F79" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G79" s="138"/>
-      <c r="H79" s="138" t="s">
+      <c r="G79" s="124"/>
+      <c r="H79" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I79" s="138"/>
-      <c r="J79" s="138">
+      <c r="I79" s="124"/>
+      <c r="J79" s="124">
         <v>3</v>
       </c>
-      <c r="K79" s="138">
+      <c r="K79" s="124">
         <f>J79*12</f>
         <v>36</v>
       </c>
-      <c r="L79" s="138">
+      <c r="L79" s="124">
         <f>36*J79</f>
         <v>108</v>
       </c>
-      <c r="M79" s="138">
+      <c r="M79" s="124">
         <f>SUM(K79:L79)</f>
         <v>144</v>
       </c>
-      <c r="N79" s="152" t="s">
+      <c r="N79" s="128" t="s">
         <v>268</v>
       </c>
-      <c r="O79" s="152" t="s">
+      <c r="O79" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="P79" s="152" t="s">
+      <c r="P79" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="Q79" s="152" t="s">
+      <c r="Q79" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="80" spans="1:19" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A80" s="24" t="str">
         <f>_xlfn.XLOOKUP(B80,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12639,23 +12639,23 @@
       <c r="B80" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C80" s="116"/>
-      <c r="D80" s="116"/>
-      <c r="E80" s="153"/>
-      <c r="F80" s="116"/>
-      <c r="G80" s="116"/>
-      <c r="H80" s="116"/>
-      <c r="I80" s="116"/>
-      <c r="J80" s="116"/>
-      <c r="K80" s="116"/>
-      <c r="L80" s="116"/>
-      <c r="M80" s="116"/>
-      <c r="N80" s="153"/>
-      <c r="O80" s="153"/>
-      <c r="P80" s="153"/>
-      <c r="Q80" s="153"/>
-    </row>
-    <row r="81" spans="1:17" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+      <c r="C80" s="119"/>
+      <c r="D80" s="119"/>
+      <c r="E80" s="129"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="119"/>
+      <c r="H80" s="119"/>
+      <c r="I80" s="119"/>
+      <c r="J80" s="119"/>
+      <c r="K80" s="119"/>
+      <c r="L80" s="119"/>
+      <c r="M80" s="119"/>
+      <c r="N80" s="129"/>
+      <c r="O80" s="129"/>
+      <c r="P80" s="129"/>
+      <c r="Q80" s="129"/>
+    </row>
+    <row r="81" spans="1:17" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A81" s="24" t="str">
         <f>_xlfn.XLOOKUP(B81,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12663,23 +12663,23 @@
       <c r="B81" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C81" s="116"/>
-      <c r="D81" s="116"/>
-      <c r="E81" s="153"/>
-      <c r="F81" s="116"/>
-      <c r="G81" s="116"/>
-      <c r="H81" s="116"/>
-      <c r="I81" s="116"/>
-      <c r="J81" s="116"/>
-      <c r="K81" s="116"/>
-      <c r="L81" s="116"/>
-      <c r="M81" s="116"/>
-      <c r="N81" s="153"/>
-      <c r="O81" s="153"/>
-      <c r="P81" s="153"/>
-      <c r="Q81" s="153"/>
-    </row>
-    <row r="82" spans="1:17" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C81" s="119"/>
+      <c r="D81" s="119"/>
+      <c r="E81" s="129"/>
+      <c r="F81" s="119"/>
+      <c r="G81" s="119"/>
+      <c r="H81" s="119"/>
+      <c r="I81" s="119"/>
+      <c r="J81" s="119"/>
+      <c r="K81" s="119"/>
+      <c r="L81" s="119"/>
+      <c r="M81" s="119"/>
+      <c r="N81" s="129"/>
+      <c r="O81" s="129"/>
+      <c r="P81" s="129"/>
+      <c r="Q81" s="129"/>
+    </row>
+    <row r="82" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A82" s="24" t="str">
         <f>_xlfn.XLOOKUP(B82,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12687,23 +12687,23 @@
       <c r="B82" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C82" s="116"/>
-      <c r="D82" s="116"/>
-      <c r="E82" s="153"/>
-      <c r="F82" s="116"/>
-      <c r="G82" s="116"/>
-      <c r="H82" s="116"/>
-      <c r="I82" s="116"/>
-      <c r="J82" s="116"/>
-      <c r="K82" s="116"/>
-      <c r="L82" s="116"/>
-      <c r="M82" s="116"/>
-      <c r="N82" s="153"/>
-      <c r="O82" s="153"/>
-      <c r="P82" s="153"/>
-      <c r="Q82" s="153"/>
-    </row>
-    <row r="83" spans="1:17" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C82" s="119"/>
+      <c r="D82" s="119"/>
+      <c r="E82" s="129"/>
+      <c r="F82" s="119"/>
+      <c r="G82" s="119"/>
+      <c r="H82" s="119"/>
+      <c r="I82" s="119"/>
+      <c r="J82" s="119"/>
+      <c r="K82" s="119"/>
+      <c r="L82" s="119"/>
+      <c r="M82" s="119"/>
+      <c r="N82" s="129"/>
+      <c r="O82" s="129"/>
+      <c r="P82" s="129"/>
+      <c r="Q82" s="129"/>
+    </row>
+    <row r="83" spans="1:17" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="80" t="str">
         <f>_xlfn.XLOOKUP(B83,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12711,23 +12711,23 @@
       <c r="B83" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C83" s="136"/>
-      <c r="D83" s="136"/>
-      <c r="E83" s="154"/>
-      <c r="F83" s="136"/>
-      <c r="G83" s="136"/>
-      <c r="H83" s="136"/>
-      <c r="I83" s="136"/>
-      <c r="J83" s="136"/>
-      <c r="K83" s="136"/>
-      <c r="L83" s="136"/>
-      <c r="M83" s="136"/>
-      <c r="N83" s="154"/>
-      <c r="O83" s="154"/>
-      <c r="P83" s="154"/>
-      <c r="Q83" s="154"/>
-    </row>
-    <row r="84" spans="1:17" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C83" s="120"/>
+      <c r="D83" s="120"/>
+      <c r="E83" s="130"/>
+      <c r="F83" s="120"/>
+      <c r="G83" s="120"/>
+      <c r="H83" s="120"/>
+      <c r="I83" s="120"/>
+      <c r="J83" s="120"/>
+      <c r="K83" s="120"/>
+      <c r="L83" s="120"/>
+      <c r="M83" s="120"/>
+      <c r="N83" s="130"/>
+      <c r="O83" s="130"/>
+      <c r="P83" s="130"/>
+      <c r="Q83" s="130"/>
+    </row>
+    <row r="84" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A84" s="24" t="str">
         <f>_xlfn.XLOOKUP(B84,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12735,52 +12735,52 @@
       <c r="B84" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C84" s="138">
+      <c r="C84" s="124">
         <v>6</v>
       </c>
-      <c r="D84" s="138" t="s">
+      <c r="D84" s="124" t="s">
         <v>269</v>
       </c>
-      <c r="E84" s="152" t="s">
+      <c r="E84" s="128" t="s">
         <v>270</v>
       </c>
-      <c r="F84" s="138" t="s">
+      <c r="F84" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G84" s="138"/>
-      <c r="H84" s="138" t="s">
+      <c r="G84" s="124"/>
+      <c r="H84" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I84" s="138"/>
-      <c r="J84" s="138">
+      <c r="I84" s="124"/>
+      <c r="J84" s="124">
         <v>3</v>
       </c>
-      <c r="K84" s="138">
+      <c r="K84" s="124">
         <f>J84*12</f>
         <v>36</v>
       </c>
-      <c r="L84" s="138">
+      <c r="L84" s="124">
         <f>36*J84</f>
         <v>108</v>
       </c>
-      <c r="M84" s="138">
+      <c r="M84" s="124">
         <f>SUM(K84:L84)</f>
         <v>144</v>
       </c>
-      <c r="N84" s="152" t="s">
+      <c r="N84" s="128" t="s">
         <v>271</v>
       </c>
-      <c r="O84" s="152" t="s">
+      <c r="O84" s="128" t="s">
         <v>183</v>
       </c>
-      <c r="P84" s="152" t="s">
+      <c r="P84" s="128" t="s">
         <v>184</v>
       </c>
-      <c r="Q84" s="152" t="s">
+      <c r="Q84" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A85" s="24" t="str">
         <f>_xlfn.XLOOKUP(B85,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12788,23 +12788,23 @@
       <c r="B85" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C85" s="116"/>
-      <c r="D85" s="116"/>
-      <c r="E85" s="153"/>
-      <c r="F85" s="116"/>
-      <c r="G85" s="116"/>
-      <c r="H85" s="116"/>
-      <c r="I85" s="116"/>
-      <c r="J85" s="116"/>
-      <c r="K85" s="116"/>
-      <c r="L85" s="116"/>
-      <c r="M85" s="116"/>
-      <c r="N85" s="153"/>
-      <c r="O85" s="153"/>
-      <c r="P85" s="153"/>
-      <c r="Q85" s="153"/>
-    </row>
-    <row r="86" spans="1:17" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+      <c r="C85" s="119"/>
+      <c r="D85" s="119"/>
+      <c r="E85" s="129"/>
+      <c r="F85" s="119"/>
+      <c r="G85" s="119"/>
+      <c r="H85" s="119"/>
+      <c r="I85" s="119"/>
+      <c r="J85" s="119"/>
+      <c r="K85" s="119"/>
+      <c r="L85" s="119"/>
+      <c r="M85" s="119"/>
+      <c r="N85" s="129"/>
+      <c r="O85" s="129"/>
+      <c r="P85" s="129"/>
+      <c r="Q85" s="129"/>
+    </row>
+    <row r="86" spans="1:17" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A86" s="24" t="str">
         <f>_xlfn.XLOOKUP(B86,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12812,23 +12812,23 @@
       <c r="B86" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C86" s="116"/>
-      <c r="D86" s="116"/>
-      <c r="E86" s="153"/>
-      <c r="F86" s="116"/>
-      <c r="G86" s="116"/>
-      <c r="H86" s="116"/>
-      <c r="I86" s="116"/>
-      <c r="J86" s="116"/>
-      <c r="K86" s="116"/>
-      <c r="L86" s="116"/>
-      <c r="M86" s="116"/>
-      <c r="N86" s="153"/>
-      <c r="O86" s="153"/>
-      <c r="P86" s="153"/>
-      <c r="Q86" s="153"/>
-    </row>
-    <row r="87" spans="1:17" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C86" s="119"/>
+      <c r="D86" s="119"/>
+      <c r="E86" s="129"/>
+      <c r="F86" s="119"/>
+      <c r="G86" s="119"/>
+      <c r="H86" s="119"/>
+      <c r="I86" s="119"/>
+      <c r="J86" s="119"/>
+      <c r="K86" s="119"/>
+      <c r="L86" s="119"/>
+      <c r="M86" s="119"/>
+      <c r="N86" s="129"/>
+      <c r="O86" s="129"/>
+      <c r="P86" s="129"/>
+      <c r="Q86" s="129"/>
+    </row>
+    <row r="87" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="str">
         <f>_xlfn.XLOOKUP(B87,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12836,23 +12836,23 @@
       <c r="B87" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C87" s="116"/>
-      <c r="D87" s="116"/>
-      <c r="E87" s="153"/>
-      <c r="F87" s="116"/>
-      <c r="G87" s="116"/>
-      <c r="H87" s="116"/>
-      <c r="I87" s="116"/>
-      <c r="J87" s="116"/>
-      <c r="K87" s="116"/>
-      <c r="L87" s="116"/>
-      <c r="M87" s="116"/>
-      <c r="N87" s="153"/>
-      <c r="O87" s="153"/>
-      <c r="P87" s="153"/>
-      <c r="Q87" s="153"/>
-    </row>
-    <row r="88" spans="1:17" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C87" s="119"/>
+      <c r="D87" s="119"/>
+      <c r="E87" s="129"/>
+      <c r="F87" s="119"/>
+      <c r="G87" s="119"/>
+      <c r="H87" s="119"/>
+      <c r="I87" s="119"/>
+      <c r="J87" s="119"/>
+      <c r="K87" s="119"/>
+      <c r="L87" s="119"/>
+      <c r="M87" s="119"/>
+      <c r="N87" s="129"/>
+      <c r="O87" s="129"/>
+      <c r="P87" s="129"/>
+      <c r="Q87" s="129"/>
+    </row>
+    <row r="88" spans="1:17" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="80" t="str">
         <f>_xlfn.XLOOKUP(B88,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12860,23 +12860,23 @@
       <c r="B88" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C88" s="136"/>
-      <c r="D88" s="136"/>
-      <c r="E88" s="154"/>
-      <c r="F88" s="136"/>
-      <c r="G88" s="136"/>
-      <c r="H88" s="136"/>
-      <c r="I88" s="136"/>
-      <c r="J88" s="136"/>
-      <c r="K88" s="136"/>
-      <c r="L88" s="136"/>
-      <c r="M88" s="136"/>
-      <c r="N88" s="154"/>
-      <c r="O88" s="154"/>
-      <c r="P88" s="154"/>
-      <c r="Q88" s="154"/>
-    </row>
-    <row r="89" spans="1:17" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C88" s="120"/>
+      <c r="D88" s="120"/>
+      <c r="E88" s="130"/>
+      <c r="F88" s="120"/>
+      <c r="G88" s="120"/>
+      <c r="H88" s="120"/>
+      <c r="I88" s="120"/>
+      <c r="J88" s="120"/>
+      <c r="K88" s="120"/>
+      <c r="L88" s="120"/>
+      <c r="M88" s="120"/>
+      <c r="N88" s="130"/>
+      <c r="O88" s="130"/>
+      <c r="P88" s="130"/>
+      <c r="Q88" s="130"/>
+    </row>
+    <row r="89" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A89" s="24" t="str">
         <f>_xlfn.XLOOKUP(B89,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12884,52 +12884,52 @@
       <c r="B89" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C89" s="138">
+      <c r="C89" s="124">
         <v>6</v>
       </c>
-      <c r="D89" s="138" t="s">
+      <c r="D89" s="124" t="s">
         <v>272</v>
       </c>
-      <c r="E89" s="152" t="s">
+      <c r="E89" s="128" t="s">
         <v>273</v>
       </c>
-      <c r="F89" s="138" t="s">
+      <c r="F89" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G89" s="138"/>
-      <c r="H89" s="138" t="s">
+      <c r="G89" s="124"/>
+      <c r="H89" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I89" s="138"/>
-      <c r="J89" s="138">
+      <c r="I89" s="124"/>
+      <c r="J89" s="124">
         <v>3</v>
       </c>
-      <c r="K89" s="138">
+      <c r="K89" s="124">
         <f>J89*12</f>
         <v>36</v>
       </c>
-      <c r="L89" s="138">
+      <c r="L89" s="124">
         <f>36*J89</f>
         <v>108</v>
       </c>
-      <c r="M89" s="138">
+      <c r="M89" s="124">
         <f>SUM(K89:L89)</f>
         <v>144</v>
       </c>
-      <c r="N89" s="152" t="s">
+      <c r="N89" s="128" t="s">
         <v>274</v>
       </c>
-      <c r="O89" s="152" t="s">
+      <c r="O89" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="P89" s="152" t="s">
+      <c r="P89" s="128" t="s">
         <v>184</v>
       </c>
-      <c r="Q89" s="152" t="s">
+      <c r="Q89" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A90" s="24" t="str">
         <f>_xlfn.XLOOKUP(B90,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12937,23 +12937,23 @@
       <c r="B90" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C90" s="116"/>
-      <c r="D90" s="116"/>
-      <c r="E90" s="153"/>
-      <c r="F90" s="116"/>
-      <c r="G90" s="116"/>
-      <c r="H90" s="116"/>
-      <c r="I90" s="116"/>
-      <c r="J90" s="116"/>
-      <c r="K90" s="116"/>
-      <c r="L90" s="116"/>
-      <c r="M90" s="116"/>
-      <c r="N90" s="153"/>
-      <c r="O90" s="153"/>
-      <c r="P90" s="153"/>
-      <c r="Q90" s="153"/>
-    </row>
-    <row r="91" spans="1:17" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+      <c r="C90" s="119"/>
+      <c r="D90" s="119"/>
+      <c r="E90" s="129"/>
+      <c r="F90" s="119"/>
+      <c r="G90" s="119"/>
+      <c r="H90" s="119"/>
+      <c r="I90" s="119"/>
+      <c r="J90" s="119"/>
+      <c r="K90" s="119"/>
+      <c r="L90" s="119"/>
+      <c r="M90" s="119"/>
+      <c r="N90" s="129"/>
+      <c r="O90" s="129"/>
+      <c r="P90" s="129"/>
+      <c r="Q90" s="129"/>
+    </row>
+    <row r="91" spans="1:17" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A91" s="24" t="str">
         <f>_xlfn.XLOOKUP(B91,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -12961,23 +12961,23 @@
       <c r="B91" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C91" s="116"/>
-      <c r="D91" s="116"/>
-      <c r="E91" s="153"/>
-      <c r="F91" s="116"/>
-      <c r="G91" s="116"/>
-      <c r="H91" s="116"/>
-      <c r="I91" s="116"/>
-      <c r="J91" s="116"/>
-      <c r="K91" s="116"/>
-      <c r="L91" s="116"/>
-      <c r="M91" s="116"/>
-      <c r="N91" s="153"/>
-      <c r="O91" s="153"/>
-      <c r="P91" s="153"/>
-      <c r="Q91" s="153"/>
-    </row>
-    <row r="92" spans="1:17" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C91" s="119"/>
+      <c r="D91" s="119"/>
+      <c r="E91" s="129"/>
+      <c r="F91" s="119"/>
+      <c r="G91" s="119"/>
+      <c r="H91" s="119"/>
+      <c r="I91" s="119"/>
+      <c r="J91" s="119"/>
+      <c r="K91" s="119"/>
+      <c r="L91" s="119"/>
+      <c r="M91" s="119"/>
+      <c r="N91" s="129"/>
+      <c r="O91" s="129"/>
+      <c r="P91" s="129"/>
+      <c r="Q91" s="129"/>
+    </row>
+    <row r="92" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A92" s="24" t="str">
         <f>_xlfn.XLOOKUP(B92,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -12985,23 +12985,23 @@
       <c r="B92" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C92" s="116"/>
-      <c r="D92" s="116"/>
-      <c r="E92" s="153"/>
-      <c r="F92" s="116"/>
-      <c r="G92" s="116"/>
-      <c r="H92" s="116"/>
-      <c r="I92" s="116"/>
-      <c r="J92" s="116"/>
-      <c r="K92" s="116"/>
-      <c r="L92" s="116"/>
-      <c r="M92" s="116"/>
-      <c r="N92" s="153"/>
-      <c r="O92" s="153"/>
-      <c r="P92" s="153"/>
-      <c r="Q92" s="153"/>
-    </row>
-    <row r="93" spans="1:17" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C92" s="119"/>
+      <c r="D92" s="119"/>
+      <c r="E92" s="129"/>
+      <c r="F92" s="119"/>
+      <c r="G92" s="119"/>
+      <c r="H92" s="119"/>
+      <c r="I92" s="119"/>
+      <c r="J92" s="119"/>
+      <c r="K92" s="119"/>
+      <c r="L92" s="119"/>
+      <c r="M92" s="119"/>
+      <c r="N92" s="129"/>
+      <c r="O92" s="129"/>
+      <c r="P92" s="129"/>
+      <c r="Q92" s="129"/>
+    </row>
+    <row r="93" spans="1:17" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="80" t="str">
         <f>_xlfn.XLOOKUP(B93,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13009,23 +13009,23 @@
       <c r="B93" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C93" s="136"/>
-      <c r="D93" s="136"/>
-      <c r="E93" s="154"/>
-      <c r="F93" s="136"/>
-      <c r="G93" s="136"/>
-      <c r="H93" s="136"/>
-      <c r="I93" s="136"/>
-      <c r="J93" s="136"/>
-      <c r="K93" s="136"/>
-      <c r="L93" s="136"/>
-      <c r="M93" s="136"/>
-      <c r="N93" s="154"/>
-      <c r="O93" s="154"/>
-      <c r="P93" s="154"/>
-      <c r="Q93" s="154"/>
-    </row>
-    <row r="94" spans="1:17" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C93" s="120"/>
+      <c r="D93" s="120"/>
+      <c r="E93" s="130"/>
+      <c r="F93" s="120"/>
+      <c r="G93" s="120"/>
+      <c r="H93" s="120"/>
+      <c r="I93" s="120"/>
+      <c r="J93" s="120"/>
+      <c r="K93" s="120"/>
+      <c r="L93" s="120"/>
+      <c r="M93" s="120"/>
+      <c r="N93" s="130"/>
+      <c r="O93" s="130"/>
+      <c r="P93" s="130"/>
+      <c r="Q93" s="130"/>
+    </row>
+    <row r="94" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A94" s="24" t="str">
         <f>_xlfn.XLOOKUP(B94,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13033,52 +13033,52 @@
       <c r="B94" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="138">
+      <c r="C94" s="124">
         <v>6</v>
       </c>
-      <c r="D94" s="138" t="s">
+      <c r="D94" s="124" t="s">
         <v>275</v>
       </c>
-      <c r="E94" s="152" t="s">
+      <c r="E94" s="128" t="s">
         <v>276</v>
       </c>
-      <c r="F94" s="138" t="s">
+      <c r="F94" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G94" s="138"/>
-      <c r="H94" s="138" t="s">
+      <c r="G94" s="124"/>
+      <c r="H94" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I94" s="138"/>
-      <c r="J94" s="138">
+      <c r="I94" s="124"/>
+      <c r="J94" s="124">
         <v>4</v>
       </c>
-      <c r="K94" s="138">
+      <c r="K94" s="124">
         <f>J94*12</f>
         <v>48</v>
       </c>
-      <c r="L94" s="138">
+      <c r="L94" s="124">
         <f>36*J94</f>
         <v>144</v>
       </c>
-      <c r="M94" s="138">
+      <c r="M94" s="124">
         <f>SUM(K94:L94)</f>
         <v>192</v>
       </c>
-      <c r="N94" s="152" t="s">
+      <c r="N94" s="128" t="s">
         <v>277</v>
       </c>
-      <c r="O94" s="152" t="s">
+      <c r="O94" s="128" t="s">
         <v>183</v>
       </c>
-      <c r="P94" s="152" t="s">
+      <c r="P94" s="128" t="s">
         <v>184</v>
       </c>
-      <c r="Q94" s="152" t="s">
+      <c r="Q94" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A95" s="24" t="str">
         <f>_xlfn.XLOOKUP(B95,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13086,23 +13086,23 @@
       <c r="B95" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C95" s="116"/>
-      <c r="D95" s="116"/>
-      <c r="E95" s="153"/>
-      <c r="F95" s="116"/>
-      <c r="G95" s="116"/>
-      <c r="H95" s="116"/>
-      <c r="I95" s="116"/>
-      <c r="J95" s="116"/>
-      <c r="K95" s="116"/>
-      <c r="L95" s="116"/>
-      <c r="M95" s="116"/>
-      <c r="N95" s="153"/>
-      <c r="O95" s="153"/>
-      <c r="P95" s="153"/>
-      <c r="Q95" s="153"/>
-    </row>
-    <row r="96" spans="1:17" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+      <c r="C95" s="119"/>
+      <c r="D95" s="119"/>
+      <c r="E95" s="129"/>
+      <c r="F95" s="119"/>
+      <c r="G95" s="119"/>
+      <c r="H95" s="119"/>
+      <c r="I95" s="119"/>
+      <c r="J95" s="119"/>
+      <c r="K95" s="119"/>
+      <c r="L95" s="119"/>
+      <c r="M95" s="119"/>
+      <c r="N95" s="129"/>
+      <c r="O95" s="129"/>
+      <c r="P95" s="129"/>
+      <c r="Q95" s="129"/>
+    </row>
+    <row r="96" spans="1:17" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A96" s="24" t="str">
         <f>_xlfn.XLOOKUP(B96,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13110,23 +13110,23 @@
       <c r="B96" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="116"/>
-      <c r="D96" s="116"/>
-      <c r="E96" s="153"/>
-      <c r="F96" s="116"/>
-      <c r="G96" s="116"/>
-      <c r="H96" s="116"/>
-      <c r="I96" s="116"/>
-      <c r="J96" s="116"/>
-      <c r="K96" s="116"/>
-      <c r="L96" s="116"/>
-      <c r="M96" s="116"/>
-      <c r="N96" s="153"/>
-      <c r="O96" s="153"/>
-      <c r="P96" s="153"/>
-      <c r="Q96" s="153"/>
-    </row>
-    <row r="97" spans="1:19" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+      <c r="C96" s="119"/>
+      <c r="D96" s="119"/>
+      <c r="E96" s="129"/>
+      <c r="F96" s="119"/>
+      <c r="G96" s="119"/>
+      <c r="H96" s="119"/>
+      <c r="I96" s="119"/>
+      <c r="J96" s="119"/>
+      <c r="K96" s="119"/>
+      <c r="L96" s="119"/>
+      <c r="M96" s="119"/>
+      <c r="N96" s="129"/>
+      <c r="O96" s="129"/>
+      <c r="P96" s="129"/>
+      <c r="Q96" s="129"/>
+    </row>
+    <row r="97" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A97" s="24" t="str">
         <f>_xlfn.XLOOKUP(B97,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13134,23 +13134,23 @@
       <c r="B97" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="116"/>
-      <c r="D97" s="116"/>
-      <c r="E97" s="153"/>
-      <c r="F97" s="116"/>
-      <c r="G97" s="116"/>
-      <c r="H97" s="116"/>
-      <c r="I97" s="116"/>
-      <c r="J97" s="116"/>
-      <c r="K97" s="116"/>
-      <c r="L97" s="116"/>
-      <c r="M97" s="116"/>
-      <c r="N97" s="153"/>
-      <c r="O97" s="153"/>
-      <c r="P97" s="153"/>
-      <c r="Q97" s="153"/>
-    </row>
-    <row r="98" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C97" s="119"/>
+      <c r="D97" s="119"/>
+      <c r="E97" s="129"/>
+      <c r="F97" s="119"/>
+      <c r="G97" s="119"/>
+      <c r="H97" s="119"/>
+      <c r="I97" s="119"/>
+      <c r="J97" s="119"/>
+      <c r="K97" s="119"/>
+      <c r="L97" s="119"/>
+      <c r="M97" s="119"/>
+      <c r="N97" s="129"/>
+      <c r="O97" s="129"/>
+      <c r="P97" s="129"/>
+      <c r="Q97" s="129"/>
+    </row>
+    <row r="98" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="80" t="str">
         <f>_xlfn.XLOOKUP(B98,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13158,23 +13158,23 @@
       <c r="B98" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C98" s="136"/>
-      <c r="D98" s="136"/>
-      <c r="E98" s="154"/>
-      <c r="F98" s="136"/>
-      <c r="G98" s="136"/>
-      <c r="H98" s="136"/>
-      <c r="I98" s="136"/>
-      <c r="J98" s="136"/>
-      <c r="K98" s="136"/>
-      <c r="L98" s="136"/>
-      <c r="M98" s="136"/>
-      <c r="N98" s="154"/>
-      <c r="O98" s="154"/>
-      <c r="P98" s="154"/>
-      <c r="Q98" s="154"/>
-    </row>
-    <row r="99" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C98" s="120"/>
+      <c r="D98" s="120"/>
+      <c r="E98" s="130"/>
+      <c r="F98" s="120"/>
+      <c r="G98" s="120"/>
+      <c r="H98" s="120"/>
+      <c r="I98" s="120"/>
+      <c r="J98" s="120"/>
+      <c r="K98" s="120"/>
+      <c r="L98" s="120"/>
+      <c r="M98" s="120"/>
+      <c r="N98" s="130"/>
+      <c r="O98" s="130"/>
+      <c r="P98" s="130"/>
+      <c r="Q98" s="130"/>
+    </row>
+    <row r="99" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A99" s="24" t="str">
         <f>_xlfn.XLOOKUP(B99,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13182,52 +13182,52 @@
       <c r="B99" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C99" s="138">
+      <c r="C99" s="124">
         <v>6</v>
       </c>
-      <c r="D99" s="138" t="s">
+      <c r="D99" s="124" t="s">
         <v>278</v>
       </c>
-      <c r="E99" s="152" t="s">
+      <c r="E99" s="128" t="s">
         <v>279</v>
       </c>
-      <c r="F99" s="138" t="s">
+      <c r="F99" s="124" t="s">
         <v>180</v>
       </c>
-      <c r="G99" s="138"/>
-      <c r="H99" s="138" t="s">
+      <c r="G99" s="124"/>
+      <c r="H99" s="124" t="s">
         <v>181</v>
       </c>
-      <c r="I99" s="138"/>
-      <c r="J99" s="138">
+      <c r="I99" s="124"/>
+      <c r="J99" s="124">
         <v>3</v>
       </c>
-      <c r="K99" s="138">
+      <c r="K99" s="124">
         <f>J99*12</f>
         <v>36</v>
       </c>
-      <c r="L99" s="138">
+      <c r="L99" s="124">
         <f>36*J99</f>
         <v>108</v>
       </c>
-      <c r="M99" s="138">
+      <c r="M99" s="124">
         <f>SUM(K99:L99)</f>
         <v>144</v>
       </c>
-      <c r="N99" s="152" t="s">
+      <c r="N99" s="128" t="s">
         <v>280</v>
       </c>
-      <c r="O99" s="152" t="s">
+      <c r="O99" s="128" t="s">
         <v>183</v>
       </c>
-      <c r="P99" s="152" t="s">
+      <c r="P99" s="128" t="s">
         <v>184</v>
       </c>
-      <c r="Q99" s="152" t="s">
+      <c r="Q99" s="128" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="100" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A100" s="24" t="str">
         <f>_xlfn.XLOOKUP(B100,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13235,23 +13235,23 @@
       <c r="B100" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C100" s="116"/>
-      <c r="D100" s="116"/>
-      <c r="E100" s="153"/>
-      <c r="F100" s="116"/>
-      <c r="G100" s="116"/>
-      <c r="H100" s="116"/>
-      <c r="I100" s="116"/>
-      <c r="J100" s="116"/>
-      <c r="K100" s="116"/>
-      <c r="L100" s="116"/>
-      <c r="M100" s="116"/>
-      <c r="N100" s="153"/>
-      <c r="O100" s="153"/>
-      <c r="P100" s="153"/>
-      <c r="Q100" s="153"/>
-    </row>
-    <row r="101" spans="1:19" s="50" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
+      <c r="C100" s="119"/>
+      <c r="D100" s="119"/>
+      <c r="E100" s="129"/>
+      <c r="F100" s="119"/>
+      <c r="G100" s="119"/>
+      <c r="H100" s="119"/>
+      <c r="I100" s="119"/>
+      <c r="J100" s="119"/>
+      <c r="K100" s="119"/>
+      <c r="L100" s="119"/>
+      <c r="M100" s="119"/>
+      <c r="N100" s="129"/>
+      <c r="O100" s="129"/>
+      <c r="P100" s="129"/>
+      <c r="Q100" s="129"/>
+    </row>
+    <row r="101" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A101" s="24" t="str">
         <f>_xlfn.XLOOKUP(B101,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13259,23 +13259,23 @@
       <c r="B101" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C101" s="116"/>
-      <c r="D101" s="116"/>
-      <c r="E101" s="153"/>
-      <c r="F101" s="116"/>
-      <c r="G101" s="116"/>
-      <c r="H101" s="116"/>
-      <c r="I101" s="116"/>
-      <c r="J101" s="116"/>
-      <c r="K101" s="116"/>
-      <c r="L101" s="116"/>
-      <c r="M101" s="116"/>
-      <c r="N101" s="153"/>
-      <c r="O101" s="153"/>
-      <c r="P101" s="153"/>
-      <c r="Q101" s="153"/>
-    </row>
-    <row r="102" spans="1:19" s="50" customFormat="1" ht="66" x14ac:dyDescent="0.35">
+      <c r="C101" s="119"/>
+      <c r="D101" s="119"/>
+      <c r="E101" s="129"/>
+      <c r="F101" s="119"/>
+      <c r="G101" s="119"/>
+      <c r="H101" s="119"/>
+      <c r="I101" s="119"/>
+      <c r="J101" s="119"/>
+      <c r="K101" s="119"/>
+      <c r="L101" s="119"/>
+      <c r="M101" s="119"/>
+      <c r="N101" s="129"/>
+      <c r="O101" s="129"/>
+      <c r="P101" s="129"/>
+      <c r="Q101" s="129"/>
+    </row>
+    <row r="102" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A102" s="24" t="str">
         <f>_xlfn.XLOOKUP(B102,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberhacer</v>
@@ -13283,23 +13283,23 @@
       <c r="B102" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C102" s="116"/>
-      <c r="D102" s="116"/>
-      <c r="E102" s="153"/>
-      <c r="F102" s="116"/>
-      <c r="G102" s="116"/>
-      <c r="H102" s="116"/>
-      <c r="I102" s="116"/>
-      <c r="J102" s="116"/>
-      <c r="K102" s="116"/>
-      <c r="L102" s="116"/>
-      <c r="M102" s="116"/>
-      <c r="N102" s="153"/>
-      <c r="O102" s="153"/>
-      <c r="P102" s="153"/>
-      <c r="Q102" s="153"/>
-    </row>
-    <row r="103" spans="1:19" s="50" customFormat="1" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="C102" s="119"/>
+      <c r="D102" s="119"/>
+      <c r="E102" s="129"/>
+      <c r="F102" s="119"/>
+      <c r="G102" s="119"/>
+      <c r="H102" s="119"/>
+      <c r="I102" s="119"/>
+      <c r="J102" s="119"/>
+      <c r="K102" s="119"/>
+      <c r="L102" s="119"/>
+      <c r="M102" s="119"/>
+      <c r="N102" s="129"/>
+      <c r="O102" s="129"/>
+      <c r="P102" s="129"/>
+      <c r="Q102" s="129"/>
+    </row>
+    <row r="103" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="str">
         <f>_xlfn.XLOOKUP(B103,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saberser</v>
@@ -13307,23 +13307,23 @@
       <c r="B103" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C103" s="116"/>
-      <c r="D103" s="116"/>
-      <c r="E103" s="153"/>
-      <c r="F103" s="116"/>
-      <c r="G103" s="116"/>
-      <c r="H103" s="116"/>
-      <c r="I103" s="116"/>
-      <c r="J103" s="116"/>
-      <c r="K103" s="116"/>
-      <c r="L103" s="116"/>
-      <c r="M103" s="116"/>
-      <c r="N103" s="153"/>
-      <c r="O103" s="153"/>
-      <c r="P103" s="153"/>
-      <c r="Q103" s="153"/>
-    </row>
-    <row r="104" spans="1:19" s="50" customFormat="1" ht="50" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C103" s="119"/>
+      <c r="D103" s="119"/>
+      <c r="E103" s="129"/>
+      <c r="F103" s="119"/>
+      <c r="G103" s="119"/>
+      <c r="H103" s="119"/>
+      <c r="I103" s="119"/>
+      <c r="J103" s="119"/>
+      <c r="K103" s="119"/>
+      <c r="L103" s="119"/>
+      <c r="M103" s="119"/>
+      <c r="N103" s="129"/>
+      <c r="O103" s="129"/>
+      <c r="P103" s="129"/>
+      <c r="Q103" s="129"/>
+    </row>
+    <row r="104" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="112" t="str">
         <f>_xlfn.XLOOKUP(B104,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13331,21 +13331,21 @@
       <c r="B104" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="136"/>
-      <c r="D104" s="136"/>
-      <c r="E104" s="154"/>
-      <c r="F104" s="136"/>
-      <c r="G104" s="136"/>
-      <c r="H104" s="136"/>
-      <c r="I104" s="136"/>
-      <c r="J104" s="136"/>
-      <c r="K104" s="136"/>
-      <c r="L104" s="136"/>
-      <c r="M104" s="136"/>
-      <c r="N104" s="154"/>
-      <c r="O104" s="154"/>
-      <c r="P104" s="154"/>
-      <c r="Q104" s="154"/>
+      <c r="C104" s="120"/>
+      <c r="D104" s="120"/>
+      <c r="E104" s="130"/>
+      <c r="F104" s="120"/>
+      <c r="G104" s="120"/>
+      <c r="H104" s="120"/>
+      <c r="I104" s="120"/>
+      <c r="J104" s="120"/>
+      <c r="K104" s="120"/>
+      <c r="L104" s="120"/>
+      <c r="M104" s="120"/>
+      <c r="N104" s="130"/>
+      <c r="O104" s="130"/>
+      <c r="P104" s="130"/>
+      <c r="Q104" s="130"/>
       <c r="R104" s="50">
         <f>SUM(J79:J104)</f>
         <v>16</v>
@@ -13355,7 +13355,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:19" s="50" customFormat="1" ht="39" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A105" s="24"/>
       <c r="B105" s="16"/>
       <c r="C105" s="111" t="s">
@@ -13395,7 +13395,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:19" s="50" customFormat="1" ht="39" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A106" s="24"/>
       <c r="B106" s="16"/>
       <c r="D106" s="19"/>
@@ -13421,7 +13421,7 @@
       <c r="P106" s="16"/>
       <c r="Q106" s="16"/>
     </row>
-    <row r="107" spans="1:19" s="50" customFormat="1" ht="39" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A107" s="24"/>
       <c r="B107" s="16"/>
       <c r="D107" s="32"/>
@@ -13447,7 +13447,7 @@
       <c r="P107" s="68"/>
       <c r="Q107" s="68"/>
     </row>
-    <row r="108" spans="1:19" s="50" customFormat="1" ht="39" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:19" s="50" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A108" s="24"/>
       <c r="B108" s="16"/>
       <c r="D108" s="32"/>
@@ -13472,7 +13472,7 @@
       <c r="P108" s="68"/>
       <c r="Q108" s="68"/>
     </row>
-    <row r="109" spans="1:19" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:19" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A109" s="24"/>
       <c r="B109" s="16"/>
       <c r="D109" s="32"/>
@@ -13490,7 +13490,7 @@
       <c r="P109" s="68"/>
       <c r="Q109" s="68"/>
     </row>
-    <row r="110" spans="1:19" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:19" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A110" s="24"/>
       <c r="B110" s="16"/>
       <c r="D110" s="32"/>
@@ -13508,7 +13508,7 @@
       <c r="P110" s="68"/>
       <c r="Q110" s="68"/>
     </row>
-    <row r="111" spans="1:19" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:19" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A111" s="24"/>
       <c r="B111" s="16"/>
       <c r="D111" s="19"/>
@@ -13526,7 +13526,7 @@
       <c r="P111" s="16"/>
       <c r="Q111" s="16"/>
     </row>
-    <row r="112" spans="1:19" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:19" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A112" s="24"/>
       <c r="B112" s="16"/>
       <c r="D112" s="19"/>
@@ -13544,7 +13544,7 @@
       <c r="P112" s="16"/>
       <c r="Q112" s="16"/>
     </row>
-    <row r="113" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A113" s="24"/>
       <c r="B113" s="16"/>
       <c r="D113" s="19"/>
@@ -13562,7 +13562,7 @@
       <c r="P113" s="16"/>
       <c r="Q113" s="16"/>
     </row>
-    <row r="114" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A114" s="24"/>
       <c r="B114" s="16"/>
       <c r="D114" s="19"/>
@@ -13580,7 +13580,7 @@
       <c r="P114" s="16"/>
       <c r="Q114" s="16"/>
     </row>
-    <row r="115" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A115" s="24"/>
       <c r="B115" s="16"/>
       <c r="D115" s="19"/>
@@ -13598,7 +13598,7 @@
       <c r="P115" s="16"/>
       <c r="Q115" s="16"/>
     </row>
-    <row r="116" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A116" s="24"/>
       <c r="B116" s="16"/>
       <c r="D116" s="19"/>
@@ -13616,7 +13616,7 @@
       <c r="P116" s="16"/>
       <c r="Q116" s="16"/>
     </row>
-    <row r="117" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A117" s="24"/>
       <c r="B117" s="16"/>
       <c r="D117" s="19"/>
@@ -13634,7 +13634,7 @@
       <c r="P117" s="16"/>
       <c r="Q117" s="16"/>
     </row>
-    <row r="118" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A118" s="24"/>
       <c r="B118" s="16"/>
       <c r="D118" s="19"/>
@@ -13652,7 +13652,7 @@
       <c r="P118" s="16"/>
       <c r="Q118" s="16"/>
     </row>
-    <row r="119" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A119" s="24"/>
       <c r="B119" s="16"/>
       <c r="D119" s="19"/>
@@ -13670,7 +13670,7 @@
       <c r="P119" s="16"/>
       <c r="Q119" s="16"/>
     </row>
-    <row r="120" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A120" s="24"/>
       <c r="B120" s="16"/>
       <c r="D120" s="19"/>
@@ -13688,7 +13688,7 @@
       <c r="P120" s="16"/>
       <c r="Q120" s="16"/>
     </row>
-    <row r="121" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A121" s="24"/>
       <c r="B121" s="22"/>
       <c r="D121" s="19"/>
@@ -13706,7 +13706,7 @@
       <c r="P121" s="22"/>
       <c r="Q121" s="22"/>
     </row>
-    <row r="122" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A122" s="24"/>
       <c r="B122" s="22"/>
       <c r="D122" s="19"/>
@@ -13724,7 +13724,7 @@
       <c r="P122" s="22"/>
       <c r="Q122" s="22"/>
     </row>
-    <row r="123" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A123" s="24"/>
       <c r="B123" s="22"/>
       <c r="D123" s="19"/>
@@ -13742,7 +13742,7 @@
       <c r="P123" s="22"/>
       <c r="Q123" s="22"/>
     </row>
-    <row r="124" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A124" s="24"/>
       <c r="B124" s="22"/>
       <c r="D124" s="19"/>
@@ -13760,7 +13760,7 @@
       <c r="P124" s="22"/>
       <c r="Q124" s="22"/>
     </row>
-    <row r="125" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A125" s="24"/>
       <c r="B125" s="16"/>
       <c r="D125" s="32"/>
@@ -13778,7 +13778,7 @@
       <c r="P125" s="68"/>
       <c r="Q125" s="68"/>
     </row>
-    <row r="126" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A126" s="24"/>
       <c r="B126" s="16"/>
       <c r="D126" s="32"/>
@@ -13796,7 +13796,7 @@
       <c r="P126" s="68"/>
       <c r="Q126" s="68"/>
     </row>
-    <row r="127" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A127" s="24"/>
       <c r="B127" s="16"/>
       <c r="D127" s="32"/>
@@ -13814,7 +13814,7 @@
       <c r="P127" s="68"/>
       <c r="Q127" s="68"/>
     </row>
-    <row r="128" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A128" s="24"/>
       <c r="B128" s="16"/>
       <c r="D128" s="32"/>
@@ -13832,7 +13832,7 @@
       <c r="P128" s="68"/>
       <c r="Q128" s="68"/>
     </row>
-    <row r="129" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A129" s="24"/>
       <c r="B129" s="16"/>
       <c r="D129" s="19"/>
@@ -13845,7 +13845,7 @@
       <c r="P129" s="16"/>
       <c r="Q129" s="16"/>
     </row>
-    <row r="130" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A130" s="24"/>
       <c r="B130" s="16"/>
       <c r="D130" s="19"/>
@@ -13858,7 +13858,7 @@
       <c r="P130" s="16"/>
       <c r="Q130" s="16"/>
     </row>
-    <row r="131" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A131" s="24"/>
       <c r="B131" s="16"/>
       <c r="D131" s="19"/>
@@ -13871,7 +13871,7 @@
       <c r="P131" s="16"/>
       <c r="Q131" s="16"/>
     </row>
-    <row r="132" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A132" s="24"/>
       <c r="B132" s="16"/>
       <c r="D132" s="19"/>
@@ -13884,7 +13884,7 @@
       <c r="P132" s="16"/>
       <c r="Q132" s="16"/>
     </row>
-    <row r="133" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A133" s="24"/>
       <c r="B133" s="16"/>
       <c r="D133" s="19"/>
@@ -13902,7 +13902,7 @@
       <c r="P133" s="69"/>
       <c r="Q133" s="69"/>
     </row>
-    <row r="134" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A134" s="24"/>
       <c r="B134" s="16"/>
       <c r="D134" s="32"/>
@@ -13920,7 +13920,7 @@
       <c r="P134" s="68"/>
       <c r="Q134" s="68"/>
     </row>
-    <row r="135" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A135" s="24"/>
       <c r="B135" s="16"/>
       <c r="D135" s="32"/>
@@ -13938,7 +13938,7 @@
       <c r="P135" s="68"/>
       <c r="Q135" s="68"/>
     </row>
-    <row r="136" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A136" s="24"/>
       <c r="B136" s="16"/>
       <c r="D136" s="32"/>
@@ -13956,7 +13956,7 @@
       <c r="P136" s="68"/>
       <c r="Q136" s="68"/>
     </row>
-    <row r="137" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A137" s="24"/>
       <c r="B137" s="16"/>
       <c r="D137" s="32"/>
@@ -13974,7 +13974,7 @@
       <c r="P137" s="68"/>
       <c r="Q137" s="68"/>
     </row>
-    <row r="138" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A138" s="24"/>
       <c r="B138" s="16"/>
       <c r="D138" s="19"/>
@@ -13992,7 +13992,7 @@
       <c r="P138" s="68"/>
       <c r="Q138" s="68"/>
     </row>
-    <row r="139" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A139" s="24"/>
       <c r="B139" s="16"/>
       <c r="D139" s="19"/>
@@ -14010,7 +14010,7 @@
       <c r="P139" s="68"/>
       <c r="Q139" s="68"/>
     </row>
-    <row r="140" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A140" s="24"/>
       <c r="B140" s="16"/>
       <c r="D140" s="19"/>
@@ -14028,7 +14028,7 @@
       <c r="P140" s="68"/>
       <c r="Q140" s="68"/>
     </row>
-    <row r="141" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A141" s="24"/>
       <c r="B141" s="16"/>
       <c r="D141" s="19"/>
@@ -14046,7 +14046,7 @@
       <c r="P141" s="68"/>
       <c r="Q141" s="68"/>
     </row>
-    <row r="142" spans="1:17" s="50" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" s="50" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A142" s="24"/>
       <c r="B142" s="16"/>
       <c r="D142" s="19"/>
@@ -14059,7 +14059,7 @@
       <c r="P142" s="16"/>
       <c r="Q142" s="16"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E143" s="57"/>
       <c r="F143" s="52"/>
       <c r="L143" s="58"/>
@@ -14069,7 +14069,7 @@
       <c r="P143" s="57"/>
       <c r="Q143" s="57"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E144" s="57"/>
       <c r="F144" s="52"/>
       <c r="L144" s="58"/>
@@ -14079,7 +14079,7 @@
       <c r="P144" s="57"/>
       <c r="Q144" s="57"/>
     </row>
-    <row r="145" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="145" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E145" s="57"/>
       <c r="F145" s="52"/>
       <c r="L145" s="58"/>
@@ -14089,7 +14089,7 @@
       <c r="P145" s="57"/>
       <c r="Q145" s="57"/>
     </row>
-    <row r="146" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="146" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E146" s="60"/>
       <c r="F146" s="52"/>
       <c r="G146" s="54"/>
@@ -14104,7 +14104,7 @@
       <c r="P146" s="60"/>
       <c r="Q146" s="60"/>
     </row>
-    <row r="147" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="147" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E147" s="57"/>
       <c r="F147" s="52"/>
       <c r="G147" s="52"/>
@@ -14119,7 +14119,7 @@
       <c r="P147" s="57"/>
       <c r="Q147" s="57"/>
     </row>
-    <row r="148" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="148" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E148" s="53"/>
       <c r="F148" s="52"/>
       <c r="G148" s="54"/>
@@ -14134,7 +14134,7 @@
       <c r="P148" s="64"/>
       <c r="Q148" s="64"/>
     </row>
-    <row r="149" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="149" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E149" s="53"/>
       <c r="F149" s="52"/>
       <c r="G149" s="54"/>
@@ -14149,7 +14149,7 @@
       <c r="P149" s="64"/>
       <c r="Q149" s="64"/>
     </row>
-    <row r="150" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="150" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E150" s="53"/>
       <c r="F150" s="52"/>
       <c r="G150" s="54"/>
@@ -14164,7 +14164,7 @@
       <c r="P150" s="64"/>
       <c r="Q150" s="64"/>
     </row>
-    <row r="151" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="151" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E151" s="53"/>
       <c r="F151" s="52"/>
       <c r="G151" s="54"/>
@@ -14179,7 +14179,7 @@
       <c r="P151" s="64"/>
       <c r="Q151" s="64"/>
     </row>
-    <row r="152" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="152" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E152" s="57"/>
       <c r="F152" s="52"/>
       <c r="G152" s="58"/>
@@ -14194,7 +14194,7 @@
       <c r="P152" s="57"/>
       <c r="Q152" s="57"/>
     </row>
-    <row r="153" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="153" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E153" s="57"/>
       <c r="F153" s="52"/>
       <c r="G153" s="58"/>
@@ -14209,7 +14209,7 @@
       <c r="P153" s="57"/>
       <c r="Q153" s="57"/>
     </row>
-    <row r="154" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="154" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E154" s="57"/>
       <c r="F154" s="52"/>
       <c r="G154" s="58"/>
@@ -14224,7 +14224,7 @@
       <c r="P154" s="57"/>
       <c r="Q154" s="57"/>
     </row>
-    <row r="155" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="155" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E155" s="57"/>
       <c r="F155" s="52"/>
       <c r="G155" s="58"/>
@@ -14239,7 +14239,7 @@
       <c r="P155" s="57"/>
       <c r="Q155" s="57"/>
     </row>
-    <row r="156" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="156" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E156" s="57"/>
       <c r="F156" s="52"/>
       <c r="I156" s="52"/>
@@ -14248,7 +14248,7 @@
       <c r="P156" s="57"/>
       <c r="Q156" s="57"/>
     </row>
-    <row r="157" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="157" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E157" s="57"/>
       <c r="F157" s="52"/>
       <c r="I157" s="52"/>
@@ -14257,7 +14257,7 @@
       <c r="P157" s="57"/>
       <c r="Q157" s="57"/>
     </row>
-    <row r="158" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="158" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E158" s="57"/>
       <c r="F158" s="52"/>
       <c r="I158" s="52"/>
@@ -14266,7 +14266,7 @@
       <c r="P158" s="57"/>
       <c r="Q158" s="57"/>
     </row>
-    <row r="159" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="159" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E159" s="57"/>
       <c r="F159" s="52"/>
       <c r="I159" s="52"/>
@@ -14275,7 +14275,7 @@
       <c r="P159" s="57"/>
       <c r="Q159" s="57"/>
     </row>
-    <row r="160" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="160" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E160" s="61"/>
       <c r="F160" s="52"/>
       <c r="G160" s="54"/>
@@ -14290,7 +14290,7 @@
       <c r="P160" s="56"/>
       <c r="Q160" s="56"/>
     </row>
-    <row r="161" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="161" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E161" s="61"/>
       <c r="F161" s="52"/>
       <c r="G161" s="54"/>
@@ -14305,7 +14305,7 @@
       <c r="P161" s="56"/>
       <c r="Q161" s="56"/>
     </row>
-    <row r="162" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="162" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E162" s="61"/>
       <c r="F162" s="52"/>
       <c r="G162" s="54"/>
@@ -14320,7 +14320,7 @@
       <c r="P162" s="56"/>
       <c r="Q162" s="56"/>
     </row>
-    <row r="163" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="163" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E163" s="53"/>
       <c r="F163" s="52"/>
       <c r="G163" s="54"/>
@@ -14335,7 +14335,7 @@
       <c r="P163" s="64"/>
       <c r="Q163" s="64"/>
     </row>
-    <row r="164" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="164" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E164" s="53"/>
       <c r="F164" s="52"/>
       <c r="G164" s="54"/>
@@ -14350,7 +14350,7 @@
       <c r="P164" s="64"/>
       <c r="Q164" s="64"/>
     </row>
-    <row r="165" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="165" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E165" s="53"/>
       <c r="F165" s="52"/>
       <c r="G165" s="54"/>
@@ -14365,7 +14365,7 @@
       <c r="P165" s="64"/>
       <c r="Q165" s="64"/>
     </row>
-    <row r="166" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="166" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E166" s="53"/>
       <c r="F166" s="52"/>
       <c r="G166" s="54"/>
@@ -14380,7 +14380,7 @@
       <c r="P166" s="64"/>
       <c r="Q166" s="64"/>
     </row>
-    <row r="167" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="167" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E167" s="53"/>
       <c r="F167" s="52"/>
       <c r="G167" s="54"/>
@@ -14395,7 +14395,7 @@
       <c r="P167" s="64"/>
       <c r="Q167" s="64"/>
     </row>
-    <row r="168" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="168" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E168" s="53"/>
       <c r="F168" s="52"/>
       <c r="G168" s="54"/>
@@ -14410,7 +14410,7 @@
       <c r="P168" s="64"/>
       <c r="Q168" s="64"/>
     </row>
-    <row r="169" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="169" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E169" s="53"/>
       <c r="F169" s="52"/>
       <c r="G169" s="54"/>
@@ -14425,7 +14425,7 @@
       <c r="P169" s="64"/>
       <c r="Q169" s="64"/>
     </row>
-    <row r="170" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="170" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E170" s="53"/>
       <c r="F170" s="52"/>
       <c r="G170" s="54"/>
@@ -14440,7 +14440,7 @@
       <c r="P170" s="64"/>
       <c r="Q170" s="64"/>
     </row>
-    <row r="171" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="171" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E171" s="53"/>
       <c r="F171" s="52"/>
       <c r="G171" s="54"/>
@@ -14455,7 +14455,7 @@
       <c r="P171" s="64"/>
       <c r="Q171" s="64"/>
     </row>
-    <row r="172" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="172" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E172" s="53"/>
       <c r="F172" s="52"/>
       <c r="G172" s="54"/>
@@ -14470,7 +14470,7 @@
       <c r="P172" s="64"/>
       <c r="Q172" s="64"/>
     </row>
-    <row r="173" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="173" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E173" s="53"/>
       <c r="F173" s="52"/>
       <c r="G173" s="54"/>
@@ -14485,7 +14485,7 @@
       <c r="P173" s="64"/>
       <c r="Q173" s="64"/>
     </row>
-    <row r="174" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="174" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E174" s="53"/>
       <c r="F174" s="52"/>
       <c r="G174" s="54"/>
@@ -14500,7 +14500,7 @@
       <c r="P174" s="64"/>
       <c r="Q174" s="64"/>
     </row>
-    <row r="175" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="175" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E175" s="53"/>
       <c r="F175" s="52"/>
       <c r="G175" s="54"/>
@@ -14515,7 +14515,7 @@
       <c r="P175" s="64"/>
       <c r="Q175" s="64"/>
     </row>
-    <row r="176" spans="5:17" x14ac:dyDescent="0.35">
+    <row r="176" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E176" s="53"/>
       <c r="F176" s="52"/>
       <c r="G176" s="54"/>
@@ -14530,7 +14530,7 @@
       <c r="P176" s="64"/>
       <c r="Q176" s="64"/>
     </row>
-    <row r="177" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="177" spans="4:17" x14ac:dyDescent="0.3">
       <c r="E177" s="53"/>
       <c r="F177" s="52"/>
       <c r="G177" s="54"/>
@@ -14545,7 +14545,7 @@
       <c r="P177" s="64"/>
       <c r="Q177" s="64"/>
     </row>
-    <row r="178" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="178" spans="4:17" x14ac:dyDescent="0.3">
       <c r="E178" s="53"/>
       <c r="F178" s="52"/>
       <c r="G178" s="54"/>
@@ -14560,7 +14560,7 @@
       <c r="P178" s="64"/>
       <c r="Q178" s="64"/>
     </row>
-    <row r="179" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="179" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D179" s="59"/>
       <c r="E179" s="53"/>
       <c r="F179" s="59"/>
@@ -14576,7 +14576,7 @@
       <c r="P179" s="64"/>
       <c r="Q179" s="64"/>
     </row>
-    <row r="180" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="180" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D180" s="59"/>
       <c r="E180" s="53"/>
       <c r="F180" s="59"/>
@@ -14592,7 +14592,7 @@
       <c r="P180" s="64"/>
       <c r="Q180" s="64"/>
     </row>
-    <row r="181" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="181" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D181" s="59"/>
       <c r="E181" s="53"/>
       <c r="F181" s="59"/>
@@ -14608,7 +14608,7 @@
       <c r="P181" s="64"/>
       <c r="Q181" s="64"/>
     </row>
-    <row r="182" spans="4:17" x14ac:dyDescent="0.35">
+    <row r="182" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D182" s="59"/>
       <c r="E182" s="53"/>
       <c r="F182" s="59"/>
@@ -14625,10 +14625,6 @@
       <c r="Q182" s="64"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q108" xr:uid="{06CB1331-AF3E-489A-B433-09E21B4DF482}">
-    <filterColumn colId="6" showButton="0"/>
-    <filterColumn colId="7" showButton="0"/>
-  </autoFilter>
   <mergeCells count="361">
     <mergeCell ref="C94:C98"/>
     <mergeCell ref="D94:D98"/>
@@ -15025,197 +15021,197 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB8B1907-1808-45DB-89DB-D7AD15506F3A}">
   <dimension ref="B1:B38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="2" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="37" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="38" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="38" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B38" s="1" t="s">
         <v>318</v>
       </c>
@@ -15231,43 +15227,43 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A97597-49CE-4804-805A-84A20592BE98}">
   <dimension ref="A1:BC108"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="20.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.54296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="26.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" style="1" customWidth="1"/>
-    <col min="12" max="17" width="17.7265625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="22.54296875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="15.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.21875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="1" customWidth="1"/>
+    <col min="12" max="17" width="17.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="22.5546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5546875" style="1" customWidth="1"/>
     <col min="20" max="20" width="15" style="1" customWidth="1"/>
-    <col min="21" max="25" width="13.1796875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16.54296875" style="1" customWidth="1"/>
-    <col min="27" max="28" width="13.1796875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="19.453125" style="1" customWidth="1"/>
-    <col min="30" max="30" width="13.81640625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="13.1796875" style="1" customWidth="1"/>
-    <col min="32" max="32" width="13.453125" style="1" customWidth="1"/>
-    <col min="33" max="33" width="30.7265625" style="1" customWidth="1"/>
-    <col min="34" max="36" width="13.1796875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.54296875" style="1" customWidth="1"/>
-    <col min="38" max="43" width="16.7265625" style="1" customWidth="1"/>
-    <col min="44" max="45" width="13.26953125" style="1" customWidth="1"/>
-    <col min="46" max="46" width="23.81640625" style="1" customWidth="1"/>
-    <col min="47" max="47" width="22.54296875" style="1" customWidth="1"/>
-    <col min="48" max="48" width="24.1796875" style="1" customWidth="1"/>
-    <col min="49" max="49" width="27.81640625" style="1" customWidth="1"/>
-    <col min="50" max="50" width="24.7265625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="22.7265625" style="1" customWidth="1"/>
-    <col min="52" max="55" width="13.26953125" style="1" customWidth="1"/>
-    <col min="56" max="16384" width="11.453125" style="1"/>
+    <col min="21" max="25" width="13.21875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16.5546875" style="1" customWidth="1"/>
+    <col min="27" max="28" width="13.21875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="19.44140625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="13.77734375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="13.21875" style="1" customWidth="1"/>
+    <col min="32" max="32" width="13.44140625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="30.77734375" style="1" customWidth="1"/>
+    <col min="34" max="36" width="13.21875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5546875" style="1" customWidth="1"/>
+    <col min="38" max="43" width="16.77734375" style="1" customWidth="1"/>
+    <col min="44" max="45" width="13.21875" style="1" customWidth="1"/>
+    <col min="46" max="46" width="23.77734375" style="1" customWidth="1"/>
+    <col min="47" max="47" width="22.5546875" style="1" customWidth="1"/>
+    <col min="48" max="48" width="24.21875" style="1" customWidth="1"/>
+    <col min="49" max="49" width="27.77734375" style="1" customWidth="1"/>
+    <col min="50" max="50" width="24.77734375" style="1" customWidth="1"/>
+    <col min="51" max="51" width="22.77734375" style="1" customWidth="1"/>
+    <col min="52" max="55" width="13.21875" style="1" customWidth="1"/>
+    <col min="56" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.5">
@@ -15447,16 +15443,16 @@
       <c r="AG3" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="AL3" s="140" t="s">
+      <c r="AL3" s="152" t="s">
         <v>346</v>
       </c>
-      <c r="AM3" s="140"/>
-      <c r="AN3" s="140"/>
-      <c r="AO3" s="140" t="s">
+      <c r="AM3" s="152"/>
+      <c r="AN3" s="152"/>
+      <c r="AO3" s="152" t="s">
         <v>347</v>
       </c>
-      <c r="AP3" s="140"/>
-      <c r="AQ3" s="140"/>
+      <c r="AP3" s="152"/>
+      <c r="AQ3" s="152"/>
       <c r="AR3" s="13"/>
       <c r="AS3" s="13"/>
       <c r="AT3" s="13"/>

--- a/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_TecnolLogistica_VNAL.xlsx
+++ b/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_TecnolLogistica_VNAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Analisis_Curricular/data/raw/FORMATOS RA CICLO UNO RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="815" documentId="13_ncr:1_{523E9347-1CEE-415F-A1AF-C055F087266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC3EA0F7-65A0-406E-8149-E6EEE82C22E7}"/>
+  <xr:revisionPtr revIDLastSave="816" documentId="13_ncr:1_{523E9347-1CEE-415F-A1AF-C055F087266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEAB5E10-0083-4DC4-815F-96DA2400AD73}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Paso 2 Redacción competen" sheetId="6" r:id="rId2"/>
     <sheet name="Paso 3 Redacción RA " sheetId="5" r:id="rId3"/>
     <sheet name="Paso 4 Estrategias mesocurricu" sheetId="8" r:id="rId4"/>
-    <sheet name="Paso 5 Estrategias microcurr" sheetId="10" r:id="rId5"/>
+    <sheet name="Paso 5 Estrategias micro" sheetId="10" r:id="rId5"/>
     <sheet name="Taxonomia para Competencias" sheetId="11" r:id="rId6"/>
     <sheet name="Taxonomias para RA" sheetId="9" r:id="rId7"/>
   </sheets>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Paso 3 Redacción RA '!$A$2:$I$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Paso 4 Estrategias mesocurricu'!$A$2:$E$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Paso 5 Estrategias microcurr'!$A$1:$Q$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Paso 5 Estrategias micro'!$A$1:$Q$108</definedName>
     <definedName name="actitudinalB" localSheetId="4">Tabla5785[ActitudinalB]</definedName>
     <definedName name="actitudinalB">Tabla5785[ActitudinalB]</definedName>
     <definedName name="ActitudinalBAK">'Taxonomias para RA'!$AC$3:$AG$3</definedName>
@@ -4108,7 +4108,28 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4117,11 +4138,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4135,9 +4158,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4146,27 +4166,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4177,6 +4177,33 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4213,33 +4240,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8435,16 +8435,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="117" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="119" t="s">
+      <c r="B3" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="126" t="s">
+      <c r="C3" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="126" t="s">
+      <c r="D3" s="131" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="16" t="s">
@@ -8456,24 +8456,24 @@
       <c r="G3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="126" t="s">
+      <c r="H3" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="126" t="s">
+      <c r="I3" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="126" t="s">
+      <c r="J3" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="119" t="s">
+      <c r="K3" s="117" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.3">
-      <c r="A4" s="119"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="131"/>
+      <c r="D4" s="131"/>
       <c r="E4" s="16" t="s">
         <v>29</v>
       </c>
@@ -8483,16 +8483,16 @@
       <c r="G4" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="126"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="126"/>
-      <c r="K4" s="119"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="117"/>
     </row>
     <row r="5" spans="1:11" ht="62.55" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="119"/>
-      <c r="B5" s="119"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
+      <c r="A5" s="117"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="131"/>
       <c r="E5" s="27" t="s">
         <v>32</v>
       </c>
@@ -8502,16 +8502,16 @@
       <c r="G5" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="119"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="131"/>
+      <c r="J5" s="131"/>
+      <c r="K5" s="117"/>
     </row>
     <row r="6" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="119"/>
-      <c r="B6" s="119"/>
-      <c r="C6" s="126"/>
-      <c r="D6" s="126"/>
+      <c r="A6" s="117"/>
+      <c r="B6" s="117"/>
+      <c r="C6" s="131"/>
+      <c r="D6" s="131"/>
       <c r="E6" s="21" t="s">
         <v>35</v>
       </c>
@@ -8521,10 +8521,10 @@
       <c r="G6" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="126"/>
-      <c r="I6" s="126"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="119"/>
+      <c r="H6" s="131"/>
+      <c r="I6" s="131"/>
+      <c r="J6" s="131"/>
+      <c r="K6" s="117"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C7" s="20"/>
@@ -9335,16 +9335,16 @@
       <c r="A3" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="138" t="s">
+      <c r="B3" s="147" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="141" t="s">
+      <c r="C3" s="150" t="s">
         <v>121</v>
       </c>
       <c r="D3" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="137" t="s">
+      <c r="E3" s="146" t="s">
         <v>123</v>
       </c>
       <c r="F3" s="17" t="s">
@@ -9355,12 +9355,12 @@
       <c r="A4" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="139"/>
-      <c r="C4" s="142"/>
+      <c r="B4" s="148"/>
+      <c r="C4" s="151"/>
       <c r="D4" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E4" s="126"/>
+      <c r="E4" s="131"/>
       <c r="F4" s="21" t="s">
         <v>126</v>
       </c>
@@ -9369,12 +9369,12 @@
       <c r="A5" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="139"/>
-      <c r="C5" s="142"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="151"/>
       <c r="D5" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="126"/>
+      <c r="E5" s="131"/>
       <c r="F5" s="21" t="s">
         <v>128</v>
       </c>
@@ -9383,26 +9383,26 @@
       <c r="A6" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="140"/>
-      <c r="C6" s="143"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="152"/>
       <c r="D6" s="46"/>
-      <c r="E6" s="127"/>
+      <c r="E6" s="132"/>
       <c r="F6" s="40"/>
     </row>
     <row r="7" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="144" t="s">
+      <c r="B7" s="153" t="s">
         <v>129</v>
       </c>
-      <c r="C7" s="145" t="s">
+      <c r="C7" s="154" t="s">
         <v>130</v>
       </c>
       <c r="D7" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="125" t="s">
+      <c r="E7" s="130" t="s">
         <v>123</v>
       </c>
       <c r="F7" s="48" t="s">
@@ -9413,12 +9413,12 @@
       <c r="A8" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="139"/>
-      <c r="C8" s="142"/>
+      <c r="B8" s="148"/>
+      <c r="C8" s="151"/>
       <c r="D8" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E8" s="126"/>
+      <c r="E8" s="131"/>
       <c r="F8" s="21" t="s">
         <v>126</v>
       </c>
@@ -9427,12 +9427,12 @@
       <c r="A9" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="139"/>
-      <c r="C9" s="142"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="151"/>
       <c r="D9" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="126"/>
+      <c r="E9" s="131"/>
       <c r="F9" s="21" t="s">
         <v>128</v>
       </c>
@@ -9441,25 +9441,25 @@
       <c r="A10" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B10" s="139"/>
-      <c r="C10" s="142"/>
-      <c r="E10" s="126"/>
+      <c r="B10" s="148"/>
+      <c r="C10" s="151"/>
+      <c r="E10" s="131"/>
       <c r="F10" s="21"/>
     </row>
     <row r="11" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A11" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="144" t="s">
+      <c r="B11" s="153" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="146" t="s">
+      <c r="C11" s="155" t="s">
         <v>132</v>
       </c>
       <c r="D11" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="125" t="s">
+      <c r="E11" s="130" t="s">
         <v>133</v>
       </c>
       <c r="F11" s="48" t="s">
@@ -9470,12 +9470,12 @@
       <c r="A12" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="139"/>
-      <c r="C12" s="147"/>
+      <c r="B12" s="148"/>
+      <c r="C12" s="156"/>
       <c r="D12" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E12" s="126"/>
+      <c r="E12" s="131"/>
       <c r="F12" s="21" t="s">
         <v>126</v>
       </c>
@@ -9484,12 +9484,12 @@
       <c r="A13" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="139"/>
-      <c r="C13" s="147"/>
+      <c r="B13" s="148"/>
+      <c r="C13" s="156"/>
       <c r="D13" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E13" s="126"/>
+      <c r="E13" s="131"/>
       <c r="F13" s="21" t="s">
         <v>128</v>
       </c>
@@ -9498,46 +9498,46 @@
       <c r="A14" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="139"/>
-      <c r="C14" s="147"/>
+      <c r="B14" s="148"/>
+      <c r="C14" s="156"/>
       <c r="D14" s="44"/>
-      <c r="E14" s="126"/>
+      <c r="E14" s="131"/>
       <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B15" s="139"/>
-      <c r="C15" s="147"/>
+      <c r="B15" s="148"/>
+      <c r="C15" s="156"/>
       <c r="D15" s="44"/>
-      <c r="E15" s="126"/>
+      <c r="E15" s="131"/>
       <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="140"/>
-      <c r="C16" s="148"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="157"/>
       <c r="D16" s="46"/>
-      <c r="E16" s="127"/>
+      <c r="E16" s="132"/>
       <c r="F16" s="40"/>
     </row>
     <row r="17" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A17" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="124" t="s">
+      <c r="B17" s="116" t="s">
         <v>134</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="C17" s="130" t="s">
         <v>135</v>
       </c>
       <c r="D17" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="125" t="s">
+      <c r="E17" s="130" t="s">
         <v>136</v>
       </c>
       <c r="F17" s="21" t="s">
@@ -9548,12 +9548,12 @@
       <c r="A18" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="119"/>
-      <c r="C18" s="126"/>
+      <c r="B18" s="117"/>
+      <c r="C18" s="131"/>
       <c r="D18" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="126"/>
+      <c r="E18" s="131"/>
       <c r="F18" s="21" t="s">
         <v>126</v>
       </c>
@@ -9562,12 +9562,12 @@
       <c r="A19" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="119"/>
-      <c r="C19" s="126"/>
+      <c r="B19" s="117"/>
+      <c r="C19" s="131"/>
       <c r="D19" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E19" s="126"/>
+      <c r="E19" s="131"/>
       <c r="F19" s="21" t="s">
         <v>128</v>
       </c>
@@ -9576,44 +9576,44 @@
       <c r="A20" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B20" s="119"/>
-      <c r="C20" s="126"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="131"/>
       <c r="D20" s="44"/>
-      <c r="E20" s="126"/>
+      <c r="E20" s="131"/>
       <c r="F20" s="21"/>
     </row>
     <row r="21" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="119"/>
-      <c r="C21" s="126"/>
-      <c r="E21" s="126"/>
+      <c r="B21" s="117"/>
+      <c r="C21" s="131"/>
+      <c r="E21" s="131"/>
     </row>
     <row r="22" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="120"/>
-      <c r="C22" s="127"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="132"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="127"/>
+      <c r="E22" s="132"/>
       <c r="F22" s="41"/>
     </row>
     <row r="23" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A23" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="124" t="s">
+      <c r="B23" s="116" t="s">
         <v>137</v>
       </c>
-      <c r="C23" s="125" t="s">
+      <c r="C23" s="130" t="s">
         <v>138</v>
       </c>
       <c r="D23" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="E23" s="125" t="s">
+      <c r="E23" s="130" t="s">
         <v>139</v>
       </c>
       <c r="F23" s="48" t="s">
@@ -9624,12 +9624,12 @@
       <c r="A24" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="119"/>
-      <c r="C24" s="126"/>
+      <c r="B24" s="117"/>
+      <c r="C24" s="131"/>
       <c r="D24" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="126"/>
+      <c r="E24" s="131"/>
       <c r="F24" s="21" t="s">
         <v>126</v>
       </c>
@@ -9638,12 +9638,12 @@
       <c r="A25" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="119"/>
-      <c r="C25" s="126"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="131"/>
       <c r="D25" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E25" s="126"/>
+      <c r="E25" s="131"/>
       <c r="F25" s="21" t="s">
         <v>128</v>
       </c>
@@ -9652,44 +9652,44 @@
       <c r="A26" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="119"/>
-      <c r="C26" s="126"/>
+      <c r="B26" s="117"/>
+      <c r="C26" s="131"/>
       <c r="D26" s="44"/>
-      <c r="E26" s="126"/>
+      <c r="E26" s="131"/>
       <c r="F26" s="21"/>
     </row>
     <row r="27" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B27" s="119"/>
-      <c r="C27" s="126"/>
-      <c r="E27" s="126"/>
+      <c r="B27" s="117"/>
+      <c r="C27" s="131"/>
+      <c r="E27" s="131"/>
     </row>
     <row r="28" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="120"/>
-      <c r="C28" s="127"/>
+      <c r="B28" s="118"/>
+      <c r="C28" s="132"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="127"/>
+      <c r="E28" s="132"/>
       <c r="F28" s="41"/>
     </row>
     <row r="29" spans="1:6" ht="36" x14ac:dyDescent="0.3">
       <c r="A29" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="151" t="s">
+      <c r="B29" s="139" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="154" t="s">
+      <c r="C29" s="142" t="s">
         <v>141</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="125" t="s">
+      <c r="E29" s="130" t="s">
         <v>142</v>
       </c>
       <c r="F29" s="12" t="s">
@@ -9700,12 +9700,12 @@
       <c r="A30" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="152"/>
-      <c r="C30" s="155"/>
+      <c r="B30" s="140"/>
+      <c r="C30" s="143"/>
       <c r="D30" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="E30" s="126"/>
+      <c r="E30" s="131"/>
       <c r="F30" s="12" t="s">
         <v>128</v>
       </c>
@@ -9714,12 +9714,12 @@
       <c r="A31" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="152"/>
-      <c r="C31" s="155"/>
+      <c r="B31" s="140"/>
+      <c r="C31" s="143"/>
       <c r="D31" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="E31" s="126"/>
+      <c r="E31" s="131"/>
       <c r="F31" s="12" t="s">
         <v>128</v>
       </c>
@@ -9728,43 +9728,43 @@
       <c r="A32" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="152"/>
-      <c r="C32" s="155"/>
-      <c r="E32" s="126"/>
+      <c r="B32" s="140"/>
+      <c r="C32" s="143"/>
+      <c r="E32" s="131"/>
     </row>
     <row r="33" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B33" s="152"/>
-      <c r="C33" s="155"/>
+      <c r="B33" s="140"/>
+      <c r="C33" s="143"/>
       <c r="D33" s="44"/>
-      <c r="E33" s="126"/>
+      <c r="E33" s="131"/>
     </row>
     <row r="34" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="153"/>
-      <c r="C34" s="156"/>
+      <c r="B34" s="141"/>
+      <c r="C34" s="144"/>
       <c r="D34" s="46"/>
-      <c r="E34" s="157"/>
+      <c r="E34" s="145"/>
       <c r="F34" s="92"/>
     </row>
     <row r="35" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="149" t="s">
+      <c r="B35" s="137" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="150" t="s">
+      <c r="C35" s="138" t="s">
         <v>145</v>
       </c>
       <c r="D35" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="150" t="s">
+      <c r="E35" s="138" t="s">
         <v>136</v>
       </c>
       <c r="F35" s="12" t="s">
@@ -9775,12 +9775,12 @@
       <c r="A36" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="119"/>
-      <c r="C36" s="126"/>
+      <c r="B36" s="117"/>
+      <c r="C36" s="131"/>
       <c r="D36" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="E36" s="126"/>
+      <c r="E36" s="131"/>
       <c r="F36" s="12" t="s">
         <v>128</v>
       </c>
@@ -9789,12 +9789,12 @@
       <c r="A37" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="119"/>
-      <c r="C37" s="126"/>
+      <c r="B37" s="117"/>
+      <c r="C37" s="131"/>
       <c r="D37" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="E37" s="126"/>
+      <c r="E37" s="131"/>
       <c r="F37" s="12" t="s">
         <v>128</v>
       </c>
@@ -9803,31 +9803,40 @@
       <c r="A38" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="119"/>
-      <c r="C38" s="126"/>
+      <c r="B38" s="117"/>
+      <c r="C38" s="131"/>
       <c r="D38" s="44"/>
-      <c r="E38" s="126"/>
+      <c r="E38" s="131"/>
     </row>
     <row r="39" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A39" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="119"/>
-      <c r="C39" s="126"/>
-      <c r="E39" s="126"/>
+      <c r="B39" s="117"/>
+      <c r="C39" s="131"/>
+      <c r="E39" s="131"/>
     </row>
     <row r="40" spans="1:6" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="120"/>
-      <c r="C40" s="127"/>
+      <c r="B40" s="118"/>
+      <c r="C40" s="132"/>
       <c r="D40" s="40"/>
-      <c r="E40" s="127"/>
+      <c r="E40" s="132"/>
       <c r="F40" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="E11:E16"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="B11:B16"/>
+    <mergeCell ref="C11:C16"/>
     <mergeCell ref="B35:B40"/>
     <mergeCell ref="C35:C40"/>
     <mergeCell ref="E35:E40"/>
@@ -9840,15 +9849,6 @@
     <mergeCell ref="C29:C34"/>
     <mergeCell ref="E29:E34"/>
     <mergeCell ref="E23:E28"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="E11:E16"/>
-    <mergeCell ref="E7:E10"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="B11:B16"/>
-    <mergeCell ref="C11:C16"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:A40" xr:uid="{D048ED25-334D-4F32-B2A7-D11385F03FF6}">
@@ -9906,11 +9906,11 @@
       <c r="F1" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="G1" s="116" t="s">
+      <c r="G1" s="133" t="s">
         <v>153</v>
       </c>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
       <c r="J1" s="18" t="s">
         <v>154</v>
       </c>
@@ -10103,48 +10103,48 @@
       <c r="B5" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="117">
+      <c r="C5" s="123">
         <v>1</v>
       </c>
-      <c r="D5" s="119" t="s">
+      <c r="D5" s="117" t="s">
         <v>190</v>
       </c>
-      <c r="E5" s="121" t="s">
+      <c r="E5" s="127" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="117" t="s">
+      <c r="F5" s="123" t="s">
         <v>180</v>
       </c>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117" t="s">
+      <c r="G5" s="123"/>
+      <c r="H5" s="123" t="s">
         <v>181</v>
       </c>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117">
+      <c r="I5" s="123"/>
+      <c r="J5" s="123">
         <v>3</v>
       </c>
-      <c r="K5" s="117">
+      <c r="K5" s="123">
         <f>J5*12</f>
         <v>36</v>
       </c>
-      <c r="L5" s="117">
+      <c r="L5" s="123">
         <f>36*J5</f>
         <v>108</v>
       </c>
-      <c r="M5" s="117">
+      <c r="M5" s="123">
         <f>SUM(K5:L5)</f>
         <v>144</v>
       </c>
-      <c r="N5" s="121" t="s">
+      <c r="N5" s="127" t="s">
         <v>192</v>
       </c>
-      <c r="O5" s="121" t="s">
+      <c r="O5" s="127" t="s">
         <v>183</v>
       </c>
-      <c r="P5" s="121" t="s">
+      <c r="P5" s="127" t="s">
         <v>193</v>
       </c>
-      <c r="Q5" s="121" t="s">
+      <c r="Q5" s="127" t="s">
         <v>185</v>
       </c>
     </row>
@@ -10156,21 +10156,21 @@
       <c r="B6" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="117"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
-      <c r="M6" s="117"/>
-      <c r="N6" s="121"/>
-      <c r="O6" s="121"/>
-      <c r="P6" s="121"/>
-      <c r="Q6" s="121"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="123"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="123"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="123"/>
+      <c r="M6" s="123"/>
+      <c r="N6" s="127"/>
+      <c r="O6" s="127"/>
+      <c r="P6" s="127"/>
+      <c r="Q6" s="127"/>
     </row>
     <row r="7" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="80" t="str">
@@ -10180,21 +10180,21 @@
       <c r="B7" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="118"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="118"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="118"/>
-      <c r="N7" s="122"/>
-      <c r="O7" s="122"/>
-      <c r="P7" s="122"/>
-      <c r="Q7" s="122"/>
+      <c r="C7" s="124"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="128"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="124"/>
+      <c r="K7" s="124"/>
+      <c r="L7" s="124"/>
+      <c r="M7" s="124"/>
+      <c r="N7" s="128"/>
+      <c r="O7" s="128"/>
+      <c r="P7" s="128"/>
+      <c r="Q7" s="128"/>
     </row>
     <row r="8" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="str">
@@ -10204,48 +10204,48 @@
       <c r="B8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="123">
+      <c r="C8" s="129">
         <v>1</v>
       </c>
-      <c r="D8" s="124" t="s">
+      <c r="D8" s="116" t="s">
         <v>194</v>
       </c>
-      <c r="E8" s="125" t="s">
+      <c r="E8" s="130" t="s">
         <v>195</v>
       </c>
-      <c r="F8" s="124" t="s">
+      <c r="F8" s="116" t="s">
         <v>196</v>
       </c>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124" t="s">
+      <c r="G8" s="116"/>
+      <c r="H8" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124">
+      <c r="I8" s="116"/>
+      <c r="J8" s="116">
         <v>2</v>
       </c>
-      <c r="K8" s="117">
+      <c r="K8" s="123">
         <f>J8*12</f>
         <v>24</v>
       </c>
-      <c r="L8" s="117">
+      <c r="L8" s="123">
         <f>36*J8</f>
         <v>72</v>
       </c>
-      <c r="M8" s="124">
+      <c r="M8" s="116">
         <f>SUM(K8:L8)</f>
         <v>96</v>
       </c>
-      <c r="N8" s="125" t="s">
+      <c r="N8" s="130" t="s">
         <v>197</v>
       </c>
-      <c r="O8" s="125" t="s">
+      <c r="O8" s="130" t="s">
         <v>198</v>
       </c>
-      <c r="P8" s="125" t="s">
+      <c r="P8" s="130" t="s">
         <v>199</v>
       </c>
-      <c r="Q8" s="125" t="s">
+      <c r="Q8" s="130" t="s">
         <v>185</v>
       </c>
     </row>
@@ -10257,21 +10257,21 @@
       <c r="B9" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="117"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="119"/>
-      <c r="I9" s="119"/>
-      <c r="J9" s="119"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="117"/>
-      <c r="M9" s="119"/>
-      <c r="N9" s="126"/>
-      <c r="O9" s="126"/>
-      <c r="P9" s="126"/>
-      <c r="Q9" s="126"/>
+      <c r="C9" s="123"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="117"/>
+      <c r="H9" s="117"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="123"/>
+      <c r="L9" s="123"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="131"/>
+      <c r="O9" s="131"/>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
     </row>
     <row r="10" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A10" s="80" t="str">
@@ -10281,21 +10281,21 @@
       <c r="B10" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="118"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="127"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="120"/>
-      <c r="K10" s="118"/>
-      <c r="L10" s="118"/>
-      <c r="M10" s="120"/>
-      <c r="N10" s="127"/>
-      <c r="O10" s="127"/>
-      <c r="P10" s="127"/>
-      <c r="Q10" s="127"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="118"/>
+      <c r="J10" s="118"/>
+      <c r="K10" s="124"/>
+      <c r="L10" s="124"/>
+      <c r="M10" s="118"/>
+      <c r="N10" s="132"/>
+      <c r="O10" s="132"/>
+      <c r="P10" s="132"/>
+      <c r="Q10" s="132"/>
     </row>
     <row r="11" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="24" t="str">
@@ -10305,48 +10305,48 @@
       <c r="B11" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="123">
+      <c r="C11" s="129">
         <v>1</v>
       </c>
-      <c r="D11" s="124" t="s">
+      <c r="D11" s="116" t="s">
         <v>200</v>
       </c>
-      <c r="E11" s="128" t="s">
+      <c r="E11" s="119" t="s">
         <v>201</v>
       </c>
-      <c r="F11" s="123" t="s">
+      <c r="F11" s="129" t="s">
         <v>180</v>
       </c>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123" t="s">
+      <c r="G11" s="129"/>
+      <c r="H11" s="129" t="s">
         <v>181</v>
       </c>
-      <c r="I11" s="123"/>
-      <c r="J11" s="123">
+      <c r="I11" s="129"/>
+      <c r="J11" s="129">
         <v>3</v>
       </c>
-      <c r="K11" s="117">
+      <c r="K11" s="123">
         <f>J11*12</f>
         <v>36</v>
       </c>
-      <c r="L11" s="117">
+      <c r="L11" s="123">
         <f>36*J11</f>
         <v>108</v>
       </c>
-      <c r="M11" s="123">
+      <c r="M11" s="129">
         <f>SUM(K11:L11)</f>
         <v>144</v>
       </c>
-      <c r="N11" s="128" t="s">
+      <c r="N11" s="119" t="s">
         <v>202</v>
       </c>
-      <c r="O11" s="128" t="s">
+      <c r="O11" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="P11" s="128" t="s">
+      <c r="P11" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q11" s="128" t="s">
+      <c r="Q11" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -10358,21 +10358,21 @@
       <c r="B12" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="117"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="117"/>
-      <c r="G12" s="117"/>
-      <c r="H12" s="117"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="117"/>
-      <c r="K12" s="117"/>
-      <c r="L12" s="117"/>
-      <c r="M12" s="117"/>
-      <c r="N12" s="129"/>
-      <c r="O12" s="129"/>
-      <c r="P12" s="129"/>
-      <c r="Q12" s="129"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="123"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
+      <c r="M12" s="123"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="120"/>
+      <c r="P12" s="120"/>
+      <c r="Q12" s="120"/>
     </row>
     <row r="13" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="80" t="str">
@@ -10382,21 +10382,21 @@
       <c r="B13" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="118"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="118"/>
-      <c r="L13" s="118"/>
-      <c r="M13" s="118"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
-      <c r="P13" s="130"/>
-      <c r="Q13" s="130"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="124"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="124"/>
+      <c r="J13" s="124"/>
+      <c r="K13" s="124"/>
+      <c r="L13" s="124"/>
+      <c r="M13" s="124"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="121"/>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="121"/>
       <c r="R13" s="50">
         <f>SUM(J3:J13)</f>
         <v>14</v>
@@ -10467,48 +10467,48 @@
       <c r="B15" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="124">
+      <c r="C15" s="116">
         <v>2</v>
       </c>
-      <c r="D15" s="124" t="s">
+      <c r="D15" s="116" t="s">
         <v>206</v>
       </c>
-      <c r="E15" s="128" t="s">
+      <c r="E15" s="119" t="s">
         <v>207</v>
       </c>
-      <c r="F15" s="124" t="s">
+      <c r="F15" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G15" s="124"/>
-      <c r="H15" s="124" t="s">
+      <c r="G15" s="116"/>
+      <c r="H15" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I15" s="124"/>
-      <c r="J15" s="124">
+      <c r="I15" s="116"/>
+      <c r="J15" s="116">
         <v>3</v>
       </c>
-      <c r="K15" s="117">
+      <c r="K15" s="123">
         <f>J15*12</f>
         <v>36</v>
       </c>
-      <c r="L15" s="117">
+      <c r="L15" s="123">
         <f>36*J15</f>
         <v>108</v>
       </c>
-      <c r="M15" s="124">
+      <c r="M15" s="116">
         <f>SUM(K15:L15)</f>
         <v>144</v>
       </c>
-      <c r="N15" s="128" t="s">
+      <c r="N15" s="119" t="s">
         <v>208</v>
       </c>
-      <c r="O15" s="128" t="s">
+      <c r="O15" s="119" t="s">
         <v>209</v>
       </c>
-      <c r="P15" s="128" t="s">
+      <c r="P15" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q15" s="128" t="s">
+      <c r="Q15" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -10520,21 +10520,21 @@
       <c r="B16" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="119"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="129"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="119"/>
-      <c r="N16" s="129"/>
-      <c r="O16" s="129"/>
-      <c r="P16" s="129"/>
-      <c r="Q16" s="129"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
+      <c r="I16" s="117"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="123"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="120"/>
     </row>
     <row r="17" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="80" t="str">
@@ -10544,21 +10544,21 @@
       <c r="B17" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="120"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="120"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="120"/>
-      <c r="K17" s="118"/>
-      <c r="L17" s="118"/>
-      <c r="M17" s="120"/>
-      <c r="N17" s="130"/>
-      <c r="O17" s="130"/>
-      <c r="P17" s="130"/>
-      <c r="Q17" s="130"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
+      <c r="K17" s="124"/>
+      <c r="L17" s="124"/>
+      <c r="M17" s="118"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="121"/>
     </row>
     <row r="18" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="str">
@@ -10568,48 +10568,48 @@
       <c r="B18" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="124">
+      <c r="C18" s="116">
         <v>2</v>
       </c>
-      <c r="D18" s="124" t="s">
+      <c r="D18" s="116" t="s">
         <v>210</v>
       </c>
-      <c r="E18" s="128" t="s">
+      <c r="E18" s="119" t="s">
         <v>211</v>
       </c>
-      <c r="F18" s="124" t="s">
+      <c r="F18" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124" t="s">
+      <c r="G18" s="116"/>
+      <c r="H18" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I18" s="124"/>
-      <c r="J18" s="124">
+      <c r="I18" s="116"/>
+      <c r="J18" s="116">
         <v>4</v>
       </c>
-      <c r="K18" s="117">
+      <c r="K18" s="123">
         <f>J18*12</f>
         <v>48</v>
       </c>
-      <c r="L18" s="117">
+      <c r="L18" s="123">
         <f>36*J18</f>
         <v>144</v>
       </c>
-      <c r="M18" s="124">
+      <c r="M18" s="116">
         <f>SUM(K18:L18)</f>
         <v>192</v>
       </c>
-      <c r="N18" s="128" t="s">
+      <c r="N18" s="119" t="s">
         <v>212</v>
       </c>
-      <c r="O18" s="128" t="s">
+      <c r="O18" s="119" t="s">
         <v>209</v>
       </c>
-      <c r="P18" s="128" t="s">
+      <c r="P18" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q18" s="128" t="s">
+      <c r="Q18" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -10621,21 +10621,21 @@
       <c r="B19" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="119"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="119"/>
-      <c r="I19" s="119"/>
-      <c r="J19" s="119"/>
-      <c r="K19" s="117"/>
-      <c r="L19" s="117"/>
-      <c r="M19" s="119"/>
-      <c r="N19" s="129"/>
-      <c r="O19" s="129"/>
-      <c r="P19" s="129"/>
-      <c r="Q19" s="129"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="123"/>
+      <c r="L19" s="123"/>
+      <c r="M19" s="117"/>
+      <c r="N19" s="120"/>
+      <c r="O19" s="120"/>
+      <c r="P19" s="120"/>
+      <c r="Q19" s="120"/>
     </row>
     <row r="20" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="80" t="str">
@@ -10645,21 +10645,21 @@
       <c r="B20" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120"/>
-      <c r="J20" s="120"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="120"/>
-      <c r="N20" s="130"/>
-      <c r="O20" s="130"/>
-      <c r="P20" s="130"/>
-      <c r="Q20" s="130"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="118"/>
+      <c r="K20" s="124"/>
+      <c r="L20" s="124"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="121"/>
     </row>
     <row r="21" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="str">
@@ -10669,48 +10669,48 @@
       <c r="B21" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="124">
+      <c r="C21" s="116">
         <v>2</v>
       </c>
-      <c r="D21" s="124" t="s">
+      <c r="D21" s="116" t="s">
         <v>213</v>
       </c>
-      <c r="E21" s="128" t="s">
+      <c r="E21" s="119" t="s">
         <v>214</v>
       </c>
-      <c r="F21" s="124" t="s">
+      <c r="F21" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G21" s="124"/>
-      <c r="H21" s="124" t="s">
+      <c r="G21" s="116"/>
+      <c r="H21" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I21" s="124"/>
-      <c r="J21" s="124">
+      <c r="I21" s="116"/>
+      <c r="J21" s="116">
         <v>3</v>
       </c>
-      <c r="K21" s="117">
+      <c r="K21" s="123">
         <f>J21*12</f>
         <v>36</v>
       </c>
-      <c r="L21" s="117">
+      <c r="L21" s="123">
         <f>36*J21</f>
         <v>108</v>
       </c>
-      <c r="M21" s="124">
+      <c r="M21" s="116">
         <f>SUM(K21:L21)</f>
         <v>144</v>
       </c>
-      <c r="N21" s="128" t="s">
+      <c r="N21" s="119" t="s">
         <v>215</v>
       </c>
-      <c r="O21" s="128" t="s">
+      <c r="O21" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="P21" s="128" t="s">
+      <c r="P21" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q21" s="128" t="s">
+      <c r="Q21" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -10722,21 +10722,21 @@
       <c r="B22" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="119"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="119"/>
-      <c r="J22" s="119"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="119"/>
-      <c r="N22" s="129"/>
-      <c r="O22" s="129"/>
-      <c r="P22" s="129"/>
-      <c r="Q22" s="129"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="120"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="123"/>
+      <c r="L22" s="123"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="120"/>
+      <c r="O22" s="120"/>
+      <c r="P22" s="120"/>
+      <c r="Q22" s="120"/>
     </row>
     <row r="23" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="80" t="str">
@@ -10746,21 +10746,21 @@
       <c r="B23" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="120"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="130"/>
-      <c r="F23" s="120"/>
-      <c r="G23" s="120"/>
-      <c r="H23" s="120"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="120"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="120"/>
-      <c r="N23" s="130"/>
-      <c r="O23" s="130"/>
-      <c r="P23" s="130"/>
-      <c r="Q23" s="130"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="121"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="124"/>
+      <c r="L23" s="124"/>
+      <c r="M23" s="118"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="121"/>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="121"/>
     </row>
     <row r="24" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="str">
@@ -10770,48 +10770,48 @@
       <c r="B24" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="124">
+      <c r="C24" s="116">
         <v>2</v>
       </c>
-      <c r="D24" s="124" t="s">
+      <c r="D24" s="116" t="s">
         <v>216</v>
       </c>
-      <c r="E24" s="128" t="s">
+      <c r="E24" s="119" t="s">
         <v>217</v>
       </c>
-      <c r="F24" s="124" t="s">
+      <c r="F24" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G24" s="124"/>
-      <c r="H24" s="124" t="s">
+      <c r="G24" s="116"/>
+      <c r="H24" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I24" s="124"/>
-      <c r="J24" s="124">
+      <c r="I24" s="116"/>
+      <c r="J24" s="116">
         <v>3</v>
       </c>
-      <c r="K24" s="117">
+      <c r="K24" s="123">
         <f>J24*12</f>
         <v>36</v>
       </c>
-      <c r="L24" s="117">
+      <c r="L24" s="123">
         <f>36*J24</f>
         <v>108</v>
       </c>
-      <c r="M24" s="124">
+      <c r="M24" s="116">
         <f>SUM(K24:L24)</f>
         <v>144</v>
       </c>
-      <c r="N24" s="128" t="s">
+      <c r="N24" s="119" t="s">
         <v>218</v>
       </c>
-      <c r="O24" s="128" t="s">
+      <c r="O24" s="119" t="s">
         <v>209</v>
       </c>
-      <c r="P24" s="128" t="s">
+      <c r="P24" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q24" s="128" t="s">
+      <c r="Q24" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -10823,21 +10823,21 @@
       <c r="B25" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="129"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="119"/>
-      <c r="I25" s="119"/>
-      <c r="J25" s="119"/>
-      <c r="K25" s="117"/>
-      <c r="L25" s="117"/>
-      <c r="M25" s="119"/>
-      <c r="N25" s="129"/>
-      <c r="O25" s="129"/>
-      <c r="P25" s="129"/>
-      <c r="Q25" s="129"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="120"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="117"/>
+      <c r="I25" s="117"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="123"/>
+      <c r="L25" s="123"/>
+      <c r="M25" s="117"/>
+      <c r="N25" s="120"/>
+      <c r="O25" s="120"/>
+      <c r="P25" s="120"/>
+      <c r="Q25" s="120"/>
     </row>
     <row r="26" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="80" t="str">
@@ -10847,21 +10847,21 @@
       <c r="B26" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="120"/>
-      <c r="D26" s="120"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="120"/>
-      <c r="I26" s="120"/>
-      <c r="J26" s="120"/>
-      <c r="K26" s="118"/>
-      <c r="L26" s="118"/>
-      <c r="M26" s="120"/>
-      <c r="N26" s="130"/>
-      <c r="O26" s="130"/>
-      <c r="P26" s="130"/>
-      <c r="Q26" s="130"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="121"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="118"/>
+      <c r="H26" s="118"/>
+      <c r="I26" s="118"/>
+      <c r="J26" s="118"/>
+      <c r="K26" s="124"/>
+      <c r="L26" s="124"/>
+      <c r="M26" s="118"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="121"/>
+      <c r="P26" s="121"/>
+      <c r="Q26" s="121"/>
       <c r="R26" s="50">
         <f>SUM(J14:J26)</f>
         <v>16</v>
@@ -10985,48 +10985,48 @@
       <c r="B29" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="124">
+      <c r="C29" s="116">
         <v>3</v>
       </c>
-      <c r="D29" s="124" t="s">
+      <c r="D29" s="116" t="s">
         <v>225</v>
       </c>
-      <c r="E29" s="128" t="s">
+      <c r="E29" s="119" t="s">
         <v>226</v>
       </c>
-      <c r="F29" s="124" t="s">
+      <c r="F29" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G29" s="124"/>
-      <c r="H29" s="124" t="s">
+      <c r="G29" s="116"/>
+      <c r="H29" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I29" s="124"/>
-      <c r="J29" s="124">
+      <c r="I29" s="116"/>
+      <c r="J29" s="116">
         <v>3</v>
       </c>
-      <c r="K29" s="117">
+      <c r="K29" s="123">
         <f>J29*12</f>
         <v>36</v>
       </c>
-      <c r="L29" s="117">
+      <c r="L29" s="123">
         <f>36*J29</f>
         <v>108</v>
       </c>
-      <c r="M29" s="124">
+      <c r="M29" s="116">
         <f>SUM(K29:L29)</f>
         <v>144</v>
       </c>
-      <c r="N29" s="128" t="s">
+      <c r="N29" s="119" t="s">
         <v>227</v>
       </c>
-      <c r="O29" s="128" t="s">
+      <c r="O29" s="119" t="s">
         <v>209</v>
       </c>
-      <c r="P29" s="128" t="s">
+      <c r="P29" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q29" s="128" t="s">
+      <c r="Q29" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -11038,21 +11038,21 @@
       <c r="B30" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="129"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="119"/>
-      <c r="H30" s="119"/>
-      <c r="I30" s="119"/>
-      <c r="J30" s="119"/>
-      <c r="K30" s="117"/>
-      <c r="L30" s="117"/>
-      <c r="M30" s="119"/>
-      <c r="N30" s="129"/>
-      <c r="O30" s="129"/>
-      <c r="P30" s="129"/>
-      <c r="Q30" s="129"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="120"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="123"/>
+      <c r="L30" s="123"/>
+      <c r="M30" s="117"/>
+      <c r="N30" s="120"/>
+      <c r="O30" s="120"/>
+      <c r="P30" s="120"/>
+      <c r="Q30" s="120"/>
     </row>
     <row r="31" spans="1:19" s="50" customFormat="1" ht="53.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="80" t="str">
@@ -11062,21 +11062,21 @@
       <c r="B31" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="120"/>
-      <c r="D31" s="120"/>
-      <c r="E31" s="130"/>
-      <c r="F31" s="120"/>
-      <c r="G31" s="120"/>
-      <c r="H31" s="120"/>
-      <c r="I31" s="120"/>
-      <c r="J31" s="120"/>
-      <c r="K31" s="118"/>
-      <c r="L31" s="118"/>
-      <c r="M31" s="120"/>
-      <c r="N31" s="130"/>
-      <c r="O31" s="130"/>
-      <c r="P31" s="130"/>
-      <c r="Q31" s="130"/>
+      <c r="C31" s="118"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="118"/>
+      <c r="G31" s="118"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="118"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="124"/>
+      <c r="L31" s="124"/>
+      <c r="M31" s="118"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="121"/>
+      <c r="P31" s="121"/>
+      <c r="Q31" s="121"/>
     </row>
     <row r="32" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A32" s="24" t="str">
@@ -11086,48 +11086,48 @@
       <c r="B32" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C32" s="124">
+      <c r="C32" s="116">
         <v>3</v>
       </c>
-      <c r="D32" s="124" t="s">
+      <c r="D32" s="116" t="s">
         <v>228</v>
       </c>
-      <c r="E32" s="128" t="s">
+      <c r="E32" s="119" t="s">
         <v>229</v>
       </c>
-      <c r="F32" s="124" t="s">
+      <c r="F32" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G32" s="124"/>
-      <c r="H32" s="124" t="s">
+      <c r="G32" s="116"/>
+      <c r="H32" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I32" s="124"/>
-      <c r="J32" s="124">
+      <c r="I32" s="116"/>
+      <c r="J32" s="116">
         <v>3</v>
       </c>
-      <c r="K32" s="117">
+      <c r="K32" s="123">
         <f>J32*12</f>
         <v>36</v>
       </c>
-      <c r="L32" s="117">
+      <c r="L32" s="123">
         <f>36*J32</f>
         <v>108</v>
       </c>
-      <c r="M32" s="124">
+      <c r="M32" s="116">
         <f>SUM(K32:L32)</f>
         <v>144</v>
       </c>
-      <c r="N32" s="128" t="s">
+      <c r="N32" s="119" t="s">
         <v>230</v>
       </c>
-      <c r="O32" s="128" t="s">
+      <c r="O32" s="119" t="s">
         <v>231</v>
       </c>
-      <c r="P32" s="128" t="s">
+      <c r="P32" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q32" s="128" t="s">
+      <c r="Q32" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -11139,21 +11139,21 @@
       <c r="B33" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="119"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="129"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="119"/>
-      <c r="H33" s="119"/>
-      <c r="I33" s="119"/>
-      <c r="J33" s="119"/>
-      <c r="K33" s="117"/>
-      <c r="L33" s="117"/>
-      <c r="M33" s="119"/>
-      <c r="N33" s="129"/>
-      <c r="O33" s="129"/>
-      <c r="P33" s="129"/>
-      <c r="Q33" s="129"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="117"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="117"/>
+      <c r="I33" s="117"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="123"/>
+      <c r="L33" s="123"/>
+      <c r="M33" s="117"/>
+      <c r="N33" s="120"/>
+      <c r="O33" s="120"/>
+      <c r="P33" s="120"/>
+      <c r="Q33" s="120"/>
     </row>
     <row r="34" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="80" t="str">
@@ -11163,21 +11163,21 @@
       <c r="B34" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="120"/>
-      <c r="D34" s="120"/>
-      <c r="E34" s="130"/>
-      <c r="F34" s="120"/>
-      <c r="G34" s="120"/>
-      <c r="H34" s="120"/>
-      <c r="I34" s="120"/>
-      <c r="J34" s="120"/>
-      <c r="K34" s="118"/>
-      <c r="L34" s="118"/>
-      <c r="M34" s="120"/>
-      <c r="N34" s="130"/>
-      <c r="O34" s="130"/>
-      <c r="P34" s="130"/>
-      <c r="Q34" s="130"/>
+      <c r="C34" s="118"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="118"/>
+      <c r="G34" s="118"/>
+      <c r="H34" s="118"/>
+      <c r="I34" s="118"/>
+      <c r="J34" s="118"/>
+      <c r="K34" s="124"/>
+      <c r="L34" s="124"/>
+      <c r="M34" s="118"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="121"/>
+      <c r="P34" s="121"/>
+      <c r="Q34" s="121"/>
     </row>
     <row r="35" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A35" s="24" t="str">
@@ -11187,48 +11187,48 @@
       <c r="B35" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="124">
+      <c r="C35" s="116">
         <v>3</v>
       </c>
-      <c r="D35" s="124" t="s">
+      <c r="D35" s="116" t="s">
         <v>232</v>
       </c>
-      <c r="E35" s="128" t="s">
+      <c r="E35" s="119" t="s">
         <v>233</v>
       </c>
-      <c r="F35" s="124" t="s">
+      <c r="F35" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G35" s="124"/>
-      <c r="H35" s="124" t="s">
+      <c r="G35" s="116"/>
+      <c r="H35" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I35" s="124"/>
-      <c r="J35" s="124">
+      <c r="I35" s="116"/>
+      <c r="J35" s="116">
         <v>4</v>
       </c>
-      <c r="K35" s="117">
+      <c r="K35" s="123">
         <f>J35*12</f>
         <v>48</v>
       </c>
-      <c r="L35" s="117">
+      <c r="L35" s="123">
         <f>36*J35</f>
         <v>144</v>
       </c>
-      <c r="M35" s="124">
+      <c r="M35" s="116">
         <f>SUM(K35:L35)</f>
         <v>192</v>
       </c>
-      <c r="N35" s="128" t="s">
+      <c r="N35" s="119" t="s">
         <v>234</v>
       </c>
-      <c r="O35" s="128" t="s">
+      <c r="O35" s="119" t="s">
         <v>209</v>
       </c>
-      <c r="P35" s="128" t="s">
+      <c r="P35" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q35" s="128" t="s">
+      <c r="Q35" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -11240,21 +11240,21 @@
       <c r="B36" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C36" s="119"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="129"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="119"/>
-      <c r="H36" s="119"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="119"/>
-      <c r="K36" s="117"/>
-      <c r="L36" s="117"/>
-      <c r="M36" s="119"/>
-      <c r="N36" s="129"/>
-      <c r="O36" s="129"/>
-      <c r="P36" s="129"/>
-      <c r="Q36" s="129"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="117"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="123"/>
+      <c r="L36" s="123"/>
+      <c r="M36" s="117"/>
+      <c r="N36" s="120"/>
+      <c r="O36" s="120"/>
+      <c r="P36" s="120"/>
+      <c r="Q36" s="120"/>
     </row>
     <row r="37" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="80" t="str">
@@ -11264,21 +11264,21 @@
       <c r="B37" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C37" s="120"/>
-      <c r="D37" s="120"/>
-      <c r="E37" s="130"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="120"/>
-      <c r="I37" s="120"/>
-      <c r="J37" s="120"/>
-      <c r="K37" s="118"/>
-      <c r="L37" s="118"/>
-      <c r="M37" s="120"/>
-      <c r="N37" s="130"/>
-      <c r="O37" s="130"/>
-      <c r="P37" s="130"/>
-      <c r="Q37" s="130"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="118"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="118"/>
+      <c r="I37" s="118"/>
+      <c r="J37" s="118"/>
+      <c r="K37" s="124"/>
+      <c r="L37" s="124"/>
+      <c r="M37" s="118"/>
+      <c r="N37" s="121"/>
+      <c r="O37" s="121"/>
+      <c r="P37" s="121"/>
+      <c r="Q37" s="121"/>
       <c r="R37" s="50">
         <f>SUM(J27:J37)</f>
         <v>16</v>
@@ -11349,48 +11349,48 @@
       <c r="B39" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C39" s="124">
+      <c r="C39" s="116">
         <v>4</v>
       </c>
-      <c r="D39" s="124" t="s">
+      <c r="D39" s="116" t="s">
         <v>238</v>
       </c>
-      <c r="E39" s="128" t="s">
+      <c r="E39" s="119" t="s">
         <v>239</v>
       </c>
-      <c r="F39" s="124" t="s">
+      <c r="F39" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G39" s="124"/>
-      <c r="H39" s="124" t="s">
+      <c r="G39" s="116"/>
+      <c r="H39" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I39" s="124"/>
-      <c r="J39" s="124">
+      <c r="I39" s="116"/>
+      <c r="J39" s="116">
         <v>3</v>
       </c>
-      <c r="K39" s="117">
+      <c r="K39" s="123">
         <f>J39*12</f>
         <v>36</v>
       </c>
-      <c r="L39" s="117">
+      <c r="L39" s="123">
         <f>36*J39</f>
         <v>108</v>
       </c>
-      <c r="M39" s="124">
+      <c r="M39" s="116">
         <f>SUM(K39:L39)</f>
         <v>144</v>
       </c>
-      <c r="N39" s="128" t="s">
+      <c r="N39" s="119" t="s">
         <v>240</v>
       </c>
-      <c r="O39" s="128" t="s">
+      <c r="O39" s="119" t="s">
         <v>241</v>
       </c>
-      <c r="P39" s="128" t="s">
+      <c r="P39" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q39" s="128" t="s">
+      <c r="Q39" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -11402,21 +11402,21 @@
       <c r="B40" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C40" s="119"/>
-      <c r="D40" s="119"/>
-      <c r="E40" s="129"/>
-      <c r="F40" s="119"/>
-      <c r="G40" s="119"/>
-      <c r="H40" s="119"/>
-      <c r="I40" s="119"/>
-      <c r="J40" s="119"/>
-      <c r="K40" s="117"/>
-      <c r="L40" s="117"/>
-      <c r="M40" s="119"/>
-      <c r="N40" s="129"/>
-      <c r="O40" s="129"/>
-      <c r="P40" s="129"/>
-      <c r="Q40" s="129"/>
+      <c r="C40" s="117"/>
+      <c r="D40" s="117"/>
+      <c r="E40" s="120"/>
+      <c r="F40" s="117"/>
+      <c r="G40" s="117"/>
+      <c r="H40" s="117"/>
+      <c r="I40" s="117"/>
+      <c r="J40" s="117"/>
+      <c r="K40" s="123"/>
+      <c r="L40" s="123"/>
+      <c r="M40" s="117"/>
+      <c r="N40" s="120"/>
+      <c r="O40" s="120"/>
+      <c r="P40" s="120"/>
+      <c r="Q40" s="120"/>
     </row>
     <row r="41" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="80" t="str">
@@ -11426,21 +11426,21 @@
       <c r="B41" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="120"/>
-      <c r="D41" s="120"/>
-      <c r="E41" s="130"/>
-      <c r="F41" s="120"/>
-      <c r="G41" s="120"/>
-      <c r="H41" s="120"/>
-      <c r="I41" s="120"/>
-      <c r="J41" s="120"/>
-      <c r="K41" s="118"/>
-      <c r="L41" s="118"/>
-      <c r="M41" s="120"/>
-      <c r="N41" s="130"/>
-      <c r="O41" s="130"/>
-      <c r="P41" s="130"/>
-      <c r="Q41" s="130"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="121"/>
+      <c r="F41" s="118"/>
+      <c r="G41" s="118"/>
+      <c r="H41" s="118"/>
+      <c r="I41" s="118"/>
+      <c r="J41" s="118"/>
+      <c r="K41" s="124"/>
+      <c r="L41" s="124"/>
+      <c r="M41" s="118"/>
+      <c r="N41" s="121"/>
+      <c r="O41" s="121"/>
+      <c r="P41" s="121"/>
+      <c r="Q41" s="121"/>
     </row>
     <row r="42" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A42" s="24" t="str">
@@ -11450,48 +11450,48 @@
       <c r="B42" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="124">
+      <c r="C42" s="116">
         <v>4</v>
       </c>
-      <c r="D42" s="124" t="s">
+      <c r="D42" s="116" t="s">
         <v>242</v>
       </c>
-      <c r="E42" s="131" t="s">
+      <c r="E42" s="126" t="s">
         <v>243</v>
       </c>
-      <c r="F42" s="124" t="s">
+      <c r="F42" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G42" s="124"/>
-      <c r="H42" s="124" t="s">
+      <c r="G42" s="116"/>
+      <c r="H42" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I42" s="124"/>
-      <c r="J42" s="124">
+      <c r="I42" s="116"/>
+      <c r="J42" s="116">
         <v>3</v>
       </c>
-      <c r="K42" s="124">
+      <c r="K42" s="116">
         <f>J42*12</f>
         <v>36</v>
       </c>
-      <c r="L42" s="124">
+      <c r="L42" s="116">
         <f>36*J42</f>
         <v>108</v>
       </c>
-      <c r="M42" s="124">
+      <c r="M42" s="116">
         <f>SUM(K42:L42)</f>
         <v>144</v>
       </c>
-      <c r="N42" s="128" t="s">
+      <c r="N42" s="119" t="s">
         <v>244</v>
       </c>
-      <c r="O42" s="128" t="s">
+      <c r="O42" s="119" t="s">
         <v>241</v>
       </c>
-      <c r="P42" s="128" t="s">
+      <c r="P42" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q42" s="128" t="s">
+      <c r="Q42" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -11503,21 +11503,21 @@
       <c r="B43" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="119"/>
-      <c r="D43" s="119"/>
-      <c r="E43" s="121"/>
-      <c r="F43" s="119"/>
-      <c r="G43" s="119"/>
-      <c r="H43" s="119"/>
-      <c r="I43" s="119"/>
-      <c r="J43" s="119"/>
-      <c r="K43" s="119"/>
-      <c r="L43" s="119"/>
-      <c r="M43" s="119"/>
-      <c r="N43" s="129"/>
-      <c r="O43" s="129"/>
-      <c r="P43" s="129"/>
-      <c r="Q43" s="129"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="127"/>
+      <c r="F43" s="117"/>
+      <c r="G43" s="117"/>
+      <c r="H43" s="117"/>
+      <c r="I43" s="117"/>
+      <c r="J43" s="117"/>
+      <c r="K43" s="117"/>
+      <c r="L43" s="117"/>
+      <c r="M43" s="117"/>
+      <c r="N43" s="120"/>
+      <c r="O43" s="120"/>
+      <c r="P43" s="120"/>
+      <c r="Q43" s="120"/>
     </row>
     <row r="44" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="str">
@@ -11527,21 +11527,21 @@
       <c r="B44" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C44" s="119"/>
-      <c r="D44" s="119"/>
-      <c r="E44" s="121"/>
-      <c r="F44" s="119"/>
-      <c r="G44" s="119"/>
-      <c r="H44" s="119"/>
-      <c r="I44" s="119"/>
-      <c r="J44" s="119"/>
-      <c r="K44" s="119"/>
-      <c r="L44" s="119"/>
-      <c r="M44" s="119"/>
-      <c r="N44" s="129"/>
-      <c r="O44" s="129"/>
-      <c r="P44" s="129"/>
-      <c r="Q44" s="129"/>
+      <c r="C44" s="117"/>
+      <c r="D44" s="117"/>
+      <c r="E44" s="127"/>
+      <c r="F44" s="117"/>
+      <c r="G44" s="117"/>
+      <c r="H44" s="117"/>
+      <c r="I44" s="117"/>
+      <c r="J44" s="117"/>
+      <c r="K44" s="117"/>
+      <c r="L44" s="117"/>
+      <c r="M44" s="117"/>
+      <c r="N44" s="120"/>
+      <c r="O44" s="120"/>
+      <c r="P44" s="120"/>
+      <c r="Q44" s="120"/>
     </row>
     <row r="45" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="80" t="str">
@@ -11551,21 +11551,21 @@
       <c r="B45" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="120"/>
-      <c r="D45" s="120"/>
-      <c r="E45" s="122"/>
-      <c r="F45" s="120"/>
-      <c r="G45" s="120"/>
-      <c r="H45" s="120"/>
-      <c r="I45" s="120"/>
-      <c r="J45" s="120"/>
-      <c r="K45" s="120"/>
-      <c r="L45" s="120"/>
-      <c r="M45" s="120"/>
-      <c r="N45" s="130"/>
-      <c r="O45" s="130"/>
-      <c r="P45" s="130"/>
-      <c r="Q45" s="130"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="118"/>
+      <c r="E45" s="128"/>
+      <c r="F45" s="118"/>
+      <c r="G45" s="118"/>
+      <c r="H45" s="118"/>
+      <c r="I45" s="118"/>
+      <c r="J45" s="118"/>
+      <c r="K45" s="118"/>
+      <c r="L45" s="118"/>
+      <c r="M45" s="118"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="121"/>
+      <c r="P45" s="121"/>
+      <c r="Q45" s="121"/>
     </row>
     <row r="46" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A46" s="24" t="str">
@@ -11575,48 +11575,48 @@
       <c r="B46" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C46" s="124">
+      <c r="C46" s="116">
         <v>4</v>
       </c>
-      <c r="D46" s="124" t="s">
+      <c r="D46" s="116" t="s">
         <v>245</v>
       </c>
-      <c r="E46" s="128" t="s">
+      <c r="E46" s="119" t="s">
         <v>246</v>
       </c>
-      <c r="F46" s="124" t="s">
+      <c r="F46" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G46" s="124"/>
-      <c r="H46" s="124" t="s">
+      <c r="G46" s="116"/>
+      <c r="H46" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I46" s="124"/>
-      <c r="J46" s="124">
+      <c r="I46" s="116"/>
+      <c r="J46" s="116">
         <v>4</v>
       </c>
-      <c r="K46" s="124">
+      <c r="K46" s="116">
         <f>J46*12</f>
         <v>48</v>
       </c>
-      <c r="L46" s="124">
+      <c r="L46" s="116">
         <f>36*J46</f>
         <v>144</v>
       </c>
-      <c r="M46" s="124">
+      <c r="M46" s="116">
         <f>SUM(K46:L46)</f>
         <v>192</v>
       </c>
-      <c r="N46" s="128" t="s">
+      <c r="N46" s="119" t="s">
         <v>247</v>
       </c>
-      <c r="O46" s="128" t="s">
+      <c r="O46" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="P46" s="128" t="s">
+      <c r="P46" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q46" s="128" t="s">
+      <c r="Q46" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -11628,21 +11628,21 @@
       <c r="B47" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C47" s="119"/>
-      <c r="D47" s="119"/>
-      <c r="E47" s="129"/>
-      <c r="F47" s="119"/>
-      <c r="G47" s="119"/>
-      <c r="H47" s="119"/>
-      <c r="I47" s="119"/>
-      <c r="J47" s="119"/>
-      <c r="K47" s="119"/>
-      <c r="L47" s="119"/>
-      <c r="M47" s="119"/>
-      <c r="N47" s="129"/>
-      <c r="O47" s="129"/>
-      <c r="P47" s="129"/>
-      <c r="Q47" s="129"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="120"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="117"/>
+      <c r="J47" s="117"/>
+      <c r="K47" s="117"/>
+      <c r="L47" s="117"/>
+      <c r="M47" s="117"/>
+      <c r="N47" s="120"/>
+      <c r="O47" s="120"/>
+      <c r="P47" s="120"/>
+      <c r="Q47" s="120"/>
     </row>
     <row r="48" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A48" s="24" t="str">
@@ -11652,21 +11652,21 @@
       <c r="B48" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="119"/>
-      <c r="D48" s="119"/>
-      <c r="E48" s="129"/>
-      <c r="F48" s="119"/>
-      <c r="G48" s="119"/>
-      <c r="H48" s="119"/>
-      <c r="I48" s="119"/>
-      <c r="J48" s="119"/>
-      <c r="K48" s="119"/>
-      <c r="L48" s="119"/>
-      <c r="M48" s="119"/>
-      <c r="N48" s="129"/>
-      <c r="O48" s="129"/>
-      <c r="P48" s="129"/>
-      <c r="Q48" s="129"/>
+      <c r="C48" s="117"/>
+      <c r="D48" s="117"/>
+      <c r="E48" s="120"/>
+      <c r="F48" s="117"/>
+      <c r="G48" s="117"/>
+      <c r="H48" s="117"/>
+      <c r="I48" s="117"/>
+      <c r="J48" s="117"/>
+      <c r="K48" s="117"/>
+      <c r="L48" s="117"/>
+      <c r="M48" s="117"/>
+      <c r="N48" s="120"/>
+      <c r="O48" s="120"/>
+      <c r="P48" s="120"/>
+      <c r="Q48" s="120"/>
     </row>
     <row r="49" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A49" s="24" t="str">
@@ -11676,21 +11676,21 @@
       <c r="B49" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="119"/>
-      <c r="D49" s="119"/>
-      <c r="E49" s="129"/>
-      <c r="F49" s="119"/>
-      <c r="G49" s="119"/>
-      <c r="H49" s="119"/>
-      <c r="I49" s="119"/>
-      <c r="J49" s="119"/>
-      <c r="K49" s="119"/>
-      <c r="L49" s="119"/>
-      <c r="M49" s="119"/>
-      <c r="N49" s="129"/>
-      <c r="O49" s="129"/>
-      <c r="P49" s="129"/>
-      <c r="Q49" s="129"/>
+      <c r="C49" s="117"/>
+      <c r="D49" s="117"/>
+      <c r="E49" s="120"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="117"/>
+      <c r="H49" s="117"/>
+      <c r="I49" s="117"/>
+      <c r="J49" s="117"/>
+      <c r="K49" s="117"/>
+      <c r="L49" s="117"/>
+      <c r="M49" s="117"/>
+      <c r="N49" s="120"/>
+      <c r="O49" s="120"/>
+      <c r="P49" s="120"/>
+      <c r="Q49" s="120"/>
     </row>
     <row r="50" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="80" t="str">
@@ -11700,21 +11700,21 @@
       <c r="B50" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C50" s="120"/>
-      <c r="D50" s="120"/>
-      <c r="E50" s="130"/>
-      <c r="F50" s="120"/>
-      <c r="G50" s="120"/>
-      <c r="H50" s="120"/>
-      <c r="I50" s="120"/>
-      <c r="J50" s="120"/>
-      <c r="K50" s="120"/>
-      <c r="L50" s="120"/>
-      <c r="M50" s="120"/>
-      <c r="N50" s="130"/>
-      <c r="O50" s="130"/>
-      <c r="P50" s="130"/>
-      <c r="Q50" s="130"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="118"/>
+      <c r="E50" s="121"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="118"/>
+      <c r="H50" s="118"/>
+      <c r="I50" s="118"/>
+      <c r="J50" s="118"/>
+      <c r="K50" s="118"/>
+      <c r="L50" s="118"/>
+      <c r="M50" s="118"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="121"/>
+      <c r="P50" s="121"/>
+      <c r="Q50" s="121"/>
     </row>
     <row r="51" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A51" s="24" t="str">
@@ -11724,48 +11724,48 @@
       <c r="B51" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C51" s="124">
+      <c r="C51" s="116">
         <v>4</v>
       </c>
-      <c r="D51" s="124" t="s">
+      <c r="D51" s="116" t="s">
         <v>248</v>
       </c>
-      <c r="E51" s="128" t="s">
+      <c r="E51" s="119" t="s">
         <v>249</v>
       </c>
-      <c r="F51" s="124" t="s">
+      <c r="F51" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G51" s="124"/>
-      <c r="H51" s="124" t="s">
+      <c r="G51" s="116"/>
+      <c r="H51" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I51" s="124"/>
-      <c r="J51" s="124">
+      <c r="I51" s="116"/>
+      <c r="J51" s="116">
         <v>3</v>
       </c>
-      <c r="K51" s="124">
+      <c r="K51" s="116">
         <f>J51*12</f>
         <v>36</v>
       </c>
-      <c r="L51" s="124">
+      <c r="L51" s="116">
         <f>36*J51</f>
         <v>108</v>
       </c>
-      <c r="M51" s="124">
+      <c r="M51" s="116">
         <f>SUM(K51:L51)</f>
         <v>144</v>
       </c>
-      <c r="N51" s="128" t="s">
+      <c r="N51" s="119" t="s">
         <v>250</v>
       </c>
-      <c r="O51" s="128" t="s">
+      <c r="O51" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="P51" s="128" t="s">
+      <c r="P51" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q51" s="128" t="s">
+      <c r="Q51" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -11777,21 +11777,21 @@
       <c r="B52" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C52" s="119"/>
-      <c r="D52" s="119"/>
-      <c r="E52" s="129"/>
-      <c r="F52" s="119"/>
-      <c r="G52" s="119"/>
-      <c r="H52" s="119"/>
-      <c r="I52" s="119"/>
-      <c r="J52" s="119"/>
-      <c r="K52" s="119"/>
-      <c r="L52" s="119"/>
-      <c r="M52" s="119"/>
-      <c r="N52" s="129"/>
-      <c r="O52" s="129"/>
-      <c r="P52" s="129"/>
-      <c r="Q52" s="129"/>
+      <c r="C52" s="117"/>
+      <c r="D52" s="117"/>
+      <c r="E52" s="120"/>
+      <c r="F52" s="117"/>
+      <c r="G52" s="117"/>
+      <c r="H52" s="117"/>
+      <c r="I52" s="117"/>
+      <c r="J52" s="117"/>
+      <c r="K52" s="117"/>
+      <c r="L52" s="117"/>
+      <c r="M52" s="117"/>
+      <c r="N52" s="120"/>
+      <c r="O52" s="120"/>
+      <c r="P52" s="120"/>
+      <c r="Q52" s="120"/>
     </row>
     <row r="53" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A53" s="24" t="str">
@@ -11801,21 +11801,21 @@
       <c r="B53" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C53" s="119"/>
-      <c r="D53" s="119"/>
-      <c r="E53" s="129"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="119"/>
-      <c r="H53" s="119"/>
-      <c r="I53" s="119"/>
-      <c r="J53" s="119"/>
-      <c r="K53" s="119"/>
-      <c r="L53" s="119"/>
-      <c r="M53" s="119"/>
-      <c r="N53" s="129"/>
-      <c r="O53" s="129"/>
-      <c r="P53" s="129"/>
-      <c r="Q53" s="129"/>
+      <c r="C53" s="117"/>
+      <c r="D53" s="117"/>
+      <c r="E53" s="120"/>
+      <c r="F53" s="117"/>
+      <c r="G53" s="117"/>
+      <c r="H53" s="117"/>
+      <c r="I53" s="117"/>
+      <c r="J53" s="117"/>
+      <c r="K53" s="117"/>
+      <c r="L53" s="117"/>
+      <c r="M53" s="117"/>
+      <c r="N53" s="120"/>
+      <c r="O53" s="120"/>
+      <c r="P53" s="120"/>
+      <c r="Q53" s="120"/>
     </row>
     <row r="54" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="str">
@@ -11825,21 +11825,21 @@
       <c r="B54" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C54" s="119"/>
-      <c r="D54" s="119"/>
-      <c r="E54" s="129"/>
-      <c r="F54" s="119"/>
-      <c r="G54" s="119"/>
-      <c r="H54" s="119"/>
-      <c r="I54" s="119"/>
-      <c r="J54" s="119"/>
-      <c r="K54" s="119"/>
-      <c r="L54" s="119"/>
-      <c r="M54" s="119"/>
-      <c r="N54" s="129"/>
-      <c r="O54" s="129"/>
-      <c r="P54" s="129"/>
-      <c r="Q54" s="129"/>
+      <c r="C54" s="117"/>
+      <c r="D54" s="117"/>
+      <c r="E54" s="120"/>
+      <c r="F54" s="117"/>
+      <c r="G54" s="117"/>
+      <c r="H54" s="117"/>
+      <c r="I54" s="117"/>
+      <c r="J54" s="117"/>
+      <c r="K54" s="117"/>
+      <c r="L54" s="117"/>
+      <c r="M54" s="117"/>
+      <c r="N54" s="120"/>
+      <c r="O54" s="120"/>
+      <c r="P54" s="120"/>
+      <c r="Q54" s="120"/>
     </row>
     <row r="55" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="80" t="str">
@@ -11849,21 +11849,21 @@
       <c r="B55" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="120"/>
-      <c r="D55" s="120"/>
-      <c r="E55" s="130"/>
-      <c r="F55" s="120"/>
-      <c r="G55" s="120"/>
-      <c r="H55" s="120"/>
-      <c r="I55" s="120"/>
-      <c r="J55" s="120"/>
-      <c r="K55" s="120"/>
-      <c r="L55" s="120"/>
-      <c r="M55" s="120"/>
-      <c r="N55" s="130"/>
-      <c r="O55" s="130"/>
-      <c r="P55" s="130"/>
-      <c r="Q55" s="130"/>
+      <c r="C55" s="118"/>
+      <c r="D55" s="118"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="118"/>
+      <c r="G55" s="118"/>
+      <c r="H55" s="118"/>
+      <c r="I55" s="118"/>
+      <c r="J55" s="118"/>
+      <c r="K55" s="118"/>
+      <c r="L55" s="118"/>
+      <c r="M55" s="118"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="121"/>
+      <c r="P55" s="121"/>
+      <c r="Q55" s="121"/>
       <c r="R55" s="50">
         <f>SUM(J38:J55)</f>
         <v>16</v>
@@ -11881,48 +11881,48 @@
       <c r="B56" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="124">
+      <c r="C56" s="116">
         <v>5</v>
       </c>
-      <c r="D56" s="124" t="s">
+      <c r="D56" s="116" t="s">
         <v>251</v>
       </c>
-      <c r="E56" s="128" t="s">
+      <c r="E56" s="119" t="s">
         <v>252</v>
       </c>
-      <c r="F56" s="124" t="s">
+      <c r="F56" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G56" s="124"/>
-      <c r="H56" s="124" t="s">
+      <c r="G56" s="116"/>
+      <c r="H56" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I56" s="124"/>
-      <c r="J56" s="124">
+      <c r="I56" s="116"/>
+      <c r="J56" s="116">
         <v>3</v>
       </c>
-      <c r="K56" s="124">
+      <c r="K56" s="116">
         <f>J56*12</f>
         <v>36</v>
       </c>
-      <c r="L56" s="124">
+      <c r="L56" s="116">
         <f>36*J56</f>
         <v>108</v>
       </c>
-      <c r="M56" s="124">
+      <c r="M56" s="116">
         <f>SUM(K56:L56)</f>
         <v>144</v>
       </c>
-      <c r="N56" s="128" t="s">
+      <c r="N56" s="119" t="s">
         <v>253</v>
       </c>
-      <c r="O56" s="128" t="s">
+      <c r="O56" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="P56" s="128" t="s">
+      <c r="P56" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q56" s="128" t="s">
+      <c r="Q56" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -11934,21 +11934,21 @@
       <c r="B57" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C57" s="119"/>
-      <c r="D57" s="119"/>
-      <c r="E57" s="129"/>
-      <c r="F57" s="119"/>
-      <c r="G57" s="119"/>
-      <c r="H57" s="119"/>
-      <c r="I57" s="119"/>
-      <c r="J57" s="119"/>
-      <c r="K57" s="119"/>
-      <c r="L57" s="119"/>
-      <c r="M57" s="119"/>
-      <c r="N57" s="129"/>
-      <c r="O57" s="129"/>
-      <c r="P57" s="129"/>
-      <c r="Q57" s="129"/>
+      <c r="C57" s="117"/>
+      <c r="D57" s="117"/>
+      <c r="E57" s="120"/>
+      <c r="F57" s="117"/>
+      <c r="G57" s="117"/>
+      <c r="H57" s="117"/>
+      <c r="I57" s="117"/>
+      <c r="J57" s="117"/>
+      <c r="K57" s="117"/>
+      <c r="L57" s="117"/>
+      <c r="M57" s="117"/>
+      <c r="N57" s="120"/>
+      <c r="O57" s="120"/>
+      <c r="P57" s="120"/>
+      <c r="Q57" s="120"/>
     </row>
     <row r="58" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A58" s="24" t="str">
@@ -11958,21 +11958,21 @@
       <c r="B58" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="119"/>
-      <c r="D58" s="119"/>
-      <c r="E58" s="129"/>
-      <c r="F58" s="119"/>
-      <c r="G58" s="119"/>
-      <c r="H58" s="119"/>
-      <c r="I58" s="119"/>
-      <c r="J58" s="119"/>
-      <c r="K58" s="119"/>
-      <c r="L58" s="119"/>
-      <c r="M58" s="119"/>
-      <c r="N58" s="129"/>
-      <c r="O58" s="129"/>
-      <c r="P58" s="129"/>
-      <c r="Q58" s="129"/>
+      <c r="C58" s="117"/>
+      <c r="D58" s="117"/>
+      <c r="E58" s="120"/>
+      <c r="F58" s="117"/>
+      <c r="G58" s="117"/>
+      <c r="H58" s="117"/>
+      <c r="I58" s="117"/>
+      <c r="J58" s="117"/>
+      <c r="K58" s="117"/>
+      <c r="L58" s="117"/>
+      <c r="M58" s="117"/>
+      <c r="N58" s="120"/>
+      <c r="O58" s="120"/>
+      <c r="P58" s="120"/>
+      <c r="Q58" s="120"/>
     </row>
     <row r="59" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="24" t="str">
@@ -11982,21 +11982,21 @@
       <c r="B59" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C59" s="119"/>
-      <c r="D59" s="119"/>
-      <c r="E59" s="129"/>
-      <c r="F59" s="119"/>
-      <c r="G59" s="119"/>
-      <c r="H59" s="119"/>
-      <c r="I59" s="119"/>
-      <c r="J59" s="119"/>
-      <c r="K59" s="119"/>
-      <c r="L59" s="119"/>
-      <c r="M59" s="119"/>
-      <c r="N59" s="129"/>
-      <c r="O59" s="129"/>
-      <c r="P59" s="129"/>
-      <c r="Q59" s="129"/>
+      <c r="C59" s="117"/>
+      <c r="D59" s="117"/>
+      <c r="E59" s="120"/>
+      <c r="F59" s="117"/>
+      <c r="G59" s="117"/>
+      <c r="H59" s="117"/>
+      <c r="I59" s="117"/>
+      <c r="J59" s="117"/>
+      <c r="K59" s="117"/>
+      <c r="L59" s="117"/>
+      <c r="M59" s="117"/>
+      <c r="N59" s="120"/>
+      <c r="O59" s="120"/>
+      <c r="P59" s="120"/>
+      <c r="Q59" s="120"/>
     </row>
     <row r="60" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="80" t="str">
@@ -12006,21 +12006,21 @@
       <c r="B60" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C60" s="120"/>
-      <c r="D60" s="120"/>
-      <c r="E60" s="130"/>
-      <c r="F60" s="120"/>
-      <c r="G60" s="120"/>
-      <c r="H60" s="120"/>
-      <c r="I60" s="120"/>
-      <c r="J60" s="120"/>
-      <c r="K60" s="120"/>
-      <c r="L60" s="120"/>
-      <c r="M60" s="120"/>
-      <c r="N60" s="130"/>
-      <c r="O60" s="130"/>
-      <c r="P60" s="130"/>
-      <c r="Q60" s="130"/>
+      <c r="C60" s="118"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="121"/>
+      <c r="F60" s="118"/>
+      <c r="G60" s="118"/>
+      <c r="H60" s="118"/>
+      <c r="I60" s="118"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="118"/>
+      <c r="L60" s="118"/>
+      <c r="M60" s="118"/>
+      <c r="N60" s="121"/>
+      <c r="O60" s="121"/>
+      <c r="P60" s="121"/>
+      <c r="Q60" s="121"/>
     </row>
     <row r="61" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="str">
@@ -12030,48 +12030,48 @@
       <c r="B61" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="124">
+      <c r="C61" s="116">
         <v>5</v>
       </c>
-      <c r="D61" s="124" t="s">
+      <c r="D61" s="116" t="s">
         <v>254</v>
       </c>
-      <c r="E61" s="128" t="s">
+      <c r="E61" s="119" t="s">
         <v>255</v>
       </c>
-      <c r="F61" s="124" t="s">
+      <c r="F61" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G61" s="124"/>
-      <c r="H61" s="124" t="s">
+      <c r="G61" s="116"/>
+      <c r="H61" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I61" s="124"/>
-      <c r="J61" s="124">
+      <c r="I61" s="116"/>
+      <c r="J61" s="116">
         <v>3</v>
       </c>
-      <c r="K61" s="124">
+      <c r="K61" s="116">
         <f>J61*12</f>
         <v>36</v>
       </c>
-      <c r="L61" s="124">
+      <c r="L61" s="116">
         <f>36*J61</f>
         <v>108</v>
       </c>
-      <c r="M61" s="124">
+      <c r="M61" s="116">
         <f>SUM(K61:L61)</f>
         <v>144</v>
       </c>
-      <c r="N61" s="128" t="s">
+      <c r="N61" s="119" t="s">
         <v>256</v>
       </c>
-      <c r="O61" s="128" t="s">
+      <c r="O61" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="P61" s="128" t="s">
+      <c r="P61" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q61" s="128" t="s">
+      <c r="Q61" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -12083,21 +12083,21 @@
       <c r="B62" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C62" s="119"/>
-      <c r="D62" s="119"/>
-      <c r="E62" s="129"/>
-      <c r="F62" s="119"/>
-      <c r="G62" s="119"/>
-      <c r="H62" s="119"/>
-      <c r="I62" s="119"/>
-      <c r="J62" s="119"/>
-      <c r="K62" s="119"/>
-      <c r="L62" s="119"/>
-      <c r="M62" s="119"/>
-      <c r="N62" s="129"/>
-      <c r="O62" s="129"/>
-      <c r="P62" s="129"/>
-      <c r="Q62" s="129"/>
+      <c r="C62" s="117"/>
+      <c r="D62" s="117"/>
+      <c r="E62" s="120"/>
+      <c r="F62" s="117"/>
+      <c r="G62" s="117"/>
+      <c r="H62" s="117"/>
+      <c r="I62" s="117"/>
+      <c r="J62" s="117"/>
+      <c r="K62" s="117"/>
+      <c r="L62" s="117"/>
+      <c r="M62" s="117"/>
+      <c r="N62" s="120"/>
+      <c r="O62" s="120"/>
+      <c r="P62" s="120"/>
+      <c r="Q62" s="120"/>
     </row>
     <row r="63" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="str">
@@ -12107,21 +12107,21 @@
       <c r="B63" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C63" s="119"/>
-      <c r="D63" s="119"/>
-      <c r="E63" s="129"/>
-      <c r="F63" s="119"/>
-      <c r="G63" s="119"/>
-      <c r="H63" s="119"/>
-      <c r="I63" s="119"/>
-      <c r="J63" s="119"/>
-      <c r="K63" s="119"/>
-      <c r="L63" s="119"/>
-      <c r="M63" s="119"/>
-      <c r="N63" s="129"/>
-      <c r="O63" s="129"/>
-      <c r="P63" s="129"/>
-      <c r="Q63" s="129"/>
+      <c r="C63" s="117"/>
+      <c r="D63" s="117"/>
+      <c r="E63" s="120"/>
+      <c r="F63" s="117"/>
+      <c r="G63" s="117"/>
+      <c r="H63" s="117"/>
+      <c r="I63" s="117"/>
+      <c r="J63" s="117"/>
+      <c r="K63" s="117"/>
+      <c r="L63" s="117"/>
+      <c r="M63" s="117"/>
+      <c r="N63" s="120"/>
+      <c r="O63" s="120"/>
+      <c r="P63" s="120"/>
+      <c r="Q63" s="120"/>
     </row>
     <row r="64" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A64" s="24" t="str">
@@ -12131,21 +12131,21 @@
       <c r="B64" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C64" s="119"/>
-      <c r="D64" s="119"/>
-      <c r="E64" s="129"/>
-      <c r="F64" s="119"/>
-      <c r="G64" s="119"/>
-      <c r="H64" s="119"/>
-      <c r="I64" s="119"/>
-      <c r="J64" s="119"/>
-      <c r="K64" s="119"/>
-      <c r="L64" s="119"/>
-      <c r="M64" s="119"/>
-      <c r="N64" s="129"/>
-      <c r="O64" s="129"/>
-      <c r="P64" s="129"/>
-      <c r="Q64" s="129"/>
+      <c r="C64" s="117"/>
+      <c r="D64" s="117"/>
+      <c r="E64" s="120"/>
+      <c r="F64" s="117"/>
+      <c r="G64" s="117"/>
+      <c r="H64" s="117"/>
+      <c r="I64" s="117"/>
+      <c r="J64" s="117"/>
+      <c r="K64" s="117"/>
+      <c r="L64" s="117"/>
+      <c r="M64" s="117"/>
+      <c r="N64" s="120"/>
+      <c r="O64" s="120"/>
+      <c r="P64" s="120"/>
+      <c r="Q64" s="120"/>
     </row>
     <row r="65" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="80" t="str">
@@ -12155,21 +12155,21 @@
       <c r="B65" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C65" s="120"/>
-      <c r="D65" s="120"/>
-      <c r="E65" s="130"/>
-      <c r="F65" s="120"/>
-      <c r="G65" s="120"/>
-      <c r="H65" s="120"/>
-      <c r="I65" s="120"/>
-      <c r="J65" s="120"/>
-      <c r="K65" s="120"/>
-      <c r="L65" s="120"/>
-      <c r="M65" s="120"/>
-      <c r="N65" s="130"/>
-      <c r="O65" s="130"/>
-      <c r="P65" s="130"/>
-      <c r="Q65" s="130"/>
+      <c r="C65" s="118"/>
+      <c r="D65" s="118"/>
+      <c r="E65" s="121"/>
+      <c r="F65" s="118"/>
+      <c r="G65" s="118"/>
+      <c r="H65" s="118"/>
+      <c r="I65" s="118"/>
+      <c r="J65" s="118"/>
+      <c r="K65" s="118"/>
+      <c r="L65" s="118"/>
+      <c r="M65" s="118"/>
+      <c r="N65" s="121"/>
+      <c r="O65" s="121"/>
+      <c r="P65" s="121"/>
+      <c r="Q65" s="121"/>
     </row>
     <row r="66" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A66" s="24" t="str">
@@ -12179,48 +12179,48 @@
       <c r="B66" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C66" s="124">
+      <c r="C66" s="116">
         <v>5</v>
       </c>
-      <c r="D66" s="124" t="s">
+      <c r="D66" s="116" t="s">
         <v>257</v>
       </c>
-      <c r="E66" s="128" t="s">
+      <c r="E66" s="119" t="s">
         <v>258</v>
       </c>
-      <c r="F66" s="124" t="s">
+      <c r="F66" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G66" s="124"/>
-      <c r="H66" s="124" t="s">
+      <c r="G66" s="116"/>
+      <c r="H66" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I66" s="124"/>
-      <c r="J66" s="124">
+      <c r="I66" s="116"/>
+      <c r="J66" s="116">
         <v>3</v>
       </c>
-      <c r="K66" s="124">
+      <c r="K66" s="116">
         <f>J66*12</f>
         <v>36</v>
       </c>
-      <c r="L66" s="124">
+      <c r="L66" s="116">
         <f>36*J66</f>
         <v>108</v>
       </c>
-      <c r="M66" s="124">
+      <c r="M66" s="116">
         <f>SUM(K66:L66)</f>
         <v>144</v>
       </c>
-      <c r="N66" s="128" t="s">
+      <c r="N66" s="119" t="s">
         <v>259</v>
       </c>
-      <c r="O66" s="128" t="s">
+      <c r="O66" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="P66" s="128" t="s">
+      <c r="P66" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q66" s="128" t="s">
+      <c r="Q66" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -12232,21 +12232,21 @@
       <c r="B67" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C67" s="119"/>
-      <c r="D67" s="119"/>
-      <c r="E67" s="129"/>
-      <c r="F67" s="119"/>
-      <c r="G67" s="119"/>
-      <c r="H67" s="119"/>
-      <c r="I67" s="119"/>
-      <c r="J67" s="119"/>
-      <c r="K67" s="119"/>
-      <c r="L67" s="119"/>
-      <c r="M67" s="119"/>
-      <c r="N67" s="129"/>
-      <c r="O67" s="129"/>
-      <c r="P67" s="129"/>
-      <c r="Q67" s="129"/>
+      <c r="C67" s="117"/>
+      <c r="D67" s="117"/>
+      <c r="E67" s="120"/>
+      <c r="F67" s="117"/>
+      <c r="G67" s="117"/>
+      <c r="H67" s="117"/>
+      <c r="I67" s="117"/>
+      <c r="J67" s="117"/>
+      <c r="K67" s="117"/>
+      <c r="L67" s="117"/>
+      <c r="M67" s="117"/>
+      <c r="N67" s="120"/>
+      <c r="O67" s="120"/>
+      <c r="P67" s="120"/>
+      <c r="Q67" s="120"/>
     </row>
     <row r="68" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A68" s="24" t="str">
@@ -12256,21 +12256,21 @@
       <c r="B68" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C68" s="119"/>
-      <c r="D68" s="119"/>
-      <c r="E68" s="129"/>
-      <c r="F68" s="119"/>
-      <c r="G68" s="119"/>
-      <c r="H68" s="119"/>
-      <c r="I68" s="119"/>
-      <c r="J68" s="119"/>
-      <c r="K68" s="119"/>
-      <c r="L68" s="119"/>
-      <c r="M68" s="119"/>
-      <c r="N68" s="129"/>
-      <c r="O68" s="129"/>
-      <c r="P68" s="129"/>
-      <c r="Q68" s="129"/>
+      <c r="C68" s="117"/>
+      <c r="D68" s="117"/>
+      <c r="E68" s="120"/>
+      <c r="F68" s="117"/>
+      <c r="G68" s="117"/>
+      <c r="H68" s="117"/>
+      <c r="I68" s="117"/>
+      <c r="J68" s="117"/>
+      <c r="K68" s="117"/>
+      <c r="L68" s="117"/>
+      <c r="M68" s="117"/>
+      <c r="N68" s="120"/>
+      <c r="O68" s="120"/>
+      <c r="P68" s="120"/>
+      <c r="Q68" s="120"/>
     </row>
     <row r="69" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A69" s="24" t="str">
@@ -12280,21 +12280,21 @@
       <c r="B69" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C69" s="119"/>
-      <c r="D69" s="119"/>
-      <c r="E69" s="129"/>
-      <c r="F69" s="119"/>
-      <c r="G69" s="119"/>
-      <c r="H69" s="119"/>
-      <c r="I69" s="119"/>
-      <c r="J69" s="119"/>
-      <c r="K69" s="119"/>
-      <c r="L69" s="119"/>
-      <c r="M69" s="119"/>
-      <c r="N69" s="129"/>
-      <c r="O69" s="129"/>
-      <c r="P69" s="129"/>
-      <c r="Q69" s="129"/>
+      <c r="C69" s="117"/>
+      <c r="D69" s="117"/>
+      <c r="E69" s="120"/>
+      <c r="F69" s="117"/>
+      <c r="G69" s="117"/>
+      <c r="H69" s="117"/>
+      <c r="I69" s="117"/>
+      <c r="J69" s="117"/>
+      <c r="K69" s="117"/>
+      <c r="L69" s="117"/>
+      <c r="M69" s="117"/>
+      <c r="N69" s="120"/>
+      <c r="O69" s="120"/>
+      <c r="P69" s="120"/>
+      <c r="Q69" s="120"/>
     </row>
     <row r="70" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="80" t="str">
@@ -12304,21 +12304,21 @@
       <c r="B70" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C70" s="120"/>
-      <c r="D70" s="120"/>
-      <c r="E70" s="132"/>
-      <c r="F70" s="120"/>
-      <c r="G70" s="120"/>
-      <c r="H70" s="120"/>
-      <c r="I70" s="120"/>
-      <c r="J70" s="120"/>
-      <c r="K70" s="120"/>
-      <c r="L70" s="120"/>
-      <c r="M70" s="120"/>
-      <c r="N70" s="130"/>
-      <c r="O70" s="130"/>
-      <c r="P70" s="130"/>
-      <c r="Q70" s="130"/>
+      <c r="C70" s="118"/>
+      <c r="D70" s="118"/>
+      <c r="E70" s="125"/>
+      <c r="F70" s="118"/>
+      <c r="G70" s="118"/>
+      <c r="H70" s="118"/>
+      <c r="I70" s="118"/>
+      <c r="J70" s="118"/>
+      <c r="K70" s="118"/>
+      <c r="L70" s="118"/>
+      <c r="M70" s="118"/>
+      <c r="N70" s="121"/>
+      <c r="O70" s="121"/>
+      <c r="P70" s="121"/>
+      <c r="Q70" s="121"/>
     </row>
     <row r="71" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A71" s="24" t="str">
@@ -12328,48 +12328,48 @@
       <c r="B71" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C71" s="124">
+      <c r="C71" s="116">
         <v>5</v>
       </c>
-      <c r="D71" s="124" t="s">
+      <c r="D71" s="116" t="s">
         <v>260</v>
       </c>
-      <c r="E71" s="129" t="s">
+      <c r="E71" s="120" t="s">
         <v>261</v>
       </c>
-      <c r="F71" s="124" t="s">
+      <c r="F71" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G71" s="124"/>
-      <c r="H71" s="124" t="s">
+      <c r="G71" s="116"/>
+      <c r="H71" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I71" s="124"/>
-      <c r="J71" s="124">
+      <c r="I71" s="116"/>
+      <c r="J71" s="116">
         <v>3</v>
       </c>
-      <c r="K71" s="124">
+      <c r="K71" s="116">
         <f>J71*12</f>
         <v>36</v>
       </c>
-      <c r="L71" s="124">
+      <c r="L71" s="116">
         <f>36*J71</f>
         <v>108</v>
       </c>
-      <c r="M71" s="124">
+      <c r="M71" s="116">
         <f>SUM(K71:L71)</f>
         <v>144</v>
       </c>
-      <c r="N71" s="128" t="s">
+      <c r="N71" s="119" t="s">
         <v>262</v>
       </c>
-      <c r="O71" s="128" t="s">
+      <c r="O71" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="P71" s="128" t="s">
+      <c r="P71" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q71" s="128" t="s">
+      <c r="Q71" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -12381,21 +12381,21 @@
       <c r="B72" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C72" s="119"/>
-      <c r="D72" s="119"/>
-      <c r="E72" s="129"/>
-      <c r="F72" s="119"/>
-      <c r="G72" s="119"/>
-      <c r="H72" s="119"/>
-      <c r="I72" s="119"/>
-      <c r="J72" s="119"/>
-      <c r="K72" s="119"/>
-      <c r="L72" s="119"/>
-      <c r="M72" s="119"/>
-      <c r="N72" s="129"/>
-      <c r="O72" s="129"/>
-      <c r="P72" s="129"/>
-      <c r="Q72" s="129"/>
+      <c r="C72" s="117"/>
+      <c r="D72" s="117"/>
+      <c r="E72" s="120"/>
+      <c r="F72" s="117"/>
+      <c r="G72" s="117"/>
+      <c r="H72" s="117"/>
+      <c r="I72" s="117"/>
+      <c r="J72" s="117"/>
+      <c r="K72" s="117"/>
+      <c r="L72" s="117"/>
+      <c r="M72" s="117"/>
+      <c r="N72" s="120"/>
+      <c r="O72" s="120"/>
+      <c r="P72" s="120"/>
+      <c r="Q72" s="120"/>
     </row>
     <row r="73" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A73" s="24" t="str">
@@ -12405,21 +12405,21 @@
       <c r="B73" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C73" s="119"/>
-      <c r="D73" s="119"/>
-      <c r="E73" s="129"/>
-      <c r="F73" s="119"/>
-      <c r="G73" s="119"/>
-      <c r="H73" s="119"/>
-      <c r="I73" s="119"/>
-      <c r="J73" s="119"/>
-      <c r="K73" s="119"/>
-      <c r="L73" s="119"/>
-      <c r="M73" s="119"/>
-      <c r="N73" s="129"/>
-      <c r="O73" s="129"/>
-      <c r="P73" s="129"/>
-      <c r="Q73" s="129"/>
+      <c r="C73" s="117"/>
+      <c r="D73" s="117"/>
+      <c r="E73" s="120"/>
+      <c r="F73" s="117"/>
+      <c r="G73" s="117"/>
+      <c r="H73" s="117"/>
+      <c r="I73" s="117"/>
+      <c r="J73" s="117"/>
+      <c r="K73" s="117"/>
+      <c r="L73" s="117"/>
+      <c r="M73" s="117"/>
+      <c r="N73" s="120"/>
+      <c r="O73" s="120"/>
+      <c r="P73" s="120"/>
+      <c r="Q73" s="120"/>
     </row>
     <row r="74" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A74" s="24" t="str">
@@ -12429,21 +12429,21 @@
       <c r="B74" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="119"/>
-      <c r="D74" s="119"/>
-      <c r="E74" s="129"/>
-      <c r="F74" s="119"/>
-      <c r="G74" s="119"/>
-      <c r="H74" s="119"/>
-      <c r="I74" s="119"/>
-      <c r="J74" s="119"/>
-      <c r="K74" s="119"/>
-      <c r="L74" s="119"/>
-      <c r="M74" s="119"/>
-      <c r="N74" s="129"/>
-      <c r="O74" s="129"/>
-      <c r="P74" s="129"/>
-      <c r="Q74" s="129"/>
+      <c r="C74" s="117"/>
+      <c r="D74" s="117"/>
+      <c r="E74" s="120"/>
+      <c r="F74" s="117"/>
+      <c r="G74" s="117"/>
+      <c r="H74" s="117"/>
+      <c r="I74" s="117"/>
+      <c r="J74" s="117"/>
+      <c r="K74" s="117"/>
+      <c r="L74" s="117"/>
+      <c r="M74" s="117"/>
+      <c r="N74" s="120"/>
+      <c r="O74" s="120"/>
+      <c r="P74" s="120"/>
+      <c r="Q74" s="120"/>
     </row>
     <row r="75" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="80" t="str">
@@ -12453,21 +12453,21 @@
       <c r="B75" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C75" s="120"/>
-      <c r="D75" s="120"/>
-      <c r="E75" s="132"/>
-      <c r="F75" s="133"/>
-      <c r="G75" s="133"/>
-      <c r="H75" s="133"/>
-      <c r="I75" s="133"/>
-      <c r="J75" s="133"/>
-      <c r="K75" s="120"/>
-      <c r="L75" s="120"/>
-      <c r="M75" s="133"/>
-      <c r="N75" s="132"/>
-      <c r="O75" s="130"/>
-      <c r="P75" s="130"/>
-      <c r="Q75" s="130"/>
+      <c r="C75" s="118"/>
+      <c r="D75" s="118"/>
+      <c r="E75" s="125"/>
+      <c r="F75" s="122"/>
+      <c r="G75" s="122"/>
+      <c r="H75" s="122"/>
+      <c r="I75" s="122"/>
+      <c r="J75" s="122"/>
+      <c r="K75" s="118"/>
+      <c r="L75" s="118"/>
+      <c r="M75" s="122"/>
+      <c r="N75" s="125"/>
+      <c r="O75" s="121"/>
+      <c r="P75" s="121"/>
+      <c r="Q75" s="121"/>
     </row>
     <row r="76" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A76" s="24" t="str">
@@ -12477,48 +12477,48 @@
       <c r="B76" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C76" s="124">
+      <c r="C76" s="116">
         <v>5</v>
       </c>
-      <c r="D76" s="124" t="s">
+      <c r="D76" s="116" t="s">
         <v>263</v>
       </c>
-      <c r="E76" s="129" t="s">
+      <c r="E76" s="120" t="s">
         <v>264</v>
       </c>
-      <c r="F76" s="119" t="s">
+      <c r="F76" s="117" t="s">
         <v>180</v>
       </c>
-      <c r="G76" s="119"/>
-      <c r="H76" s="119" t="s">
+      <c r="G76" s="117"/>
+      <c r="H76" s="117" t="s">
         <v>181</v>
       </c>
-      <c r="I76" s="119"/>
-      <c r="J76" s="119">
+      <c r="I76" s="117"/>
+      <c r="J76" s="117">
         <v>4</v>
       </c>
-      <c r="K76" s="117">
+      <c r="K76" s="123">
         <f>J76*12</f>
         <v>48</v>
       </c>
-      <c r="L76" s="117">
+      <c r="L76" s="123">
         <f>36*J76</f>
         <v>144</v>
       </c>
-      <c r="M76" s="119">
+      <c r="M76" s="117">
         <f>SUM(K76:L76)</f>
         <v>192</v>
       </c>
-      <c r="N76" s="129" t="s">
+      <c r="N76" s="120" t="s">
         <v>265</v>
       </c>
-      <c r="O76" s="128" t="s">
+      <c r="O76" s="119" t="s">
         <v>231</v>
       </c>
-      <c r="P76" s="128" t="s">
+      <c r="P76" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q76" s="128" t="s">
+      <c r="Q76" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -12530,21 +12530,21 @@
       <c r="B77" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C77" s="119"/>
-      <c r="D77" s="119"/>
-      <c r="E77" s="129"/>
-      <c r="F77" s="119"/>
-      <c r="G77" s="119"/>
-      <c r="H77" s="119"/>
-      <c r="I77" s="119"/>
-      <c r="J77" s="119"/>
-      <c r="K77" s="117"/>
-      <c r="L77" s="117"/>
-      <c r="M77" s="119"/>
-      <c r="N77" s="129"/>
-      <c r="O77" s="129"/>
-      <c r="P77" s="129"/>
-      <c r="Q77" s="129"/>
+      <c r="C77" s="117"/>
+      <c r="D77" s="117"/>
+      <c r="E77" s="120"/>
+      <c r="F77" s="117"/>
+      <c r="G77" s="117"/>
+      <c r="H77" s="117"/>
+      <c r="I77" s="117"/>
+      <c r="J77" s="117"/>
+      <c r="K77" s="123"/>
+      <c r="L77" s="123"/>
+      <c r="M77" s="117"/>
+      <c r="N77" s="120"/>
+      <c r="O77" s="120"/>
+      <c r="P77" s="120"/>
+      <c r="Q77" s="120"/>
     </row>
     <row r="78" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="80" t="str">
@@ -12554,21 +12554,21 @@
       <c r="B78" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C78" s="120"/>
-      <c r="D78" s="120"/>
-      <c r="E78" s="130"/>
-      <c r="F78" s="120"/>
-      <c r="G78" s="120"/>
-      <c r="H78" s="120"/>
-      <c r="I78" s="120"/>
-      <c r="J78" s="120"/>
-      <c r="K78" s="118"/>
-      <c r="L78" s="118"/>
-      <c r="M78" s="120"/>
-      <c r="N78" s="130"/>
-      <c r="O78" s="130"/>
-      <c r="P78" s="130"/>
-      <c r="Q78" s="130"/>
+      <c r="C78" s="118"/>
+      <c r="D78" s="118"/>
+      <c r="E78" s="121"/>
+      <c r="F78" s="118"/>
+      <c r="G78" s="118"/>
+      <c r="H78" s="118"/>
+      <c r="I78" s="118"/>
+      <c r="J78" s="118"/>
+      <c r="K78" s="124"/>
+      <c r="L78" s="124"/>
+      <c r="M78" s="118"/>
+      <c r="N78" s="121"/>
+      <c r="O78" s="121"/>
+      <c r="P78" s="121"/>
+      <c r="Q78" s="121"/>
       <c r="R78" s="50">
         <f>SUM(J56:J78)</f>
         <v>16</v>
@@ -12586,48 +12586,48 @@
       <c r="B79" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C79" s="124">
+      <c r="C79" s="116">
         <v>6</v>
       </c>
-      <c r="D79" s="124" t="s">
+      <c r="D79" s="116" t="s">
         <v>266</v>
       </c>
-      <c r="E79" s="128" t="s">
+      <c r="E79" s="119" t="s">
         <v>267</v>
       </c>
-      <c r="F79" s="124" t="s">
+      <c r="F79" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G79" s="124"/>
-      <c r="H79" s="124" t="s">
+      <c r="G79" s="116"/>
+      <c r="H79" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I79" s="124"/>
-      <c r="J79" s="124">
+      <c r="I79" s="116"/>
+      <c r="J79" s="116">
         <v>3</v>
       </c>
-      <c r="K79" s="124">
+      <c r="K79" s="116">
         <f>J79*12</f>
         <v>36</v>
       </c>
-      <c r="L79" s="124">
+      <c r="L79" s="116">
         <f>36*J79</f>
         <v>108</v>
       </c>
-      <c r="M79" s="124">
+      <c r="M79" s="116">
         <f>SUM(K79:L79)</f>
         <v>144</v>
       </c>
-      <c r="N79" s="128" t="s">
+      <c r="N79" s="119" t="s">
         <v>268</v>
       </c>
-      <c r="O79" s="128" t="s">
+      <c r="O79" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="P79" s="128" t="s">
+      <c r="P79" s="119" t="s">
         <v>193</v>
       </c>
-      <c r="Q79" s="128" t="s">
+      <c r="Q79" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -12639,21 +12639,21 @@
       <c r="B80" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C80" s="119"/>
-      <c r="D80" s="119"/>
-      <c r="E80" s="129"/>
-      <c r="F80" s="119"/>
-      <c r="G80" s="119"/>
-      <c r="H80" s="119"/>
-      <c r="I80" s="119"/>
-      <c r="J80" s="119"/>
-      <c r="K80" s="119"/>
-      <c r="L80" s="119"/>
-      <c r="M80" s="119"/>
-      <c r="N80" s="129"/>
-      <c r="O80" s="129"/>
-      <c r="P80" s="129"/>
-      <c r="Q80" s="129"/>
+      <c r="C80" s="117"/>
+      <c r="D80" s="117"/>
+      <c r="E80" s="120"/>
+      <c r="F80" s="117"/>
+      <c r="G80" s="117"/>
+      <c r="H80" s="117"/>
+      <c r="I80" s="117"/>
+      <c r="J80" s="117"/>
+      <c r="K80" s="117"/>
+      <c r="L80" s="117"/>
+      <c r="M80" s="117"/>
+      <c r="N80" s="120"/>
+      <c r="O80" s="120"/>
+      <c r="P80" s="120"/>
+      <c r="Q80" s="120"/>
     </row>
     <row r="81" spans="1:17" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A81" s="24" t="str">
@@ -12663,21 +12663,21 @@
       <c r="B81" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C81" s="119"/>
-      <c r="D81" s="119"/>
-      <c r="E81" s="129"/>
-      <c r="F81" s="119"/>
-      <c r="G81" s="119"/>
-      <c r="H81" s="119"/>
-      <c r="I81" s="119"/>
-      <c r="J81" s="119"/>
-      <c r="K81" s="119"/>
-      <c r="L81" s="119"/>
-      <c r="M81" s="119"/>
-      <c r="N81" s="129"/>
-      <c r="O81" s="129"/>
-      <c r="P81" s="129"/>
-      <c r="Q81" s="129"/>
+      <c r="C81" s="117"/>
+      <c r="D81" s="117"/>
+      <c r="E81" s="120"/>
+      <c r="F81" s="117"/>
+      <c r="G81" s="117"/>
+      <c r="H81" s="117"/>
+      <c r="I81" s="117"/>
+      <c r="J81" s="117"/>
+      <c r="K81" s="117"/>
+      <c r="L81" s="117"/>
+      <c r="M81" s="117"/>
+      <c r="N81" s="120"/>
+      <c r="O81" s="120"/>
+      <c r="P81" s="120"/>
+      <c r="Q81" s="120"/>
     </row>
     <row r="82" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A82" s="24" t="str">
@@ -12687,21 +12687,21 @@
       <c r="B82" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C82" s="119"/>
-      <c r="D82" s="119"/>
-      <c r="E82" s="129"/>
-      <c r="F82" s="119"/>
-      <c r="G82" s="119"/>
-      <c r="H82" s="119"/>
-      <c r="I82" s="119"/>
-      <c r="J82" s="119"/>
-      <c r="K82" s="119"/>
-      <c r="L82" s="119"/>
-      <c r="M82" s="119"/>
-      <c r="N82" s="129"/>
-      <c r="O82" s="129"/>
-      <c r="P82" s="129"/>
-      <c r="Q82" s="129"/>
+      <c r="C82" s="117"/>
+      <c r="D82" s="117"/>
+      <c r="E82" s="120"/>
+      <c r="F82" s="117"/>
+      <c r="G82" s="117"/>
+      <c r="H82" s="117"/>
+      <c r="I82" s="117"/>
+      <c r="J82" s="117"/>
+      <c r="K82" s="117"/>
+      <c r="L82" s="117"/>
+      <c r="M82" s="117"/>
+      <c r="N82" s="120"/>
+      <c r="O82" s="120"/>
+      <c r="P82" s="120"/>
+      <c r="Q82" s="120"/>
     </row>
     <row r="83" spans="1:17" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="80" t="str">
@@ -12711,21 +12711,21 @@
       <c r="B83" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C83" s="120"/>
-      <c r="D83" s="120"/>
-      <c r="E83" s="130"/>
-      <c r="F83" s="120"/>
-      <c r="G83" s="120"/>
-      <c r="H83" s="120"/>
-      <c r="I83" s="120"/>
-      <c r="J83" s="120"/>
-      <c r="K83" s="120"/>
-      <c r="L83" s="120"/>
-      <c r="M83" s="120"/>
-      <c r="N83" s="130"/>
-      <c r="O83" s="130"/>
-      <c r="P83" s="130"/>
-      <c r="Q83" s="130"/>
+      <c r="C83" s="118"/>
+      <c r="D83" s="118"/>
+      <c r="E83" s="121"/>
+      <c r="F83" s="118"/>
+      <c r="G83" s="118"/>
+      <c r="H83" s="118"/>
+      <c r="I83" s="118"/>
+      <c r="J83" s="118"/>
+      <c r="K83" s="118"/>
+      <c r="L83" s="118"/>
+      <c r="M83" s="118"/>
+      <c r="N83" s="121"/>
+      <c r="O83" s="121"/>
+      <c r="P83" s="121"/>
+      <c r="Q83" s="121"/>
     </row>
     <row r="84" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A84" s="24" t="str">
@@ -12735,48 +12735,48 @@
       <c r="B84" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C84" s="124">
+      <c r="C84" s="116">
         <v>6</v>
       </c>
-      <c r="D84" s="124" t="s">
+      <c r="D84" s="116" t="s">
         <v>269</v>
       </c>
-      <c r="E84" s="128" t="s">
+      <c r="E84" s="119" t="s">
         <v>270</v>
       </c>
-      <c r="F84" s="124" t="s">
+      <c r="F84" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G84" s="124"/>
-      <c r="H84" s="124" t="s">
+      <c r="G84" s="116"/>
+      <c r="H84" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I84" s="124"/>
-      <c r="J84" s="124">
+      <c r="I84" s="116"/>
+      <c r="J84" s="116">
         <v>3</v>
       </c>
-      <c r="K84" s="124">
+      <c r="K84" s="116">
         <f>J84*12</f>
         <v>36</v>
       </c>
-      <c r="L84" s="124">
+      <c r="L84" s="116">
         <f>36*J84</f>
         <v>108</v>
       </c>
-      <c r="M84" s="124">
+      <c r="M84" s="116">
         <f>SUM(K84:L84)</f>
         <v>144</v>
       </c>
-      <c r="N84" s="128" t="s">
+      <c r="N84" s="119" t="s">
         <v>271</v>
       </c>
-      <c r="O84" s="128" t="s">
+      <c r="O84" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="P84" s="128" t="s">
+      <c r="P84" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="Q84" s="128" t="s">
+      <c r="Q84" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -12788,21 +12788,21 @@
       <c r="B85" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C85" s="119"/>
-      <c r="D85" s="119"/>
-      <c r="E85" s="129"/>
-      <c r="F85" s="119"/>
-      <c r="G85" s="119"/>
-      <c r="H85" s="119"/>
-      <c r="I85" s="119"/>
-      <c r="J85" s="119"/>
-      <c r="K85" s="119"/>
-      <c r="L85" s="119"/>
-      <c r="M85" s="119"/>
-      <c r="N85" s="129"/>
-      <c r="O85" s="129"/>
-      <c r="P85" s="129"/>
-      <c r="Q85" s="129"/>
+      <c r="C85" s="117"/>
+      <c r="D85" s="117"/>
+      <c r="E85" s="120"/>
+      <c r="F85" s="117"/>
+      <c r="G85" s="117"/>
+      <c r="H85" s="117"/>
+      <c r="I85" s="117"/>
+      <c r="J85" s="117"/>
+      <c r="K85" s="117"/>
+      <c r="L85" s="117"/>
+      <c r="M85" s="117"/>
+      <c r="N85" s="120"/>
+      <c r="O85" s="120"/>
+      <c r="P85" s="120"/>
+      <c r="Q85" s="120"/>
     </row>
     <row r="86" spans="1:17" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A86" s="24" t="str">
@@ -12812,21 +12812,21 @@
       <c r="B86" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C86" s="119"/>
-      <c r="D86" s="119"/>
-      <c r="E86" s="129"/>
-      <c r="F86" s="119"/>
-      <c r="G86" s="119"/>
-      <c r="H86" s="119"/>
-      <c r="I86" s="119"/>
-      <c r="J86" s="119"/>
-      <c r="K86" s="119"/>
-      <c r="L86" s="119"/>
-      <c r="M86" s="119"/>
-      <c r="N86" s="129"/>
-      <c r="O86" s="129"/>
-      <c r="P86" s="129"/>
-      <c r="Q86" s="129"/>
+      <c r="C86" s="117"/>
+      <c r="D86" s="117"/>
+      <c r="E86" s="120"/>
+      <c r="F86" s="117"/>
+      <c r="G86" s="117"/>
+      <c r="H86" s="117"/>
+      <c r="I86" s="117"/>
+      <c r="J86" s="117"/>
+      <c r="K86" s="117"/>
+      <c r="L86" s="117"/>
+      <c r="M86" s="117"/>
+      <c r="N86" s="120"/>
+      <c r="O86" s="120"/>
+      <c r="P86" s="120"/>
+      <c r="Q86" s="120"/>
     </row>
     <row r="87" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="str">
@@ -12836,21 +12836,21 @@
       <c r="B87" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C87" s="119"/>
-      <c r="D87" s="119"/>
-      <c r="E87" s="129"/>
-      <c r="F87" s="119"/>
-      <c r="G87" s="119"/>
-      <c r="H87" s="119"/>
-      <c r="I87" s="119"/>
-      <c r="J87" s="119"/>
-      <c r="K87" s="119"/>
-      <c r="L87" s="119"/>
-      <c r="M87" s="119"/>
-      <c r="N87" s="129"/>
-      <c r="O87" s="129"/>
-      <c r="P87" s="129"/>
-      <c r="Q87" s="129"/>
+      <c r="C87" s="117"/>
+      <c r="D87" s="117"/>
+      <c r="E87" s="120"/>
+      <c r="F87" s="117"/>
+      <c r="G87" s="117"/>
+      <c r="H87" s="117"/>
+      <c r="I87" s="117"/>
+      <c r="J87" s="117"/>
+      <c r="K87" s="117"/>
+      <c r="L87" s="117"/>
+      <c r="M87" s="117"/>
+      <c r="N87" s="120"/>
+      <c r="O87" s="120"/>
+      <c r="P87" s="120"/>
+      <c r="Q87" s="120"/>
     </row>
     <row r="88" spans="1:17" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="80" t="str">
@@ -12860,21 +12860,21 @@
       <c r="B88" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C88" s="120"/>
-      <c r="D88" s="120"/>
-      <c r="E88" s="130"/>
-      <c r="F88" s="120"/>
-      <c r="G88" s="120"/>
-      <c r="H88" s="120"/>
-      <c r="I88" s="120"/>
-      <c r="J88" s="120"/>
-      <c r="K88" s="120"/>
-      <c r="L88" s="120"/>
-      <c r="M88" s="120"/>
-      <c r="N88" s="130"/>
-      <c r="O88" s="130"/>
-      <c r="P88" s="130"/>
-      <c r="Q88" s="130"/>
+      <c r="C88" s="118"/>
+      <c r="D88" s="118"/>
+      <c r="E88" s="121"/>
+      <c r="F88" s="118"/>
+      <c r="G88" s="118"/>
+      <c r="H88" s="118"/>
+      <c r="I88" s="118"/>
+      <c r="J88" s="118"/>
+      <c r="K88" s="118"/>
+      <c r="L88" s="118"/>
+      <c r="M88" s="118"/>
+      <c r="N88" s="121"/>
+      <c r="O88" s="121"/>
+      <c r="P88" s="121"/>
+      <c r="Q88" s="121"/>
     </row>
     <row r="89" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A89" s="24" t="str">
@@ -12884,48 +12884,48 @@
       <c r="B89" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C89" s="124">
+      <c r="C89" s="116">
         <v>6</v>
       </c>
-      <c r="D89" s="124" t="s">
+      <c r="D89" s="116" t="s">
         <v>272</v>
       </c>
-      <c r="E89" s="128" t="s">
+      <c r="E89" s="119" t="s">
         <v>273</v>
       </c>
-      <c r="F89" s="124" t="s">
+      <c r="F89" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G89" s="124"/>
-      <c r="H89" s="124" t="s">
+      <c r="G89" s="116"/>
+      <c r="H89" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I89" s="124"/>
-      <c r="J89" s="124">
+      <c r="I89" s="116"/>
+      <c r="J89" s="116">
         <v>3</v>
       </c>
-      <c r="K89" s="124">
+      <c r="K89" s="116">
         <f>J89*12</f>
         <v>36</v>
       </c>
-      <c r="L89" s="124">
+      <c r="L89" s="116">
         <f>36*J89</f>
         <v>108</v>
       </c>
-      <c r="M89" s="124">
+      <c r="M89" s="116">
         <f>SUM(K89:L89)</f>
         <v>144</v>
       </c>
-      <c r="N89" s="128" t="s">
+      <c r="N89" s="119" t="s">
         <v>274</v>
       </c>
-      <c r="O89" s="128" t="s">
+      <c r="O89" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="P89" s="128" t="s">
+      <c r="P89" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="Q89" s="128" t="s">
+      <c r="Q89" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -12937,21 +12937,21 @@
       <c r="B90" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C90" s="119"/>
-      <c r="D90" s="119"/>
-      <c r="E90" s="129"/>
-      <c r="F90" s="119"/>
-      <c r="G90" s="119"/>
-      <c r="H90" s="119"/>
-      <c r="I90" s="119"/>
-      <c r="J90" s="119"/>
-      <c r="K90" s="119"/>
-      <c r="L90" s="119"/>
-      <c r="M90" s="119"/>
-      <c r="N90" s="129"/>
-      <c r="O90" s="129"/>
-      <c r="P90" s="129"/>
-      <c r="Q90" s="129"/>
+      <c r="C90" s="117"/>
+      <c r="D90" s="117"/>
+      <c r="E90" s="120"/>
+      <c r="F90" s="117"/>
+      <c r="G90" s="117"/>
+      <c r="H90" s="117"/>
+      <c r="I90" s="117"/>
+      <c r="J90" s="117"/>
+      <c r="K90" s="117"/>
+      <c r="L90" s="117"/>
+      <c r="M90" s="117"/>
+      <c r="N90" s="120"/>
+      <c r="O90" s="120"/>
+      <c r="P90" s="120"/>
+      <c r="Q90" s="120"/>
     </row>
     <row r="91" spans="1:17" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A91" s="24" t="str">
@@ -12961,21 +12961,21 @@
       <c r="B91" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C91" s="119"/>
-      <c r="D91" s="119"/>
-      <c r="E91" s="129"/>
-      <c r="F91" s="119"/>
-      <c r="G91" s="119"/>
-      <c r="H91" s="119"/>
-      <c r="I91" s="119"/>
-      <c r="J91" s="119"/>
-      <c r="K91" s="119"/>
-      <c r="L91" s="119"/>
-      <c r="M91" s="119"/>
-      <c r="N91" s="129"/>
-      <c r="O91" s="129"/>
-      <c r="P91" s="129"/>
-      <c r="Q91" s="129"/>
+      <c r="C91" s="117"/>
+      <c r="D91" s="117"/>
+      <c r="E91" s="120"/>
+      <c r="F91" s="117"/>
+      <c r="G91" s="117"/>
+      <c r="H91" s="117"/>
+      <c r="I91" s="117"/>
+      <c r="J91" s="117"/>
+      <c r="K91" s="117"/>
+      <c r="L91" s="117"/>
+      <c r="M91" s="117"/>
+      <c r="N91" s="120"/>
+      <c r="O91" s="120"/>
+      <c r="P91" s="120"/>
+      <c r="Q91" s="120"/>
     </row>
     <row r="92" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A92" s="24" t="str">
@@ -12985,21 +12985,21 @@
       <c r="B92" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C92" s="119"/>
-      <c r="D92" s="119"/>
-      <c r="E92" s="129"/>
-      <c r="F92" s="119"/>
-      <c r="G92" s="119"/>
-      <c r="H92" s="119"/>
-      <c r="I92" s="119"/>
-      <c r="J92" s="119"/>
-      <c r="K92" s="119"/>
-      <c r="L92" s="119"/>
-      <c r="M92" s="119"/>
-      <c r="N92" s="129"/>
-      <c r="O92" s="129"/>
-      <c r="P92" s="129"/>
-      <c r="Q92" s="129"/>
+      <c r="C92" s="117"/>
+      <c r="D92" s="117"/>
+      <c r="E92" s="120"/>
+      <c r="F92" s="117"/>
+      <c r="G92" s="117"/>
+      <c r="H92" s="117"/>
+      <c r="I92" s="117"/>
+      <c r="J92" s="117"/>
+      <c r="K92" s="117"/>
+      <c r="L92" s="117"/>
+      <c r="M92" s="117"/>
+      <c r="N92" s="120"/>
+      <c r="O92" s="120"/>
+      <c r="P92" s="120"/>
+      <c r="Q92" s="120"/>
     </row>
     <row r="93" spans="1:17" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="80" t="str">
@@ -13009,21 +13009,21 @@
       <c r="B93" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C93" s="120"/>
-      <c r="D93" s="120"/>
-      <c r="E93" s="130"/>
-      <c r="F93" s="120"/>
-      <c r="G93" s="120"/>
-      <c r="H93" s="120"/>
-      <c r="I93" s="120"/>
-      <c r="J93" s="120"/>
-      <c r="K93" s="120"/>
-      <c r="L93" s="120"/>
-      <c r="M93" s="120"/>
-      <c r="N93" s="130"/>
-      <c r="O93" s="130"/>
-      <c r="P93" s="130"/>
-      <c r="Q93" s="130"/>
+      <c r="C93" s="118"/>
+      <c r="D93" s="118"/>
+      <c r="E93" s="121"/>
+      <c r="F93" s="118"/>
+      <c r="G93" s="118"/>
+      <c r="H93" s="118"/>
+      <c r="I93" s="118"/>
+      <c r="J93" s="118"/>
+      <c r="K93" s="118"/>
+      <c r="L93" s="118"/>
+      <c r="M93" s="118"/>
+      <c r="N93" s="121"/>
+      <c r="O93" s="121"/>
+      <c r="P93" s="121"/>
+      <c r="Q93" s="121"/>
     </row>
     <row r="94" spans="1:17" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A94" s="24" t="str">
@@ -13033,48 +13033,48 @@
       <c r="B94" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="124">
+      <c r="C94" s="116">
         <v>6</v>
       </c>
-      <c r="D94" s="124" t="s">
+      <c r="D94" s="116" t="s">
         <v>275</v>
       </c>
-      <c r="E94" s="128" t="s">
+      <c r="E94" s="119" t="s">
         <v>276</v>
       </c>
-      <c r="F94" s="124" t="s">
+      <c r="F94" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G94" s="124"/>
-      <c r="H94" s="124" t="s">
+      <c r="G94" s="116"/>
+      <c r="H94" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I94" s="124"/>
-      <c r="J94" s="124">
+      <c r="I94" s="116"/>
+      <c r="J94" s="116">
         <v>4</v>
       </c>
-      <c r="K94" s="124">
+      <c r="K94" s="116">
         <f>J94*12</f>
         <v>48</v>
       </c>
-      <c r="L94" s="124">
+      <c r="L94" s="116">
         <f>36*J94</f>
         <v>144</v>
       </c>
-      <c r="M94" s="124">
+      <c r="M94" s="116">
         <f>SUM(K94:L94)</f>
         <v>192</v>
       </c>
-      <c r="N94" s="128" t="s">
+      <c r="N94" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="O94" s="128" t="s">
+      <c r="O94" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="P94" s="128" t="s">
+      <c r="P94" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="Q94" s="128" t="s">
+      <c r="Q94" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -13086,21 +13086,21 @@
       <c r="B95" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C95" s="119"/>
-      <c r="D95" s="119"/>
-      <c r="E95" s="129"/>
-      <c r="F95" s="119"/>
-      <c r="G95" s="119"/>
-      <c r="H95" s="119"/>
-      <c r="I95" s="119"/>
-      <c r="J95" s="119"/>
-      <c r="K95" s="119"/>
-      <c r="L95" s="119"/>
-      <c r="M95" s="119"/>
-      <c r="N95" s="129"/>
-      <c r="O95" s="129"/>
-      <c r="P95" s="129"/>
-      <c r="Q95" s="129"/>
+      <c r="C95" s="117"/>
+      <c r="D95" s="117"/>
+      <c r="E95" s="120"/>
+      <c r="F95" s="117"/>
+      <c r="G95" s="117"/>
+      <c r="H95" s="117"/>
+      <c r="I95" s="117"/>
+      <c r="J95" s="117"/>
+      <c r="K95" s="117"/>
+      <c r="L95" s="117"/>
+      <c r="M95" s="117"/>
+      <c r="N95" s="120"/>
+      <c r="O95" s="120"/>
+      <c r="P95" s="120"/>
+      <c r="Q95" s="120"/>
     </row>
     <row r="96" spans="1:17" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A96" s="24" t="str">
@@ -13110,21 +13110,21 @@
       <c r="B96" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C96" s="119"/>
-      <c r="D96" s="119"/>
-      <c r="E96" s="129"/>
-      <c r="F96" s="119"/>
-      <c r="G96" s="119"/>
-      <c r="H96" s="119"/>
-      <c r="I96" s="119"/>
-      <c r="J96" s="119"/>
-      <c r="K96" s="119"/>
-      <c r="L96" s="119"/>
-      <c r="M96" s="119"/>
-      <c r="N96" s="129"/>
-      <c r="O96" s="129"/>
-      <c r="P96" s="129"/>
-      <c r="Q96" s="129"/>
+      <c r="C96" s="117"/>
+      <c r="D96" s="117"/>
+      <c r="E96" s="120"/>
+      <c r="F96" s="117"/>
+      <c r="G96" s="117"/>
+      <c r="H96" s="117"/>
+      <c r="I96" s="117"/>
+      <c r="J96" s="117"/>
+      <c r="K96" s="117"/>
+      <c r="L96" s="117"/>
+      <c r="M96" s="117"/>
+      <c r="N96" s="120"/>
+      <c r="O96" s="120"/>
+      <c r="P96" s="120"/>
+      <c r="Q96" s="120"/>
     </row>
     <row r="97" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A97" s="24" t="str">
@@ -13134,21 +13134,21 @@
       <c r="B97" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C97" s="119"/>
-      <c r="D97" s="119"/>
-      <c r="E97" s="129"/>
-      <c r="F97" s="119"/>
-      <c r="G97" s="119"/>
-      <c r="H97" s="119"/>
-      <c r="I97" s="119"/>
-      <c r="J97" s="119"/>
-      <c r="K97" s="119"/>
-      <c r="L97" s="119"/>
-      <c r="M97" s="119"/>
-      <c r="N97" s="129"/>
-      <c r="O97" s="129"/>
-      <c r="P97" s="129"/>
-      <c r="Q97" s="129"/>
+      <c r="C97" s="117"/>
+      <c r="D97" s="117"/>
+      <c r="E97" s="120"/>
+      <c r="F97" s="117"/>
+      <c r="G97" s="117"/>
+      <c r="H97" s="117"/>
+      <c r="I97" s="117"/>
+      <c r="J97" s="117"/>
+      <c r="K97" s="117"/>
+      <c r="L97" s="117"/>
+      <c r="M97" s="117"/>
+      <c r="N97" s="120"/>
+      <c r="O97" s="120"/>
+      <c r="P97" s="120"/>
+      <c r="Q97" s="120"/>
     </row>
     <row r="98" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="80" t="str">
@@ -13158,21 +13158,21 @@
       <c r="B98" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C98" s="120"/>
-      <c r="D98" s="120"/>
-      <c r="E98" s="130"/>
-      <c r="F98" s="120"/>
-      <c r="G98" s="120"/>
-      <c r="H98" s="120"/>
-      <c r="I98" s="120"/>
-      <c r="J98" s="120"/>
-      <c r="K98" s="120"/>
-      <c r="L98" s="120"/>
-      <c r="M98" s="120"/>
-      <c r="N98" s="130"/>
-      <c r="O98" s="130"/>
-      <c r="P98" s="130"/>
-      <c r="Q98" s="130"/>
+      <c r="C98" s="118"/>
+      <c r="D98" s="118"/>
+      <c r="E98" s="121"/>
+      <c r="F98" s="118"/>
+      <c r="G98" s="118"/>
+      <c r="H98" s="118"/>
+      <c r="I98" s="118"/>
+      <c r="J98" s="118"/>
+      <c r="K98" s="118"/>
+      <c r="L98" s="118"/>
+      <c r="M98" s="118"/>
+      <c r="N98" s="121"/>
+      <c r="O98" s="121"/>
+      <c r="P98" s="121"/>
+      <c r="Q98" s="121"/>
     </row>
     <row r="99" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A99" s="24" t="str">
@@ -13182,48 +13182,48 @@
       <c r="B99" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C99" s="124">
+      <c r="C99" s="116">
         <v>6</v>
       </c>
-      <c r="D99" s="124" t="s">
+      <c r="D99" s="116" t="s">
         <v>278</v>
       </c>
-      <c r="E99" s="128" t="s">
+      <c r="E99" s="119" t="s">
         <v>279</v>
       </c>
-      <c r="F99" s="124" t="s">
+      <c r="F99" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="G99" s="124"/>
-      <c r="H99" s="124" t="s">
+      <c r="G99" s="116"/>
+      <c r="H99" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="I99" s="124"/>
-      <c r="J99" s="124">
+      <c r="I99" s="116"/>
+      <c r="J99" s="116">
         <v>3</v>
       </c>
-      <c r="K99" s="124">
+      <c r="K99" s="116">
         <f>J99*12</f>
         <v>36</v>
       </c>
-      <c r="L99" s="124">
+      <c r="L99" s="116">
         <f>36*J99</f>
         <v>108</v>
       </c>
-      <c r="M99" s="124">
+      <c r="M99" s="116">
         <f>SUM(K99:L99)</f>
         <v>144</v>
       </c>
-      <c r="N99" s="128" t="s">
+      <c r="N99" s="119" t="s">
         <v>280</v>
       </c>
-      <c r="O99" s="128" t="s">
+      <c r="O99" s="119" t="s">
         <v>183</v>
       </c>
-      <c r="P99" s="128" t="s">
+      <c r="P99" s="119" t="s">
         <v>184</v>
       </c>
-      <c r="Q99" s="128" t="s">
+      <c r="Q99" s="119" t="s">
         <v>185</v>
       </c>
     </row>
@@ -13235,21 +13235,21 @@
       <c r="B100" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C100" s="119"/>
-      <c r="D100" s="119"/>
-      <c r="E100" s="129"/>
-      <c r="F100" s="119"/>
-      <c r="G100" s="119"/>
-      <c r="H100" s="119"/>
-      <c r="I100" s="119"/>
-      <c r="J100" s="119"/>
-      <c r="K100" s="119"/>
-      <c r="L100" s="119"/>
-      <c r="M100" s="119"/>
-      <c r="N100" s="129"/>
-      <c r="O100" s="129"/>
-      <c r="P100" s="129"/>
-      <c r="Q100" s="129"/>
+      <c r="C100" s="117"/>
+      <c r="D100" s="117"/>
+      <c r="E100" s="120"/>
+      <c r="F100" s="117"/>
+      <c r="G100" s="117"/>
+      <c r="H100" s="117"/>
+      <c r="I100" s="117"/>
+      <c r="J100" s="117"/>
+      <c r="K100" s="117"/>
+      <c r="L100" s="117"/>
+      <c r="M100" s="117"/>
+      <c r="N100" s="120"/>
+      <c r="O100" s="120"/>
+      <c r="P100" s="120"/>
+      <c r="Q100" s="120"/>
     </row>
     <row r="101" spans="1:19" s="50" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A101" s="24" t="str">
@@ -13259,21 +13259,21 @@
       <c r="B101" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C101" s="119"/>
-      <c r="D101" s="119"/>
-      <c r="E101" s="129"/>
-      <c r="F101" s="119"/>
-      <c r="G101" s="119"/>
-      <c r="H101" s="119"/>
-      <c r="I101" s="119"/>
-      <c r="J101" s="119"/>
-      <c r="K101" s="119"/>
-      <c r="L101" s="119"/>
-      <c r="M101" s="119"/>
-      <c r="N101" s="129"/>
-      <c r="O101" s="129"/>
-      <c r="P101" s="129"/>
-      <c r="Q101" s="129"/>
+      <c r="C101" s="117"/>
+      <c r="D101" s="117"/>
+      <c r="E101" s="120"/>
+      <c r="F101" s="117"/>
+      <c r="G101" s="117"/>
+      <c r="H101" s="117"/>
+      <c r="I101" s="117"/>
+      <c r="J101" s="117"/>
+      <c r="K101" s="117"/>
+      <c r="L101" s="117"/>
+      <c r="M101" s="117"/>
+      <c r="N101" s="120"/>
+      <c r="O101" s="120"/>
+      <c r="P101" s="120"/>
+      <c r="Q101" s="120"/>
     </row>
     <row r="102" spans="1:19" s="50" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A102" s="24" t="str">
@@ -13283,21 +13283,21 @@
       <c r="B102" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C102" s="119"/>
-      <c r="D102" s="119"/>
-      <c r="E102" s="129"/>
-      <c r="F102" s="119"/>
-      <c r="G102" s="119"/>
-      <c r="H102" s="119"/>
-      <c r="I102" s="119"/>
-      <c r="J102" s="119"/>
-      <c r="K102" s="119"/>
-      <c r="L102" s="119"/>
-      <c r="M102" s="119"/>
-      <c r="N102" s="129"/>
-      <c r="O102" s="129"/>
-      <c r="P102" s="129"/>
-      <c r="Q102" s="129"/>
+      <c r="C102" s="117"/>
+      <c r="D102" s="117"/>
+      <c r="E102" s="120"/>
+      <c r="F102" s="117"/>
+      <c r="G102" s="117"/>
+      <c r="H102" s="117"/>
+      <c r="I102" s="117"/>
+      <c r="J102" s="117"/>
+      <c r="K102" s="117"/>
+      <c r="L102" s="117"/>
+      <c r="M102" s="117"/>
+      <c r="N102" s="120"/>
+      <c r="O102" s="120"/>
+      <c r="P102" s="120"/>
+      <c r="Q102" s="120"/>
     </row>
     <row r="103" spans="1:19" s="50" customFormat="1" ht="54" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="str">
@@ -13307,21 +13307,21 @@
       <c r="B103" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C103" s="119"/>
-      <c r="D103" s="119"/>
-      <c r="E103" s="129"/>
-      <c r="F103" s="119"/>
-      <c r="G103" s="119"/>
-      <c r="H103" s="119"/>
-      <c r="I103" s="119"/>
-      <c r="J103" s="119"/>
-      <c r="K103" s="119"/>
-      <c r="L103" s="119"/>
-      <c r="M103" s="119"/>
-      <c r="N103" s="129"/>
-      <c r="O103" s="129"/>
-      <c r="P103" s="129"/>
-      <c r="Q103" s="129"/>
+      <c r="C103" s="117"/>
+      <c r="D103" s="117"/>
+      <c r="E103" s="120"/>
+      <c r="F103" s="117"/>
+      <c r="G103" s="117"/>
+      <c r="H103" s="117"/>
+      <c r="I103" s="117"/>
+      <c r="J103" s="117"/>
+      <c r="K103" s="117"/>
+      <c r="L103" s="117"/>
+      <c r="M103" s="117"/>
+      <c r="N103" s="120"/>
+      <c r="O103" s="120"/>
+      <c r="P103" s="120"/>
+      <c r="Q103" s="120"/>
     </row>
     <row r="104" spans="1:19" s="50" customFormat="1" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="112" t="str">
@@ -13331,21 +13331,21 @@
       <c r="B104" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C104" s="120"/>
-      <c r="D104" s="120"/>
-      <c r="E104" s="130"/>
-      <c r="F104" s="120"/>
-      <c r="G104" s="120"/>
-      <c r="H104" s="120"/>
-      <c r="I104" s="120"/>
-      <c r="J104" s="120"/>
-      <c r="K104" s="120"/>
-      <c r="L104" s="120"/>
-      <c r="M104" s="120"/>
-      <c r="N104" s="130"/>
-      <c r="O104" s="130"/>
-      <c r="P104" s="130"/>
-      <c r="Q104" s="130"/>
+      <c r="C104" s="118"/>
+      <c r="D104" s="118"/>
+      <c r="E104" s="121"/>
+      <c r="F104" s="118"/>
+      <c r="G104" s="118"/>
+      <c r="H104" s="118"/>
+      <c r="I104" s="118"/>
+      <c r="J104" s="118"/>
+      <c r="K104" s="118"/>
+      <c r="L104" s="118"/>
+      <c r="M104" s="118"/>
+      <c r="N104" s="121"/>
+      <c r="O104" s="121"/>
+      <c r="P104" s="121"/>
+      <c r="Q104" s="121"/>
       <c r="R104" s="50">
         <f>SUM(J79:J104)</f>
         <v>16</v>
@@ -14626,6 +14626,343 @@
     </row>
   </sheetData>
   <mergeCells count="361">
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="O5:O7"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="Q5:Q7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="K8:K10"/>
+    <mergeCell ref="L8:L10"/>
+    <mergeCell ref="M8:M10"/>
+    <mergeCell ref="N8:N10"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="K5:K7"/>
+    <mergeCell ref="L5:L7"/>
+    <mergeCell ref="M5:M7"/>
+    <mergeCell ref="N5:N7"/>
+    <mergeCell ref="O8:O10"/>
+    <mergeCell ref="P8:P10"/>
+    <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="P11:P13"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F15:F17"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="M11:M13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="N11:N13"/>
+    <mergeCell ref="O11:O13"/>
+    <mergeCell ref="M15:M17"/>
+    <mergeCell ref="N15:N17"/>
+    <mergeCell ref="O15:O17"/>
+    <mergeCell ref="P15:P17"/>
+    <mergeCell ref="Q15:Q17"/>
+    <mergeCell ref="H15:H17"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="J15:J17"/>
+    <mergeCell ref="K15:K17"/>
+    <mergeCell ref="L15:L17"/>
+    <mergeCell ref="Q18:Q20"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="J18:J20"/>
+    <mergeCell ref="K18:K20"/>
+    <mergeCell ref="L18:L20"/>
+    <mergeCell ref="O18:O20"/>
+    <mergeCell ref="P18:P20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="M21:M23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="O21:O23"/>
+    <mergeCell ref="P21:P23"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="Q21:Q23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="K21:K23"/>
+    <mergeCell ref="L21:L23"/>
+    <mergeCell ref="Q24:Q26"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="J24:J26"/>
+    <mergeCell ref="K24:K26"/>
+    <mergeCell ref="L24:L26"/>
+    <mergeCell ref="M24:M26"/>
+    <mergeCell ref="N24:N26"/>
+    <mergeCell ref="O24:O26"/>
+    <mergeCell ref="P24:P26"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="Q29:Q31"/>
+    <mergeCell ref="H29:H31"/>
+    <mergeCell ref="I29:I31"/>
+    <mergeCell ref="J29:J31"/>
+    <mergeCell ref="K29:K31"/>
+    <mergeCell ref="L29:L31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="M29:M31"/>
+    <mergeCell ref="N29:N31"/>
+    <mergeCell ref="O29:O31"/>
+    <mergeCell ref="P29:P31"/>
+    <mergeCell ref="M32:M34"/>
+    <mergeCell ref="N32:N34"/>
+    <mergeCell ref="O32:O34"/>
+    <mergeCell ref="P32:P34"/>
+    <mergeCell ref="Q32:Q34"/>
+    <mergeCell ref="H32:H34"/>
+    <mergeCell ref="I32:I34"/>
+    <mergeCell ref="J32:J34"/>
+    <mergeCell ref="K32:K34"/>
+    <mergeCell ref="L32:L34"/>
+    <mergeCell ref="Q35:Q37"/>
+    <mergeCell ref="I35:I37"/>
+    <mergeCell ref="J35:J37"/>
+    <mergeCell ref="K35:K37"/>
+    <mergeCell ref="L35:L37"/>
+    <mergeCell ref="M35:M37"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="G42:G45"/>
+    <mergeCell ref="M42:M45"/>
+    <mergeCell ref="N42:N45"/>
+    <mergeCell ref="O42:O45"/>
+    <mergeCell ref="P42:P45"/>
+    <mergeCell ref="L39:L41"/>
+    <mergeCell ref="M39:M41"/>
+    <mergeCell ref="N39:N41"/>
+    <mergeCell ref="O39:O41"/>
+    <mergeCell ref="P39:P41"/>
+    <mergeCell ref="Q39:Q41"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="N35:N37"/>
+    <mergeCell ref="O35:O37"/>
+    <mergeCell ref="P35:P37"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="H35:H37"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E39:E41"/>
+    <mergeCell ref="F39:F41"/>
+    <mergeCell ref="G39:G41"/>
+    <mergeCell ref="H39:H41"/>
+    <mergeCell ref="I39:I41"/>
+    <mergeCell ref="J39:J41"/>
+    <mergeCell ref="K39:K41"/>
+    <mergeCell ref="Q42:Q45"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="I42:I45"/>
+    <mergeCell ref="J42:J45"/>
+    <mergeCell ref="K42:K45"/>
+    <mergeCell ref="L42:L45"/>
+    <mergeCell ref="Q46:Q50"/>
+    <mergeCell ref="H46:H50"/>
+    <mergeCell ref="I46:I50"/>
+    <mergeCell ref="J46:J50"/>
+    <mergeCell ref="K46:K50"/>
+    <mergeCell ref="L46:L50"/>
+    <mergeCell ref="M46:M50"/>
+    <mergeCell ref="N46:N50"/>
+    <mergeCell ref="O46:O50"/>
+    <mergeCell ref="P46:P50"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="D46:D50"/>
+    <mergeCell ref="E46:E50"/>
+    <mergeCell ref="F46:F50"/>
+    <mergeCell ref="G46:G50"/>
+    <mergeCell ref="C51:C55"/>
+    <mergeCell ref="D51:D55"/>
+    <mergeCell ref="E51:E55"/>
+    <mergeCell ref="F51:F55"/>
+    <mergeCell ref="G51:G55"/>
+    <mergeCell ref="M51:M55"/>
+    <mergeCell ref="N51:N55"/>
+    <mergeCell ref="O51:O55"/>
+    <mergeCell ref="P51:P55"/>
+    <mergeCell ref="Q51:Q55"/>
+    <mergeCell ref="H51:H55"/>
+    <mergeCell ref="I51:I55"/>
+    <mergeCell ref="J51:J55"/>
+    <mergeCell ref="K51:K55"/>
+    <mergeCell ref="L51:L55"/>
+    <mergeCell ref="C56:C60"/>
+    <mergeCell ref="D56:D60"/>
+    <mergeCell ref="E56:E60"/>
+    <mergeCell ref="F56:F60"/>
+    <mergeCell ref="G56:G60"/>
+    <mergeCell ref="M56:M60"/>
+    <mergeCell ref="N56:N60"/>
+    <mergeCell ref="O56:O60"/>
+    <mergeCell ref="P56:P60"/>
+    <mergeCell ref="Q56:Q60"/>
+    <mergeCell ref="H56:H60"/>
+    <mergeCell ref="I56:I60"/>
+    <mergeCell ref="J56:J60"/>
+    <mergeCell ref="K56:K60"/>
+    <mergeCell ref="L56:L60"/>
+    <mergeCell ref="Q61:Q65"/>
+    <mergeCell ref="H61:H65"/>
+    <mergeCell ref="I61:I65"/>
+    <mergeCell ref="J61:J65"/>
+    <mergeCell ref="K61:K65"/>
+    <mergeCell ref="L61:L65"/>
+    <mergeCell ref="M61:M65"/>
+    <mergeCell ref="N61:N65"/>
+    <mergeCell ref="O61:O65"/>
+    <mergeCell ref="P61:P65"/>
+    <mergeCell ref="C61:C65"/>
+    <mergeCell ref="D61:D65"/>
+    <mergeCell ref="E61:E65"/>
+    <mergeCell ref="F61:F65"/>
+    <mergeCell ref="G61:G65"/>
+    <mergeCell ref="C66:C70"/>
+    <mergeCell ref="D66:D70"/>
+    <mergeCell ref="E66:E70"/>
+    <mergeCell ref="F66:F70"/>
+    <mergeCell ref="G66:G70"/>
+    <mergeCell ref="M66:M70"/>
+    <mergeCell ref="N66:N70"/>
+    <mergeCell ref="O66:O70"/>
+    <mergeCell ref="P66:P70"/>
+    <mergeCell ref="Q66:Q70"/>
+    <mergeCell ref="H66:H70"/>
+    <mergeCell ref="I66:I70"/>
+    <mergeCell ref="J66:J70"/>
+    <mergeCell ref="K66:K70"/>
+    <mergeCell ref="L66:L70"/>
+    <mergeCell ref="C71:C75"/>
+    <mergeCell ref="D71:D75"/>
+    <mergeCell ref="E71:E75"/>
+    <mergeCell ref="F71:F75"/>
+    <mergeCell ref="G71:G75"/>
+    <mergeCell ref="M71:M75"/>
+    <mergeCell ref="N71:N75"/>
+    <mergeCell ref="O71:O75"/>
+    <mergeCell ref="P71:P75"/>
+    <mergeCell ref="O79:O83"/>
+    <mergeCell ref="P79:P83"/>
+    <mergeCell ref="Q71:Q75"/>
+    <mergeCell ref="H71:H75"/>
+    <mergeCell ref="I71:I75"/>
+    <mergeCell ref="J71:J75"/>
+    <mergeCell ref="K71:K75"/>
+    <mergeCell ref="L71:L75"/>
+    <mergeCell ref="Q76:Q78"/>
+    <mergeCell ref="H76:H78"/>
+    <mergeCell ref="I76:I78"/>
+    <mergeCell ref="J76:J78"/>
+    <mergeCell ref="K76:K78"/>
+    <mergeCell ref="L76:L78"/>
+    <mergeCell ref="Q79:Q83"/>
+    <mergeCell ref="P89:P93"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="E76:E78"/>
+    <mergeCell ref="F76:F78"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="M76:M78"/>
+    <mergeCell ref="N76:N78"/>
+    <mergeCell ref="O76:O78"/>
+    <mergeCell ref="P76:P78"/>
+    <mergeCell ref="D84:D88"/>
+    <mergeCell ref="E84:E88"/>
+    <mergeCell ref="F84:F88"/>
+    <mergeCell ref="G84:G88"/>
+    <mergeCell ref="I79:I83"/>
+    <mergeCell ref="J79:J83"/>
+    <mergeCell ref="F79:F83"/>
+    <mergeCell ref="G79:G83"/>
+    <mergeCell ref="M79:M83"/>
+    <mergeCell ref="J84:J88"/>
+    <mergeCell ref="K84:K88"/>
+    <mergeCell ref="L84:L88"/>
+    <mergeCell ref="H79:H83"/>
+    <mergeCell ref="N79:N83"/>
+    <mergeCell ref="Q89:Q93"/>
+    <mergeCell ref="H89:H93"/>
+    <mergeCell ref="I89:I93"/>
+    <mergeCell ref="K79:K83"/>
+    <mergeCell ref="L79:L83"/>
+    <mergeCell ref="C84:C88"/>
+    <mergeCell ref="J89:J93"/>
+    <mergeCell ref="K89:K93"/>
+    <mergeCell ref="L89:L93"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="C89:C93"/>
+    <mergeCell ref="D89:D93"/>
+    <mergeCell ref="E89:E93"/>
+    <mergeCell ref="F89:F93"/>
+    <mergeCell ref="G89:G93"/>
+    <mergeCell ref="M84:M88"/>
+    <mergeCell ref="N84:N88"/>
+    <mergeCell ref="O84:O88"/>
+    <mergeCell ref="P84:P88"/>
+    <mergeCell ref="M89:M93"/>
+    <mergeCell ref="N89:N93"/>
+    <mergeCell ref="O89:O93"/>
+    <mergeCell ref="H94:H98"/>
+    <mergeCell ref="I94:I98"/>
+    <mergeCell ref="J94:J98"/>
+    <mergeCell ref="K94:K98"/>
+    <mergeCell ref="L94:L98"/>
+    <mergeCell ref="M94:M98"/>
+    <mergeCell ref="N94:N98"/>
+    <mergeCell ref="O94:O98"/>
+    <mergeCell ref="P94:P98"/>
     <mergeCell ref="C94:C98"/>
     <mergeCell ref="D94:D98"/>
     <mergeCell ref="E94:E98"/>
@@ -14650,343 +14987,6 @@
     <mergeCell ref="O99:O104"/>
     <mergeCell ref="P99:P104"/>
     <mergeCell ref="Q94:Q98"/>
-    <mergeCell ref="H94:H98"/>
-    <mergeCell ref="I94:I98"/>
-    <mergeCell ref="J94:J98"/>
-    <mergeCell ref="K94:K98"/>
-    <mergeCell ref="L94:L98"/>
-    <mergeCell ref="M94:M98"/>
-    <mergeCell ref="N94:N98"/>
-    <mergeCell ref="O94:O98"/>
-    <mergeCell ref="P94:P98"/>
-    <mergeCell ref="Q89:Q93"/>
-    <mergeCell ref="H89:H93"/>
-    <mergeCell ref="I89:I93"/>
-    <mergeCell ref="K79:K83"/>
-    <mergeCell ref="L79:L83"/>
-    <mergeCell ref="C84:C88"/>
-    <mergeCell ref="J89:J93"/>
-    <mergeCell ref="K89:K93"/>
-    <mergeCell ref="L89:L93"/>
-    <mergeCell ref="C79:C83"/>
-    <mergeCell ref="D79:D83"/>
-    <mergeCell ref="E79:E83"/>
-    <mergeCell ref="C89:C93"/>
-    <mergeCell ref="D89:D93"/>
-    <mergeCell ref="E89:E93"/>
-    <mergeCell ref="F89:F93"/>
-    <mergeCell ref="G89:G93"/>
-    <mergeCell ref="M84:M88"/>
-    <mergeCell ref="N84:N88"/>
-    <mergeCell ref="O84:O88"/>
-    <mergeCell ref="P84:P88"/>
-    <mergeCell ref="M89:M93"/>
-    <mergeCell ref="N89:N93"/>
-    <mergeCell ref="O89:O93"/>
-    <mergeCell ref="P89:P93"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="E76:E78"/>
-    <mergeCell ref="F76:F78"/>
-    <mergeCell ref="G76:G78"/>
-    <mergeCell ref="M76:M78"/>
-    <mergeCell ref="N76:N78"/>
-    <mergeCell ref="O76:O78"/>
-    <mergeCell ref="P76:P78"/>
-    <mergeCell ref="D84:D88"/>
-    <mergeCell ref="E84:E88"/>
-    <mergeCell ref="F84:F88"/>
-    <mergeCell ref="G84:G88"/>
-    <mergeCell ref="I79:I83"/>
-    <mergeCell ref="J79:J83"/>
-    <mergeCell ref="F79:F83"/>
-    <mergeCell ref="G79:G83"/>
-    <mergeCell ref="M79:M83"/>
-    <mergeCell ref="J84:J88"/>
-    <mergeCell ref="K84:K88"/>
-    <mergeCell ref="L84:L88"/>
-    <mergeCell ref="H79:H83"/>
-    <mergeCell ref="N79:N83"/>
-    <mergeCell ref="O79:O83"/>
-    <mergeCell ref="P79:P83"/>
-    <mergeCell ref="Q71:Q75"/>
-    <mergeCell ref="H71:H75"/>
-    <mergeCell ref="I71:I75"/>
-    <mergeCell ref="J71:J75"/>
-    <mergeCell ref="K71:K75"/>
-    <mergeCell ref="L71:L75"/>
-    <mergeCell ref="Q76:Q78"/>
-    <mergeCell ref="H76:H78"/>
-    <mergeCell ref="I76:I78"/>
-    <mergeCell ref="J76:J78"/>
-    <mergeCell ref="K76:K78"/>
-    <mergeCell ref="L76:L78"/>
-    <mergeCell ref="Q79:Q83"/>
-    <mergeCell ref="C71:C75"/>
-    <mergeCell ref="D71:D75"/>
-    <mergeCell ref="E71:E75"/>
-    <mergeCell ref="F71:F75"/>
-    <mergeCell ref="G71:G75"/>
-    <mergeCell ref="M71:M75"/>
-    <mergeCell ref="N71:N75"/>
-    <mergeCell ref="O71:O75"/>
-    <mergeCell ref="P71:P75"/>
-    <mergeCell ref="M66:M70"/>
-    <mergeCell ref="N66:N70"/>
-    <mergeCell ref="O66:O70"/>
-    <mergeCell ref="P66:P70"/>
-    <mergeCell ref="Q66:Q70"/>
-    <mergeCell ref="H66:H70"/>
-    <mergeCell ref="I66:I70"/>
-    <mergeCell ref="J66:J70"/>
-    <mergeCell ref="K66:K70"/>
-    <mergeCell ref="L66:L70"/>
-    <mergeCell ref="C61:C65"/>
-    <mergeCell ref="D61:D65"/>
-    <mergeCell ref="E61:E65"/>
-    <mergeCell ref="F61:F65"/>
-    <mergeCell ref="G61:G65"/>
-    <mergeCell ref="C66:C70"/>
-    <mergeCell ref="D66:D70"/>
-    <mergeCell ref="E66:E70"/>
-    <mergeCell ref="F66:F70"/>
-    <mergeCell ref="G66:G70"/>
-    <mergeCell ref="Q56:Q60"/>
-    <mergeCell ref="H56:H60"/>
-    <mergeCell ref="I56:I60"/>
-    <mergeCell ref="J56:J60"/>
-    <mergeCell ref="K56:K60"/>
-    <mergeCell ref="L56:L60"/>
-    <mergeCell ref="Q61:Q65"/>
-    <mergeCell ref="H61:H65"/>
-    <mergeCell ref="I61:I65"/>
-    <mergeCell ref="J61:J65"/>
-    <mergeCell ref="K61:K65"/>
-    <mergeCell ref="L61:L65"/>
-    <mergeCell ref="M61:M65"/>
-    <mergeCell ref="N61:N65"/>
-    <mergeCell ref="O61:O65"/>
-    <mergeCell ref="P61:P65"/>
-    <mergeCell ref="C56:C60"/>
-    <mergeCell ref="D56:D60"/>
-    <mergeCell ref="E56:E60"/>
-    <mergeCell ref="F56:F60"/>
-    <mergeCell ref="G56:G60"/>
-    <mergeCell ref="M56:M60"/>
-    <mergeCell ref="N56:N60"/>
-    <mergeCell ref="O56:O60"/>
-    <mergeCell ref="P56:P60"/>
-    <mergeCell ref="M51:M55"/>
-    <mergeCell ref="N51:N55"/>
-    <mergeCell ref="O51:O55"/>
-    <mergeCell ref="P51:P55"/>
-    <mergeCell ref="Q51:Q55"/>
-    <mergeCell ref="H51:H55"/>
-    <mergeCell ref="I51:I55"/>
-    <mergeCell ref="J51:J55"/>
-    <mergeCell ref="K51:K55"/>
-    <mergeCell ref="L51:L55"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="D46:D50"/>
-    <mergeCell ref="E46:E50"/>
-    <mergeCell ref="F46:F50"/>
-    <mergeCell ref="G46:G50"/>
-    <mergeCell ref="C51:C55"/>
-    <mergeCell ref="D51:D55"/>
-    <mergeCell ref="E51:E55"/>
-    <mergeCell ref="F51:F55"/>
-    <mergeCell ref="G51:G55"/>
-    <mergeCell ref="Q42:Q45"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="I42:I45"/>
-    <mergeCell ref="J42:J45"/>
-    <mergeCell ref="K42:K45"/>
-    <mergeCell ref="L42:L45"/>
-    <mergeCell ref="Q46:Q50"/>
-    <mergeCell ref="H46:H50"/>
-    <mergeCell ref="I46:I50"/>
-    <mergeCell ref="J46:J50"/>
-    <mergeCell ref="K46:K50"/>
-    <mergeCell ref="L46:L50"/>
-    <mergeCell ref="M46:M50"/>
-    <mergeCell ref="N46:N50"/>
-    <mergeCell ref="O46:O50"/>
-    <mergeCell ref="P46:P50"/>
-    <mergeCell ref="L39:L41"/>
-    <mergeCell ref="M39:M41"/>
-    <mergeCell ref="N39:N41"/>
-    <mergeCell ref="O39:O41"/>
-    <mergeCell ref="P39:P41"/>
-    <mergeCell ref="Q39:Q41"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="N35:N37"/>
-    <mergeCell ref="O35:O37"/>
-    <mergeCell ref="P35:P37"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="H35:H37"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E39:E41"/>
-    <mergeCell ref="F39:F41"/>
-    <mergeCell ref="G39:G41"/>
-    <mergeCell ref="H39:H41"/>
-    <mergeCell ref="I39:I41"/>
-    <mergeCell ref="J39:J41"/>
-    <mergeCell ref="K39:K41"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="G42:G45"/>
-    <mergeCell ref="M42:M45"/>
-    <mergeCell ref="N42:N45"/>
-    <mergeCell ref="O42:O45"/>
-    <mergeCell ref="P42:P45"/>
-    <mergeCell ref="Q32:Q34"/>
-    <mergeCell ref="H32:H34"/>
-    <mergeCell ref="I32:I34"/>
-    <mergeCell ref="J32:J34"/>
-    <mergeCell ref="K32:K34"/>
-    <mergeCell ref="L32:L34"/>
-    <mergeCell ref="Q35:Q37"/>
-    <mergeCell ref="I35:I37"/>
-    <mergeCell ref="J35:J37"/>
-    <mergeCell ref="K35:K37"/>
-    <mergeCell ref="L35:L37"/>
-    <mergeCell ref="M35:M37"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="M29:M31"/>
-    <mergeCell ref="N29:N31"/>
-    <mergeCell ref="O29:O31"/>
-    <mergeCell ref="P29:P31"/>
-    <mergeCell ref="M32:M34"/>
-    <mergeCell ref="N32:N34"/>
-    <mergeCell ref="O32:O34"/>
-    <mergeCell ref="P32:P34"/>
-    <mergeCell ref="Q29:Q31"/>
-    <mergeCell ref="H29:H31"/>
-    <mergeCell ref="I29:I31"/>
-    <mergeCell ref="J29:J31"/>
-    <mergeCell ref="K29:K31"/>
-    <mergeCell ref="L29:L31"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="G29:G31"/>
-    <mergeCell ref="O21:O23"/>
-    <mergeCell ref="P21:P23"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="Q21:Q23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="K21:K23"/>
-    <mergeCell ref="L21:L23"/>
-    <mergeCell ref="Q24:Q26"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="I24:I26"/>
-    <mergeCell ref="J24:J26"/>
-    <mergeCell ref="K24:K26"/>
-    <mergeCell ref="L24:L26"/>
-    <mergeCell ref="M24:M26"/>
-    <mergeCell ref="N24:N26"/>
-    <mergeCell ref="O24:O26"/>
-    <mergeCell ref="P24:P26"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="M21:M23"/>
-    <mergeCell ref="N21:N23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="P15:P17"/>
-    <mergeCell ref="Q15:Q17"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="J15:J17"/>
-    <mergeCell ref="K15:K17"/>
-    <mergeCell ref="L15:L17"/>
-    <mergeCell ref="Q18:Q20"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="I18:I20"/>
-    <mergeCell ref="J18:J20"/>
-    <mergeCell ref="K18:K20"/>
-    <mergeCell ref="L18:L20"/>
-    <mergeCell ref="O18:O20"/>
-    <mergeCell ref="P18:P20"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="M11:M13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="N11:N13"/>
-    <mergeCell ref="O11:O13"/>
-    <mergeCell ref="M15:M17"/>
-    <mergeCell ref="N15:N17"/>
-    <mergeCell ref="O15:O17"/>
-    <mergeCell ref="P11:P13"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="J11:J13"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="Q5:Q7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="H8:H10"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="L8:L10"/>
-    <mergeCell ref="M8:M10"/>
-    <mergeCell ref="N8:N10"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="K5:K7"/>
-    <mergeCell ref="L5:L7"/>
-    <mergeCell ref="M5:M7"/>
-    <mergeCell ref="N5:N7"/>
-    <mergeCell ref="O8:O10"/>
-    <mergeCell ref="P8:P10"/>
-    <mergeCell ref="Q8:Q10"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="O5:O7"/>
-    <mergeCell ref="P5:P7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15443,16 +15443,16 @@
       <c r="AG3" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="AL3" s="152" t="s">
+      <c r="AL3" s="140" t="s">
         <v>346</v>
       </c>
-      <c r="AM3" s="152"/>
-      <c r="AN3" s="152"/>
-      <c r="AO3" s="152" t="s">
+      <c r="AM3" s="140"/>
+      <c r="AN3" s="140"/>
+      <c r="AO3" s="140" t="s">
         <v>347</v>
       </c>
-      <c r="AP3" s="152"/>
-      <c r="AQ3" s="152"/>
+      <c r="AP3" s="140"/>
+      <c r="AQ3" s="140"/>
       <c r="AR3" s="13"/>
       <c r="AS3" s="13"/>
       <c r="AT3" s="13"/>
@@ -20421,16 +20421,16 @@
     <sortCondition ref="AU5:AU66"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="AC2:AG2"/>
+    <mergeCell ref="AL2:AQ2"/>
     <mergeCell ref="AL3:AN3"/>
     <mergeCell ref="AO3:AQ3"/>
     <mergeCell ref="AT1:AY1"/>
     <mergeCell ref="S1:AG1"/>
     <mergeCell ref="AL1:AQ1"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="Y2:AB2"/>
-    <mergeCell ref="AC2:AG2"/>
-    <mergeCell ref="AL2:AQ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
